--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -493,10 +493,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Validator</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B12" t="str">
-        <v>ICC-Profilvalidator</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="13">
@@ -629,10 +629,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Validator · powered by IccProfLib</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B29" t="str">
-        <v>ICC-Profilvalidator · betrieben mit IccProfLib</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="30">

--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B69"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -643,9 +643,321 @@
         <v>Fehler:</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B31" t="str">
+        <v>In XML konvertieren</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B32" t="str">
+        <v>In JSON konvertieren</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B33" t="str">
+        <v>In ICC konvertieren</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Konvertiere in XML…</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Konvertiere in JSON…</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Konvertiere in ICC…</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B37" t="str">
+        <v>ICC-Profil laden</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Profil-ID</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Keine Tags gefunden.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Tag-Name</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B42" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Größe</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Auffüllung</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Bytes seit dem Laden geändert</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Typ</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Array von {type}</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>(Kein Inhalt)</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Bytes</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Lade vollständige Beschreibung…</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Keine Validierungsausgabe</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Keine Warnungen oder Fehler gefunden.</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Gültig</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Warnung</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Fehler</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Unbekannt</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B63" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B64" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Profile written from edits, but re-validation failed:</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B79"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -869,95 +869,175 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B59" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B60" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B61" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B62" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B63" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B64" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B65" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B66" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B67" t="str">
-        <v>Einrückung</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B68" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B73" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B74" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B69" t="str">
+      <c r="B79" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B81"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -821,223 +821,239 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B53" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B54" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B55" t="str">
-        <v>Gültig</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B56" t="str">
-        <v>Warnung</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B57" t="str">
-        <v>Fehler</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B58" t="str">
-        <v>Unbekannt</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B59" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B60" t="str">
-        <v>Validierungsdetail</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B61" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B62" t="str">
-        <v>Feld</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B63" t="str">
-        <v>Aktueller Wert</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B64" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B65" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B66" t="str">
-        <v>Ungültig</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B67" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B68" t="str">
-        <v>Schließen</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B69" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B70" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B71" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B72" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B73" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B74" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B75" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B76" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B77" t="str">
-        <v>Einrückung</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B78" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B81" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B87"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -845,215 +845,263 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B56" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B57" t="str">
-        <v>Gültig</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Warning</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B58" t="str">
-        <v>Warnung</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Error</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B59" t="str">
-        <v>Fehler</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B60" t="str">
-        <v>Unbekannt</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B61" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B62" t="str">
-        <v>Validierungsdetail</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B63" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B64" t="str">
-        <v>Feld</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B65" t="str">
-        <v>Aktueller Wert</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B66" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Expected: {value}</v>
+        <v>View in context</v>
       </c>
       <c r="B67" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Invalid</v>
+        <v>Validation detail</v>
       </c>
       <c r="B68" t="str">
-        <v>Ungültig</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Triggered by</v>
       </c>
       <c r="B69" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Close</v>
+        <v>Field</v>
       </c>
       <c r="B70" t="str">
-        <v>Schließen</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Loading XML editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B71" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B72" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B73" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B74" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>● unsaved XML edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B75" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Close</v>
       </c>
       <c r="B76" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B77" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B78" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>indent</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B79" t="str">
-        <v>Einrückung</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B80" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B81" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B82" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B87" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B98"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,503 +605,591 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Raw Output</v>
+        <v>Profile Assessment WG</v>
       </c>
       <c r="B26" t="str">
-        <v>Rohausgabe</v>
+        <v>Profile Assessment WG</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B27" t="str">
-        <v>XML</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>JSON</v>
       </c>
       <c r="B29" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Error:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B30" t="str">
-        <v>Fehler:</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Convert to XML</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B31" t="str">
-        <v>In XML konvertieren</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Convert to JSON</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B32" t="str">
-        <v>In JSON konvertieren</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Convert to ICC</v>
+        <v>Security</v>
       </c>
       <c r="B33" t="str">
-        <v>In ICC konvertieren</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Converting to XML…</v>
+        <v>Conformance</v>
       </c>
       <c r="B34" t="str">
-        <v>Konvertiere in XML…</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Converting to JSON…</v>
+        <v>Quality</v>
       </c>
       <c r="B35" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Converting to ICC…</v>
+        <v>REPORT</v>
       </c>
       <c r="B36" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Load ICC profile</v>
+        <v>FAIL</v>
       </c>
       <c r="B37" t="str">
-        <v>ICC-Profil laden</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>checks</v>
       </c>
       <c r="B38" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Profile ID</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B39" t="str">
-        <v>Profil-ID</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B40" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B41" t="str">
-        <v>Tag-Name</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B42" t="str">
-        <v>ID</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B43" t="str">
-        <v>Offset</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B44" t="str">
-        <v>Größe</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B45" t="str">
-        <v>Auffüllung</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B46" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B47" t="str">
-        <v>Typ</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B48" t="str">
-        <v>Array von {type}</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B49" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B50" t="str">
-        <v>Bytes</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B51" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B52" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B53" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B54" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B55" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B56" t="str">
-        <v>Profil ist gültig</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B57" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B58" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B59" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B60" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B61" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B62" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B63" t="str">
-        <v>Gültig</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B64" t="str">
-        <v>Warnung</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B65" t="str">
-        <v>Fehler</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B66" t="str">
-        <v>Unbekannt</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B67" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B68" t="str">
-        <v>Validierungsdetail</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B69" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B70" t="str">
-        <v>Feld</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B71" t="str">
-        <v>Aktueller Wert</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B72" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B73" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B74" t="str">
-        <v>Ungültig</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B75" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B76" t="str">
-        <v>Schließen</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B77" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B78" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B79" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B80" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B81" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B82" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B83" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B84" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B85" t="str">
-        <v>Einrückung</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B86" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B92" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B93" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B98" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B100"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -637,23 +637,23 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -661,7 +661,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Security</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -669,7 +669,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Conformance</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -677,7 +677,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Quality</v>
+        <v>Security</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -685,7 +685,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>REPORT</v>
+        <v>Conformance</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -693,7 +693,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FAIL</v>
+        <v>Quality</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -701,7 +701,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -709,7 +709,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -717,479 +717,495 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B40" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Error:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B41" t="str">
-        <v>Fehler:</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Convert to XML</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B42" t="str">
-        <v>In XML konvertieren</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B43" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B44" t="str">
-        <v>In ICC konvertieren</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B45" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B46" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B47" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B48" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B49" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B50" t="str">
-        <v>Profil-ID</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B51" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B52" t="str">
-        <v>Tag-Name</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B53" t="str">
-        <v>ID</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B54" t="str">
-        <v>Offset</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B55" t="str">
-        <v>Größe</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B56" t="str">
-        <v>Auffüllung</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B57" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B58" t="str">
-        <v>Typ</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B59" t="str">
-        <v>Array von {type}</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B60" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B61" t="str">
-        <v>Bytes</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B62" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B63" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B64" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B65" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B66" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B67" t="str">
-        <v>Profil ist gültig</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B68" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B69" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B70" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B71" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B72" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B73" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B74" t="str">
-        <v>Gültig</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B75" t="str">
-        <v>Warnung</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B76" t="str">
-        <v>Fehler</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B77" t="str">
-        <v>Unbekannt</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B78" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B79" t="str">
-        <v>Validierungsdetail</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B80" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B81" t="str">
-        <v>Feld</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B82" t="str">
-        <v>Aktueller Wert</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B83" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B84" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B85" t="str">
-        <v>Ungültig</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B86" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B87" t="str">
-        <v>Schließen</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B88" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B89" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B90" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B91" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B92" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B93" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B94" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B95" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B96" t="str">
-        <v>Einrückung</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B97" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B100" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B129"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -512,12 +512,12 @@
         <v>specification using the</v>
       </c>
       <c r="B14" t="str">
-        <v>mit der Referenzimplementierung</v>
+        <v>mit der Demo-Implementierung</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>reference implementation.</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B15" t="str">
         <v>zu validieren.</v>
@@ -525,687 +525,919 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Validating…</v>
+        <v>Based on</v>
       </c>
       <c r="B16" t="str">
-        <v>Validierung…</v>
+        <v>Basierend auf der</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Save ICC profile</v>
+        <v>demo implementation</v>
       </c>
       <c r="B17" t="str">
-        <v>ICC-Profil speichern</v>
+        <v>Demo-Implementierung</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Validating…</v>
       </c>
       <c r="B18" t="str">
-        <v>● Geändert — nicht gespeichert</v>
+        <v>Validierung…</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B19" t="str">
-        <v>ICC-Profil hierher ziehen</v>
+        <v>ICC-Profil speichern</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>or</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B20" t="str">
-        <v>oder</v>
+        <v>● Geändert — nicht gespeichert</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Choose file</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B21" t="str">
-        <v>Datei wählen</v>
+        <v>ICC-Profil hierher ziehen</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>.icc and .icm files</v>
+        <v>or</v>
       </c>
       <c r="B22" t="str">
-        <v>.icc- und .icm-Dateien</v>
+        <v>oder</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Header</v>
+        <v>Choose file</v>
       </c>
       <c r="B23" t="str">
-        <v>Header</v>
+        <v>Datei wählen</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tags</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B24" t="str">
-        <v>Tags</v>
+        <v>.icc- und .icm-Dateien</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Validation</v>
+        <v>Header</v>
       </c>
       <c r="B25" t="str">
-        <v>Validierung</v>
+        <v>Header</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Profile Assessment WG</v>
+        <v>Tags</v>
       </c>
       <c r="B26" t="str">
-        <v>Profile Assessment WG</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Raw Output</v>
+        <v>Validation</v>
       </c>
       <c r="B27" t="str">
-        <v>Rohausgabe</v>
+        <v>Validierung</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>XML</v>
+        <v>Plot</v>
       </c>
       <c r="B28" t="str">
-        <v>XML</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>JSON</v>
+        <v>Raw Output</v>
       </c>
       <c r="B29" t="str">
-        <v>JSON</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Invalid profile URL:</v>
+        <v>XML</v>
       </c>
       <c r="B30" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>JSON</v>
       </c>
       <c r="B31" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Curves</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Input curves</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Output curves</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Security</v>
+        <v>CLUT image</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Conformance</v>
+        <v>Gamut image</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Quality</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>REPORT</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>FAIL</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>checks</v>
+        <v>Curve table</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Tables</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Data</v>
       </c>
       <c r="B42" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Error:</v>
+        <v>Evaluate</v>
       </c>
       <c r="B43" t="str">
-        <v>Fehler:</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to XML</v>
+        <v>Loading…</v>
       </c>
       <c r="B44" t="str">
-        <v>In XML konvertieren</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Convert to JSON</v>
+        <v>Input</v>
       </c>
       <c r="B45" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Convert to ICC</v>
+        <v>Output</v>
       </c>
       <c r="B46" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to XML…</v>
+        <v>Floating point</v>
       </c>
       <c r="B47" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Converting to JSON…</v>
+        <v>Grid point</v>
       </c>
       <c r="B48" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Converting to ICC…</v>
+        <v>Normalized</v>
       </c>
       <c r="B49" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Load ICC profile</v>
+        <v>Human</v>
       </c>
       <c r="B50" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B51" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Profile ID</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B52" t="str">
-        <v>Profil-ID</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No tags found.</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B53" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag Name</v>
+        <v>Loading…</v>
       </c>
       <c r="B54" t="str">
-        <v>Tag-Name</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ID</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B55" t="str">
-        <v>ID</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Offset</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B56" t="str">
-        <v>Offset</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Size</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B57" t="str">
-        <v>Größe</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Pad</v>
+        <v>Loading plot module…</v>
       </c>
       <c r="B58" t="str">
-        <v>Auffüllung</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bytes changed since load</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B59" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Type</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B60" t="str">
-        <v>Typ</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Array of {type}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B61" t="str">
-        <v>Array von {type}</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>(No content)</v>
+        <v>Security</v>
       </c>
       <c r="B62" t="str">
-        <v>(Kein Inhalt)</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>bytes</v>
+        <v>Conformance</v>
       </c>
       <c r="B63" t="str">
-        <v>Bytes</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Loading full description…</v>
+        <v>Quality</v>
       </c>
       <c r="B64" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Could not load full description:</v>
+        <v>REPORT</v>
       </c>
       <c r="B65" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>FAIL</v>
       </c>
       <c r="B66" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>checks</v>
       </c>
       <c r="B67" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No validation output</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B68" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is valid</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B69" t="str">
-        <v>Profil ist gültig</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Error:</v>
       </c>
       <c r="B70" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B71" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical validation error</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B72" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Unknown validation status</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B73" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B74" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B75" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B76" t="str">
-        <v>Gültig</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Warning</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B77" t="str">
-        <v>Warnung</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Error</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B78" t="str">
-        <v>Fehler</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Unknown</v>
+        <v>Profile ID</v>
       </c>
       <c r="B79" t="str">
-        <v>Unbekannt</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>View in context</v>
+        <v>No tags found.</v>
       </c>
       <c r="B80" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Validation detail</v>
+        <v>Tag Name</v>
       </c>
       <c r="B81" t="str">
-        <v>Validierungsdetail</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Triggered by</v>
+        <v>ID</v>
       </c>
       <c r="B82" t="str">
-        <v>Ausgelöst durch</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Field</v>
+        <v>Offset</v>
       </c>
       <c r="B83" t="str">
-        <v>Feld</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Current value</v>
+        <v>Size</v>
       </c>
       <c r="B84" t="str">
-        <v>Aktueller Wert</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Required: 0</v>
+        <v>Pad</v>
       </c>
       <c r="B85" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Expected: {value}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B86" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Invalid</v>
+        <v>Type</v>
       </c>
       <c r="B87" t="str">
-        <v>Ungültig</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B88" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Close</v>
+        <v>(No content)</v>
       </c>
       <c r="B89" t="str">
-        <v>Schließen</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading XML editor…</v>
+        <v>bytes</v>
       </c>
       <c r="B90" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B91" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B92" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B93" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B94" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>No validation output</v>
       </c>
       <c r="B95" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B96" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B97" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>indent</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B98" t="str">
-        <v>Einrückung</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>sort keys</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B99" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Unbekannter Validierungsstatus</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Keine Warnungen oder Fehler gefunden.</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Gültig</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Warnung</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Fehler</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Unbekannt</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Bestanden</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Fehlgeschlagen</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Im Kontext anzeigen</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Validierungsdetail</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Ausgelöst durch</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Feld</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Aktueller Wert</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Erforderlich: 0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Erwartet: {value}</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B123" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B124" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B129" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B128"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -861,583 +861,575 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading plot module…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Security</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Security</v>
+        <v>Conformance</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Conformance</v>
+        <v>Quality</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Quality</v>
+        <v>REPORT</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>REPORT</v>
+        <v>FAIL</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>FAIL</v>
+        <v>checks</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>checks</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Error:</v>
       </c>
       <c r="B69" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Error:</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B70" t="str">
-        <v>Fehler:</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to XML</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B71" t="str">
-        <v>In XML konvertieren</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B72" t="str">
-        <v>In JSON konvertieren</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B73" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to XML…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B74" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B75" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to ICC…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B76" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Load ICC profile</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B77" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Profile ID</v>
       </c>
       <c r="B78" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Profile ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B79" t="str">
-        <v>Profil-ID</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>No tags found.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B80" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tag Name</v>
+        <v>ID</v>
       </c>
       <c r="B81" t="str">
-        <v>Tag-Name</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ID</v>
+        <v>Offset</v>
       </c>
       <c r="B82" t="str">
-        <v>ID</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Offset</v>
+        <v>Size</v>
       </c>
       <c r="B83" t="str">
-        <v>Offset</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Size</v>
+        <v>Pad</v>
       </c>
       <c r="B84" t="str">
-        <v>Größe</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Pad</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B85" t="str">
-        <v>Auffüllung</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bytes changed since load</v>
+        <v>Type</v>
       </c>
       <c r="B86" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Type</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B87" t="str">
-        <v>Typ</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Array of {type}</v>
+        <v>(No content)</v>
       </c>
       <c r="B88" t="str">
-        <v>Array von {type}</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>(No content)</v>
+        <v>bytes</v>
       </c>
       <c r="B89" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>bytes</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B90" t="str">
-        <v>Bytes</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading full description…</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B91" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not load full description:</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B92" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B93" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>No validation output</v>
       </c>
       <c r="B94" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>No validation output</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B95" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile is valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B96" t="str">
-        <v>Profil ist gültig</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B97" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B98" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Critical validation error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B99" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B100" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B101" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Valid</v>
       </c>
       <c r="B102" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Valid</v>
+        <v>Warning</v>
       </c>
       <c r="B103" t="str">
-        <v>Gültig</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Warning</v>
+        <v>Error</v>
       </c>
       <c r="B104" t="str">
-        <v>Warnung</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Error</v>
+        <v>Unknown</v>
       </c>
       <c r="B105" t="str">
-        <v>Fehler</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Unknown</v>
+        <v>Pass</v>
       </c>
       <c r="B106" t="str">
-        <v>Unbekannt</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="B107" t="str">
-        <v>Bestanden</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Fail</v>
+        <v>View in context</v>
       </c>
       <c r="B108" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>View in context</v>
+        <v>Validation detail</v>
       </c>
       <c r="B109" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Validation detail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B110" t="str">
-        <v>Validierungsdetail</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Triggered by</v>
+        <v>Field</v>
       </c>
       <c r="B111" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Field</v>
+        <v>Current value</v>
       </c>
       <c r="B112" t="str">
-        <v>Feld</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Current value</v>
+        <v>Required: 0</v>
       </c>
       <c r="B113" t="str">
-        <v>Aktueller Wert</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Required: 0</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B114" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid</v>
       </c>
       <c r="B115" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Invalid</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B116" t="str">
-        <v>Ungültig</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Close</v>
       </c>
       <c r="B117" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Close</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B118" t="str">
-        <v>Schließen</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading XML editor…</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B119" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Loading JSON editor…</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B120" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B121" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B122" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved XML edits</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B123" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B124" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B125" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>indent</v>
       </c>
       <c r="B126" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Einrückung</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>indent</v>
+        <v>sort keys</v>
       </c>
       <c r="B127" t="str">
-        <v>Einrückung</v>
+        <v>Schlüssel sortieren</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>sort keys</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B128" t="str">
-        <v>Schlüssel sortieren</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B129" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B131"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -477,959 +477,983 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Help</v>
+        <v>Number format</v>
       </c>
       <c r="B10" t="str">
-        <v>Hilfe</v>
+        <v>Zahlenformat</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Contact</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B11" t="str">
-        <v>Kontakt</v>
+        <v>Hexadezimal</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Decimal</v>
       </c>
       <c r="B12" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Dezimal</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Help</v>
       </c>
       <c r="B13" t="str">
-        <v>Laden Sie ein ICC-Profil hoch, um es gegen die Spezifikation</v>
+        <v>Hilfe</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>specification using the</v>
+        <v>Contact</v>
       </c>
       <c r="B14" t="str">
-        <v>mit der Demo-Implementierung</v>
+        <v>Kontakt</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>demo implementation.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B15" t="str">
-        <v>zu validieren.</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Based on</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B16" t="str">
-        <v>Basierend auf der</v>
+        <v>Laden Sie ein ICC-Profil hoch, um es gegen die Spezifikation</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>demo implementation</v>
+        <v>specification using the</v>
       </c>
       <c r="B17" t="str">
-        <v>Demo-Implementierung</v>
+        <v>mit der Demo-Implementierung</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Validating…</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B18" t="str">
-        <v>Validierung…</v>
+        <v>zu validieren.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Save ICC profile</v>
+        <v>Based on</v>
       </c>
       <c r="B19" t="str">
-        <v>ICC-Profil speichern</v>
+        <v>Basierend auf der</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>demo implementation</v>
       </c>
       <c r="B20" t="str">
-        <v>● Geändert — nicht gespeichert</v>
+        <v>Demo-Implementierung</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Validating…</v>
       </c>
       <c r="B21" t="str">
-        <v>ICC-Profil hierher ziehen</v>
+        <v>Validierung…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>or</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B22" t="str">
-        <v>oder</v>
+        <v>ICC-Profil speichern</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Choose file</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B23" t="str">
-        <v>Datei wählen</v>
+        <v>● Geändert — nicht gespeichert</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>.icc and .icm files</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B24" t="str">
-        <v>.icc- und .icm-Dateien</v>
+        <v>ICC-Profil hierher ziehen</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Header</v>
+        <v>or</v>
       </c>
       <c r="B25" t="str">
-        <v>Header</v>
+        <v>oder</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Tags</v>
+        <v>Choose file</v>
       </c>
       <c r="B26" t="str">
-        <v>Tags</v>
+        <v>Datei wählen</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Validation</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B27" t="str">
-        <v>Validierung</v>
+        <v>.icc- und .icm-Dateien</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Plot</v>
+        <v>Header</v>
       </c>
       <c r="B28" t="str">
-        <v>Diagramm</v>
+        <v>Header</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Raw Output</v>
+        <v>Tags</v>
       </c>
       <c r="B29" t="str">
-        <v>Rohausgabe</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>XML</v>
+        <v>Validation</v>
       </c>
       <c r="B30" t="str">
-        <v>XML</v>
+        <v>Validierung</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>JSON</v>
+        <v>Plot</v>
       </c>
       <c r="B31" t="str">
-        <v>JSON</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B32" t="str">
-        <v>Kurven</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Input curves</v>
+        <v>XML</v>
       </c>
       <c r="B33" t="str">
-        <v>Eingangskurven</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Output curves</v>
+        <v>JSON</v>
       </c>
       <c r="B34" t="str">
-        <v>Ausgangskurven</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CLUT image</v>
+        <v>Curves</v>
       </c>
       <c r="B35" t="str">
-        <v>CLUT-Bild</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gamut image</v>
+        <v>Input curves</v>
       </c>
       <c r="B36" t="str">
-        <v>Gamut-Bild</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Chromaticity</v>
+        <v>Output curves</v>
       </c>
       <c r="B37" t="str">
-        <v>Chromazität</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Scatter plot</v>
+        <v>CLUT image</v>
       </c>
       <c r="B38" t="str">
-        <v>Streudiagramm</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Tone response curve</v>
+        <v>Gamut image</v>
       </c>
       <c r="B39" t="str">
-        <v>Tonwertkurve</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Curve table</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B40" t="str">
-        <v>Kurventabelle</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tables</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B41" t="str">
-        <v>Tabellen</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Data</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B42" t="str">
-        <v>Daten</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Evaluate</v>
+        <v>Curve table</v>
       </c>
       <c r="B43" t="str">
-        <v>Auswerten</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Loading…</v>
+        <v>Tables</v>
       </c>
       <c r="B44" t="str">
-        <v>Wird geladen…</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Input</v>
+        <v>Data</v>
       </c>
       <c r="B45" t="str">
-        <v>Eingang</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Output</v>
+        <v>Evaluate</v>
       </c>
       <c r="B46" t="str">
-        <v>Ausgang</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Floating point</v>
+        <v>Loading…</v>
       </c>
       <c r="B47" t="str">
-        <v>Gleitkomma</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Grid point</v>
+        <v>Input</v>
       </c>
       <c r="B48" t="str">
-        <v>Gitterpunkt</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Normalized</v>
+        <v>Output</v>
       </c>
       <c r="B49" t="str">
-        <v>Normalisiert</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Human</v>
+        <v>Floating point</v>
       </c>
       <c r="B50" t="str">
-        <v>Lesbar</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Device → PCS</v>
+        <v>Grid point</v>
       </c>
       <c r="B51" t="str">
-        <v>Gerät → PCS</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PCS → Device</v>
+        <v>Normalized</v>
       </c>
       <c r="B52" t="str">
-        <v>PCS → Gerät</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No CLUT grid</v>
+        <v>Human</v>
       </c>
       <c r="B53" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Loading…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B54" t="str">
-        <v>Wird geladen…</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B55" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Invalid profile URL:</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B56" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Loading…</v>
       </c>
       <c r="B57" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B58" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B59" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B60" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Security</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B61" t="str">
-        <v>Sicherheit</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Conformance</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B62" t="str">
-        <v>Konformität</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Quality</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B63" t="str">
-        <v>Qualität</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>REPORT</v>
+        <v>Security</v>
       </c>
       <c r="B64" t="str">
-        <v>BERICHT</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>FAIL</v>
+        <v>Conformance</v>
       </c>
       <c r="B65" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>checks</v>
+        <v>Quality</v>
       </c>
       <c r="B66" t="str">
-        <v>Prüfungen</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>REPORT</v>
       </c>
       <c r="B67" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>FAIL</v>
       </c>
       <c r="B68" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Error:</v>
+        <v>checks</v>
       </c>
       <c r="B69" t="str">
-        <v>Fehler:</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Convert to XML</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B70" t="str">
-        <v>In XML konvertieren</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to JSON</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B71" t="str">
-        <v>In JSON konvertieren</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to ICC</v>
+        <v>Error:</v>
       </c>
       <c r="B72" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B73" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B74" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B75" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B76" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B77" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Profile ID</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B78" t="str">
-        <v>Profil-ID</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>No tags found.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B79" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Tag Name</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B80" t="str">
-        <v>Tag-Name</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ID</v>
+        <v>Profile ID</v>
       </c>
       <c r="B81" t="str">
-        <v>ID</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Offset</v>
+        <v>No tags found.</v>
       </c>
       <c r="B82" t="str">
-        <v>Offset</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Size</v>
+        <v>Tag Name</v>
       </c>
       <c r="B83" t="str">
-        <v>Größe</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Pad</v>
+        <v>ID</v>
       </c>
       <c r="B84" t="str">
-        <v>Auffüllung</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bytes changed since load</v>
+        <v>Offset</v>
       </c>
       <c r="B85" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Type</v>
+        <v>Size</v>
       </c>
       <c r="B86" t="str">
-        <v>Typ</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Array of {type}</v>
+        <v>Pad</v>
       </c>
       <c r="B87" t="str">
-        <v>Array von {type}</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>(No content)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B88" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>bytes</v>
+        <v>Type</v>
       </c>
       <c r="B89" t="str">
-        <v>Bytes</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading full description…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B90" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Could not load full description:</v>
+        <v>(No content)</v>
       </c>
       <c r="B91" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>bytes</v>
       </c>
       <c r="B92" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B93" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>No validation output</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B94" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Profile is valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B95" t="str">
-        <v>Profil ist gültig</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B96" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile is non-compliant</v>
+        <v>No validation output</v>
       </c>
       <c r="B97" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B98" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B99" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B100" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B101" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Valid</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B102" t="str">
-        <v>Gültig</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Warning</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B103" t="str">
-        <v>Warnung</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B104" t="str">
-        <v>Fehler</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Unknown</v>
+        <v>Valid</v>
       </c>
       <c r="B105" t="str">
-        <v>Unbekannt</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Pass</v>
+        <v>Warning</v>
       </c>
       <c r="B106" t="str">
-        <v>Bestanden</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Fail</v>
+        <v>Error</v>
       </c>
       <c r="B107" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>View in context</v>
+        <v>Unknown</v>
       </c>
       <c r="B108" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Validation detail</v>
+        <v>Pass</v>
       </c>
       <c r="B109" t="str">
-        <v>Validierungsdetail</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Triggered by</v>
+        <v>Fail</v>
       </c>
       <c r="B110" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Field</v>
+        <v>View in context</v>
       </c>
       <c r="B111" t="str">
-        <v>Feld</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Current value</v>
+        <v>Validation detail</v>
       </c>
       <c r="B112" t="str">
-        <v>Aktueller Wert</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Required: 0</v>
+        <v>Triggered by</v>
       </c>
       <c r="B113" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Expected: {value}</v>
+        <v>Field</v>
       </c>
       <c r="B114" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Invalid</v>
+        <v>Current value</v>
       </c>
       <c r="B115" t="str">
-        <v>Ungültig</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B116" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Close</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B117" t="str">
-        <v>Schließen</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Loading XML editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B118" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading JSON editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B119" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B120" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B121" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B123" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B125" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>indent</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B126" t="str">
-        <v>Einrückung</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B127" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B128" t="str">
+      <c r="B131" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -885,575 +885,583 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B61" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B62" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B63" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B64" t="str">
-        <v>Sicherheit</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B65" t="str">
-        <v>Konformität</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B66" t="str">
-        <v>Qualität</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B67" t="str">
-        <v>BERICHT</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B68" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B69" t="str">
-        <v>Prüfungen</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B70" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B71" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Error:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B72" t="str">
-        <v>Fehler:</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B73" t="str">
-        <v>In XML konvertieren</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B74" t="str">
-        <v>In JSON konvertieren</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B75" t="str">
-        <v>In ICC konvertieren</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B76" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B77" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B78" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B79" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B80" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B81" t="str">
-        <v>Profil-ID</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B82" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B83" t="str">
-        <v>Tag-Name</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B84" t="str">
-        <v>ID</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B85" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B86" t="str">
-        <v>Größe</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B87" t="str">
-        <v>Auffüllung</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B88" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B89" t="str">
-        <v>Typ</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B90" t="str">
-        <v>Array von {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B91" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B92" t="str">
-        <v>Bytes</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B93" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B94" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B95" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B96" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B97" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B98" t="str">
-        <v>Profil ist gültig</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B99" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B100" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B101" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B102" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B103" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B104" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B105" t="str">
-        <v>Gültig</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B106" t="str">
-        <v>Warnung</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B107" t="str">
-        <v>Fehler</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B108" t="str">
-        <v>Unbekannt</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B109" t="str">
-        <v>Bestanden</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B110" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B111" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B112" t="str">
-        <v>Validierungsdetail</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B113" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B114" t="str">
-        <v>Feld</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B115" t="str">
-        <v>Aktueller Wert</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B116" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B117" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B118" t="str">
-        <v>Ungültig</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B119" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B120" t="str">
-        <v>Schließen</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B121" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B123" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B125" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B126" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B127" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B128" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B129" t="str">
-        <v>Einrückung</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B130" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Einrückung</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B131" t="str">
+      <c r="B132" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B132"/>
+  <dimension ref="A1:B181"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -645,823 +645,1215 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Plot</v>
+        <v>Analysis</v>
       </c>
       <c r="B31" t="str">
-        <v>Diagramm</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Raw Output</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B32" t="str">
-        <v>Rohausgabe</v>
+        <v>Neutralachsen-Einfärbung</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>XML</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B33" t="str">
-        <v>XML</v>
+        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>JSON</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B34" t="str">
-        <v>JSON</v>
+        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Curves</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B35" t="str">
-        <v>Kurven</v>
+        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Input curves</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B36" t="str">
-        <v>Eingangskurven</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Output curves</v>
+        <v>% ink</v>
       </c>
       <c r="B37" t="str">
-        <v>Ausgangskurven</v>
+        <v>% Farbe</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CLUT image</v>
+        <v>Perceptual</v>
       </c>
       <c r="B38" t="str">
-        <v>CLUT-Bild</v>
+        <v>Perzeptiv</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gamut image</v>
+        <v>Relative colorimetric</v>
       </c>
       <c r="B39" t="str">
-        <v>Gamut-Bild</v>
+        <v>Relativ farbmetrisch</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Chromaticity</v>
+        <v>Saturation</v>
       </c>
       <c r="B40" t="str">
-        <v>Chromazität</v>
+        <v>Sättigung</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Scatter plot</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B41" t="str">
-        <v>Streudiagramm</v>
+        <v>Kanäle mit vielen Umkehrungen zeigen nur die {shown} größten nach ΔL*.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Tone response curve</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B42" t="str">
-        <v>Tonwertkurve</v>
+        <v>Mehr anzeigen ({n})</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Curve table</v>
+        <v>All</v>
       </c>
       <c r="B43" t="str">
-        <v>Kurventabelle</v>
+        <v>Alle</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tables</v>
+        <v>Analysing…</v>
       </c>
       <c r="B44" t="str">
-        <v>Tabellen</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Data</v>
+        <v>Analysis</v>
       </c>
       <c r="B45" t="str">
-        <v>Daten</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Evaluate</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B46" t="str">
-        <v>Auswerten</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Loading…</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B47" t="str">
-        <v>Wird geladen…</v>
+        <v>L*-Tonwertumkehr</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Input</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B48" t="str">
-        <v>Eingang</v>
+        <v>Mehr Farbe sollte eine Farbe nie heller machen. Jeder Gerätekanal wird durchlaufen, die anderen bleiben fest; jeder Schritt, in dem L* steigt, wird markiert. Algorithmus ursprünglich von Harold Boll.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Output</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B49" t="str">
-        <v>Ausgang</v>
+        <v>Keine Gerät→PCS-CLUT in diesem Profil – die L*-Umkehrprüfung ist nicht anwendbar (z. B. ein Matrix-/TRC-Anzeigeprofil).</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Floating point</v>
+        <v>LUT table</v>
       </c>
       <c r="B50" t="str">
-        <v>Gleitkomma</v>
+        <v>LUT-Tabelle</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Grid point</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B51" t="str">
-        <v>Gitterpunkt</v>
+        <v>ΔL*-Schwelle (ε)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Normalized</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B52" t="str">
-        <v>Normalisiert</v>
+        <v>{n} Umkehrungen über ε = {eps}</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Human</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B53" t="str">
-        <v>Lesbar</v>
+        <v>Keine L*-Umkehrungen über ε = {eps}</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Device → PCS</v>
+        <v>Channel</v>
       </c>
       <c r="B54" t="str">
-        <v>Gerät → PCS</v>
+        <v>Kanal</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PCS → Device</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B55" t="str">
-        <v>PCS → Gerät</v>
+        <v>Farbe (niedrig → hoch)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No CLUT grid</v>
+        <v>Plot</v>
       </c>
       <c r="B56" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Loading…</v>
+        <v>Raw Output</v>
       </c>
       <c r="B57" t="str">
-        <v>Wird geladen…</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>XML</v>
       </c>
       <c r="B58" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Invalid profile URL:</v>
+        <v>JSON</v>
       </c>
       <c r="B59" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curves</v>
       </c>
       <c r="B60" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Input curves</v>
       </c>
       <c r="B61" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Output curves</v>
       </c>
       <c r="B62" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B63" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Gamut image</v>
       </c>
       <c r="B64" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Security</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B65" t="str">
-        <v>Sicherheit</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Conformance</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B66" t="str">
-        <v>Konformität</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Quality</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B67" t="str">
-        <v>Qualität</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>REPORT</v>
+        <v>Curve table</v>
       </c>
       <c r="B68" t="str">
-        <v>BERICHT</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>FAIL</v>
+        <v>Tables</v>
       </c>
       <c r="B69" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>checks</v>
+        <v>Data</v>
       </c>
       <c r="B70" t="str">
-        <v>Prüfungen</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B71" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading…</v>
       </c>
       <c r="B72" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Error:</v>
+        <v>Input</v>
       </c>
       <c r="B73" t="str">
-        <v>Fehler:</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to XML</v>
+        <v>Output</v>
       </c>
       <c r="B74" t="str">
-        <v>In XML konvertieren</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to JSON</v>
+        <v>Floating point</v>
       </c>
       <c r="B75" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Convert to ICC</v>
+        <v>Grid point</v>
       </c>
       <c r="B76" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to XML…</v>
+        <v>Normalized</v>
       </c>
       <c r="B77" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to JSON…</v>
+        <v>Human</v>
       </c>
       <c r="B78" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B79" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Load ICC profile</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B80" t="str">
-        <v>ICC-Profil laden</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B81" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Profile ID</v>
+        <v>Loading…</v>
       </c>
       <c r="B82" t="str">
-        <v>Profil-ID</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>No tags found.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B83" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Tag Name</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B84" t="str">
-        <v>Tag-Name</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ID</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B85" t="str">
-        <v>ID</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Offset</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B86" t="str">
-        <v>Offset</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Size</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B87" t="str">
-        <v>Größe</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Pad</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B88" t="str">
-        <v>Auffüllung</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B89" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Type</v>
+        <v>Security</v>
       </c>
       <c r="B90" t="str">
-        <v>Typ</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Array of {type}</v>
+        <v>Conformance</v>
       </c>
       <c r="B91" t="str">
-        <v>Array von {type}</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>(No content)</v>
+        <v>Quality</v>
       </c>
       <c r="B92" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>bytes</v>
+        <v>REPORT</v>
       </c>
       <c r="B93" t="str">
-        <v>Bytes</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading full description…</v>
+        <v>FAIL</v>
       </c>
       <c r="B94" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Could not load full description:</v>
+        <v>checks</v>
       </c>
       <c r="B95" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B96" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B97" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>No validation output</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B98" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile is valid</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B99" t="str">
-        <v>Profil ist gültig</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B100" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B101" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Critical validation error</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B102" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Unknown validation status</v>
+        <v>Close</v>
       </c>
       <c r="B103" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B104" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Email address</v>
       </c>
       <c r="B105" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Valid</v>
+        <v>you@example.com</v>
       </c>
       <c r="B106" t="str">
-        <v>Gültig</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Warning</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B107" t="str">
-        <v>Warnung</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Error</v>
+        <v>(optional)</v>
       </c>
       <c r="B108" t="str">
-        <v>Fehler</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Unknown</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B109" t="str">
-        <v>Unbekannt</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Pass</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B110" t="str">
-        <v>Bestanden</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Fail</v>
+        <v>Cancel</v>
       </c>
       <c r="B111" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>View in context</v>
+        <v>Subscribe</v>
       </c>
       <c r="B112" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Validation detail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B113" t="str">
-        <v>Validierungsdetail</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Triggered by</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B114" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Field</v>
+        <v>Close</v>
       </c>
       <c r="B115" t="str">
-        <v>Feld</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Current value</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B116" t="str">
-        <v>Aktueller Wert</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Required: 0</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B117" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Expected: {value}</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B118" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Invalid</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B119" t="str">
-        <v>Ungültig</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B120" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Close</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B121" t="str">
-        <v>Schließen</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading XML editor…</v>
+        <v>Error:</v>
       </c>
       <c r="B122" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B123" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B124" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B125" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B126" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B127" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B128" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B129" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>indent</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B130" t="str">
-        <v>Einrückung</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>sort keys</v>
+        <v>Profile ID</v>
       </c>
       <c r="B131" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Keine Tags gefunden.</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Tag-Name</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B134" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Größe</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Auffüllung</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Bytes seit dem Laden geändert</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Typ</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Array von {type}</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B141" t="str">
+        <v>(Kein Inhalt)</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Bytes</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Lade vollständige Beschreibung…</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Keine Validierungsausgabe</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Profil ist gültig</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Profil hat Warnung(en)</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Profil ist nicht konform</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Kritischer Validierungsfehler</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Unbekannter Validierungsstatus</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Keine Warnungen oder Fehler gefunden.</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Gültig</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Warnung</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Fehler</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Unbekannt</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Bestanden</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Fehlgeschlagen</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Im Kontext anzeigen</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Validierungsdetail</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Ausgelöst durch</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Feld</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Aktueller Wert</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Erforderlich: 0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Erwartet: {value}</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B175" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B176" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B132" t="str">
+      <c r="B181" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B190"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -517,1343 +517,1415 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ICC Profile Tool</v>
+        <v>User guide</v>
       </c>
       <c r="B15" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Benutzerhandbuch</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Search guide</v>
       </c>
       <c r="B16" t="str">
-        <v>Laden Sie ein ICC-Profil hoch, um es gegen die Spezifikation</v>
+        <v>Handbuch durchsuchen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>specification using the</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B17" t="str">
-        <v>mit der Demo-Implementierung</v>
+        <v>Benutzerhandbuch durchsuchen</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>demo implementation.</v>
+        <v>Previous match</v>
       </c>
       <c r="B18" t="str">
-        <v>zu validieren.</v>
+        <v>Vorheriger Treffer</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Based on</v>
+        <v>Next match</v>
       </c>
       <c r="B19" t="str">
-        <v>Basierend auf der</v>
+        <v>Nächster Treffer</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>demo implementation</v>
+        <v>Close user guide</v>
       </c>
       <c r="B20" t="str">
-        <v>Demo-Implementierung</v>
+        <v>Handbuch schließen</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Validating…</v>
+        <v>Loading…</v>
       </c>
       <c r="B21" t="str">
-        <v>Validierung…</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Save ICC profile</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B22" t="str">
-        <v>ICC-Profil speichern</v>
+        <v>Benutzerhandbuch konnte nicht geladen werden.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>None</v>
       </c>
       <c r="B23" t="str">
-        <v>● Geändert — nicht gespeichert</v>
+        <v>Keine</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B24" t="str">
-        <v>ICC-Profil hierher ziehen</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>or</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B25" t="str">
-        <v>oder</v>
+        <v>Laden Sie ein ICC-Profil hoch, um es gegen die Spezifikation</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Choose file</v>
+        <v>specification using the</v>
       </c>
       <c r="B26" t="str">
-        <v>Datei wählen</v>
+        <v>mit der Demo-Implementierung</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>.icc and .icm files</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B27" t="str">
-        <v>.icc- und .icm-Dateien</v>
+        <v>zu validieren.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Header</v>
+        <v>Based on</v>
       </c>
       <c r="B28" t="str">
-        <v>Header</v>
+        <v>Basierend auf der</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tags</v>
+        <v>demo implementation</v>
       </c>
       <c r="B29" t="str">
-        <v>Tags</v>
+        <v>Demo-Implementierung</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validation</v>
+        <v>Validating…</v>
       </c>
       <c r="B30" t="str">
-        <v>Validierung</v>
+        <v>Validierung…</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Analysis</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B31" t="str">
-        <v>Analyse</v>
+        <v>ICC-Profil speichern</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B32" t="str">
-        <v>Neutralachsen-Einfärbung</v>
+        <v>● Geändert — nicht gespeichert</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B33" t="str">
-        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
+        <v>ICC-Profil hierher ziehen</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>or</v>
       </c>
       <c r="B34" t="str">
-        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>oder</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Choose file</v>
       </c>
       <c r="B35" t="str">
-        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
+        <v>Datei wählen</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Rendering intent</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B36" t="str">
-        <v>Render-Intent</v>
+        <v>.icc- und .icm-Dateien</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>% ink</v>
+        <v>Header</v>
       </c>
       <c r="B37" t="str">
-        <v>% Farbe</v>
+        <v>Header</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Perceptual</v>
+        <v>Tags</v>
       </c>
       <c r="B38" t="str">
-        <v>Perzeptiv</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Relative colorimetric</v>
+        <v>Validation</v>
       </c>
       <c r="B39" t="str">
-        <v>Relativ farbmetrisch</v>
+        <v>Validierung</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Saturation</v>
+        <v>Analysis</v>
       </c>
       <c r="B40" t="str">
-        <v>Sättigung</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B41" t="str">
-        <v>Kanäle mit vielen Umkehrungen zeigen nur die {shown} größten nach ΔL*.</v>
+        <v>Neutralachsen-Einfärbung</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Show more ({n})</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B42" t="str">
-        <v>Mehr anzeigen ({n})</v>
+        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>All</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B43" t="str">
-        <v>Alle</v>
+        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Analysing…</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B44" t="str">
-        <v>Analyse läuft…</v>
+        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B45" t="str">
-        <v>Analyse</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>% ink</v>
       </c>
       <c r="B46" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v>% Farbe</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Perceptual</v>
       </c>
       <c r="B47" t="str">
-        <v>L*-Tonwertumkehr</v>
+        <v>Perzeptiv</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B48" t="str">
-        <v>Mehr Farbe sollte eine Farbe nie heller machen. Jeder Gerätekanal wird durchlaufen, die anderen bleiben fest; jeder Schritt, in dem L* steigt, wird markiert. Algorithmus ursprünglich von Harold Boll.</v>
+        <v>Relativ farbmetrisch</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B49" t="str">
-        <v>Keine Gerät→PCS-CLUT in diesem Profil – die L*-Umkehrprüfung ist nicht anwendbar (z. B. ein Matrix-/TRC-Anzeigeprofil).</v>
+        <v>Sättigung</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LUT table</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B50" t="str">
-        <v>LUT-Tabelle</v>
+        <v>Kanäle mit vielen Umkehrungen zeigen nur die {shown} größten nach ΔL*.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B51" t="str">
-        <v>ΔL*-Schwelle (ε)</v>
+        <v>Mehr anzeigen ({n})</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B52" t="str">
-        <v>{n} Umkehrungen über ε = {eps}</v>
+        <v>Alle</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Analysing…</v>
       </c>
       <c r="B53" t="str">
-        <v>Keine L*-Umkehrungen über ε = {eps}</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Channel</v>
+        <v>Analysis</v>
       </c>
       <c r="B54" t="str">
-        <v>Kanal</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ink (low → high)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B55" t="str">
-        <v>Farbe (niedrig → hoch)</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Plot</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B56" t="str">
-        <v>Diagramm</v>
+        <v>L*-Tonwertumkehr</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Raw Output</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B57" t="str">
-        <v>Rohausgabe</v>
+        <v>Mehr Farbe sollte eine Farbe nie heller machen. Jeder Gerätekanal wird durchlaufen, die anderen bleiben fest; jeder Schritt, in dem L* steigt, wird markiert. Algorithmus ursprünglich von Harold Boll.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>XML</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B58" t="str">
-        <v>XML</v>
+        <v>Keine Gerät→PCS-CLUT in diesem Profil – die L*-Umkehrprüfung ist nicht anwendbar (z. B. ein Matrix-/TRC-Anzeigeprofil).</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>JSON</v>
+        <v>LUT table</v>
       </c>
       <c r="B59" t="str">
-        <v>JSON</v>
+        <v>LUT-Tabelle</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B60" t="str">
-        <v>Kurven</v>
+        <v>ΔL*-Schwelle (ε)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Input curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B61" t="str">
-        <v>Eingangskurven</v>
+        <v>{n} Umkehrungen über ε = {eps}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Output curves</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B62" t="str">
-        <v>Ausgangskurven</v>
+        <v>Keine L*-Umkehrungen über ε = {eps}</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>CLUT image</v>
+        <v>Channel</v>
       </c>
       <c r="B63" t="str">
-        <v>CLUT-Bild</v>
+        <v>Kanal</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Gamut image</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B64" t="str">
-        <v>Gamut-Bild</v>
+        <v>Farbe (niedrig → hoch)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Chromaticity</v>
+        <v>Plot</v>
       </c>
       <c r="B65" t="str">
-        <v>Chromazität</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Scatter plot</v>
+        <v>Raw Output</v>
       </c>
       <c r="B66" t="str">
-        <v>Streudiagramm</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tone response curve</v>
+        <v>XML</v>
       </c>
       <c r="B67" t="str">
-        <v>Tonwertkurve</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curve table</v>
+        <v>JSON</v>
       </c>
       <c r="B68" t="str">
-        <v>Kurventabelle</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tables</v>
+        <v>Curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Tabellen</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Data</v>
+        <v>Input curves</v>
       </c>
       <c r="B70" t="str">
-        <v>Daten</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Evaluate</v>
+        <v>Output curves</v>
       </c>
       <c r="B71" t="str">
-        <v>Auswerten</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B72" t="str">
-        <v>Wird geladen…</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Input</v>
+        <v>Gamut image</v>
       </c>
       <c r="B73" t="str">
-        <v>Eingang</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Output</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B74" t="str">
-        <v>Ausgang</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Floating point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B75" t="str">
-        <v>Gleitkomma</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Grid point</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B76" t="str">
-        <v>Gitterpunkt</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Normalized</v>
+        <v>Curve table</v>
       </c>
       <c r="B77" t="str">
-        <v>Normalisiert</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Human</v>
+        <v>Tables</v>
       </c>
       <c r="B78" t="str">
-        <v>Lesbar</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Device → PCS</v>
+        <v>Data</v>
       </c>
       <c r="B79" t="str">
-        <v>Gerät → PCS</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PCS → Device</v>
+        <v>Evaluate</v>
       </c>
       <c r="B80" t="str">
-        <v>PCS → Gerät</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>No CLUT grid</v>
+        <v>Loading…</v>
       </c>
       <c r="B81" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Loading…</v>
+        <v>Input</v>
       </c>
       <c r="B82" t="str">
-        <v>Wird geladen…</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Output</v>
       </c>
       <c r="B83" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Floating point</v>
       </c>
       <c r="B84" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Grid point</v>
       </c>
       <c r="B85" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Normalized</v>
       </c>
       <c r="B86" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Human</v>
       </c>
       <c r="B87" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B88" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B89" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Security</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B90" t="str">
-        <v>Sicherheit</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Conformance</v>
+        <v>Loading…</v>
       </c>
       <c r="B91" t="str">
-        <v>Konformität</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Quality</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B92" t="str">
-        <v>Qualität</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>REPORT</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B93" t="str">
-        <v>BERICHT</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FAIL</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B94" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>checks</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B95" t="str">
-        <v>Prüfungen</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B96" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B97" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B98" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Powered by {lib}</v>
+        <v>Security</v>
       </c>
       <c r="B99" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Subscribe</v>
+        <v>Conformance</v>
       </c>
       <c r="B100" t="str">
-        <v>Abonnieren</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Quality</v>
       </c>
       <c r="B101" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Get notified about new releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B102" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Close</v>
+        <v>FAIL</v>
       </c>
       <c r="B103" t="str">
-        <v>Schließen</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>checks</v>
       </c>
       <c r="B104" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Email address</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B105" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B106" t="str">
-        <v>sie@example.com</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B107" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>(optional)</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B108" t="str">
-        <v>(optional)</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B109" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B110" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B111" t="str">
-        <v>Abbrechen</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B112" t="str">
-        <v>Abonnieren</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B113" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Email address</v>
       </c>
       <c r="B114" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B115" t="str">
-        <v>Schließen</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Privacy notice</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B116" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>(optional)</v>
       </c>
       <c r="B117" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B118" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Please check the form and try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B119" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B120" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B121" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Error:</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B122" t="str">
-        <v>Fehler:</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Convert to XML</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B123" t="str">
-        <v>In XML konvertieren</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Convert to JSON</v>
+        <v>Close</v>
       </c>
       <c r="B124" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Convert to ICC</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B125" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Converting to XML…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B126" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Converting to JSON…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B127" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Load ICC profile</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B130" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Profile ID</v>
+        <v>Error:</v>
       </c>
       <c r="B131" t="str">
-        <v>Profil-ID</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>No tags found.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B132" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Tag Name</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B133" t="str">
-        <v>Tag-Name</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ID</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B134" t="str">
-        <v>ID</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Offset</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B135" t="str">
-        <v>Offset</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Size</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B136" t="str">
-        <v>Größe</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pad</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B137" t="str">
-        <v>Auffüllung</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Bytes changed since load</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B138" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Type</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B139" t="str">
-        <v>Typ</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Array of {type}</v>
+        <v>Profile ID</v>
       </c>
       <c r="B140" t="str">
-        <v>Array von {type}</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>(No content)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B141" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>bytes</v>
+        <v>Tag Name</v>
       </c>
       <c r="B142" t="str">
-        <v>Bytes</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Loading full description…</v>
+        <v>ID</v>
       </c>
       <c r="B143" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Could not load full description:</v>
+        <v>Offset</v>
       </c>
       <c r="B144" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Size</v>
       </c>
       <c r="B145" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Pad</v>
       </c>
       <c r="B146" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>No validation output</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B147" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Profile is valid</v>
+        <v>Type</v>
       </c>
       <c r="B148" t="str">
-        <v>Profil ist gültig</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B149" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile is non-compliant</v>
+        <v>(No content)</v>
       </c>
       <c r="B150" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Critical validation error</v>
+        <v>bytes</v>
       </c>
       <c r="B151" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Unknown validation status</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B152" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B153" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No warnings or errors found.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B154" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B155" t="str">
-        <v>Gültig</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Warning</v>
+        <v>No validation output</v>
       </c>
       <c r="B156" t="str">
-        <v>Warnung</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B157" t="str">
-        <v>Fehler</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Unknown</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B158" t="str">
-        <v>Unbekannt</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Pass</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B159" t="str">
-        <v>Bestanden</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B160" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>View in context</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B161" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Validation detail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B162" t="str">
-        <v>Validierungsdetail</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Triggered by</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B163" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Field</v>
+        <v>Valid</v>
       </c>
       <c r="B164" t="str">
-        <v>Feld</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Current value</v>
+        <v>Warning</v>
       </c>
       <c r="B165" t="str">
-        <v>Aktueller Wert</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Required: 0</v>
+        <v>Error</v>
       </c>
       <c r="B166" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Expected: {value}</v>
+        <v>Unknown</v>
       </c>
       <c r="B167" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Invalid</v>
+        <v>Pass</v>
       </c>
       <c r="B168" t="str">
-        <v>Ungültig</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Fail</v>
       </c>
       <c r="B169" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>View in context</v>
       </c>
       <c r="B170" t="str">
-        <v>Schließen</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Loading XML editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B171" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B172" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B173" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B174" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B175" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B176" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B177" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B178" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>indent</v>
+        <v>Close</v>
       </c>
       <c r="B179" t="str">
-        <v>Einrückung</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>sort keys</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B184" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B185" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B181" t="str">
+      <c r="B190" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B200"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -797,330 +797,330 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B50" t="str">
-        <v>Kanäle mit vielen Umkehrungen zeigen nur die {shown} größten nach ΔL*.</v>
+        <v>Absolut farbmetrisch</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Show more ({n})</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B51" t="str">
-        <v>Mehr anzeigen ({n})</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>All</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B52" t="str">
-        <v>Alle</v>
+        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Analysing…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B53" t="str">
-        <v>Analyse läuft…</v>
+        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B54" t="str">
-        <v>Analyse</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B55" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v>Gamut-Volumen (ΔE³)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B56" t="str">
-        <v>L*-Tonwertumkehr</v>
+        <v>Roundtrip-ΔE</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>mean</v>
       </c>
       <c r="B57" t="str">
-        <v>Mehr Farbe sollte eine Farbe nie heller machen. Jeder Gerätekanal wird durchlaufen, die anderen bleiben fest; jeder Schritt, in dem L* steigt, wird markiert. Algorithmus ursprünglich von Harold Boll.</v>
+        <v>Mittel</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>P90</v>
       </c>
       <c r="B58" t="str">
-        <v>Keine Gerät→PCS-CLUT in diesem Profil – die L*-Umkehrprüfung ist nicht anwendbar (z. B. ein Matrix-/TRC-Anzeigeprofil).</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>LUT table</v>
+        <v>max</v>
       </c>
       <c r="B59" t="str">
-        <v>LUT-Tabelle</v>
+        <v>Max.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B60" t="str">
-        <v>ΔL*-Schwelle (ε)</v>
+        <v>Kanäle mit vielen Umkehrungen zeigen nur die {shown} größten nach ΔL*.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B61" t="str">
-        <v>{n} Umkehrungen über ε = {eps}</v>
+        <v>Mehr anzeigen ({n})</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B62" t="str">
-        <v>Keine L*-Umkehrungen über ε = {eps}</v>
+        <v>Alle</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Channel</v>
+        <v>Analysing…</v>
       </c>
       <c r="B63" t="str">
-        <v>Kanal</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ink (low → high)</v>
+        <v>Analysis</v>
       </c>
       <c r="B64" t="str">
-        <v>Farbe (niedrig → hoch)</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B65" t="str">
-        <v>Diagramm</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Raw Output</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B66" t="str">
-        <v>Rohausgabe</v>
+        <v>L*-Tonwertumkehr</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>XML</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B67" t="str">
-        <v>XML</v>
+        <v>Mehr Farbe sollte eine Farbe nie heller machen. Jeder Gerätekanal wird durchlaufen, die anderen bleiben fest; jeder Schritt, in dem L* steigt, wird markiert. Algorithmus ursprünglich von Harold Boll.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>JSON</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B68" t="str">
-        <v>JSON</v>
+        <v>Keine Gerät→PCS-CLUT in diesem Profil – die L*-Umkehrprüfung ist nicht anwendbar (z. B. ein Matrix-/TRC-Anzeigeprofil).</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Curves</v>
+        <v>LUT table</v>
       </c>
       <c r="B69" t="str">
-        <v>Kurven</v>
+        <v>LUT-Tabelle</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Input curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B70" t="str">
-        <v>Eingangskurven</v>
+        <v>ΔL*-Schwelle (ε)</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Output curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B71" t="str">
-        <v>Ausgangskurven</v>
+        <v>{n} Umkehrungen über ε = {eps}</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CLUT image</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B72" t="str">
-        <v>CLUT-Bild</v>
+        <v>Keine L*-Umkehrungen über ε = {eps}</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut image</v>
+        <v>Channel</v>
       </c>
       <c r="B73" t="str">
-        <v>Gamut-Bild</v>
+        <v>Kanal</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Chromaticity</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B74" t="str">
-        <v>Chromazität</v>
+        <v>Farbe (niedrig → hoch)</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Scatter plot</v>
+        <v>Plot</v>
       </c>
       <c r="B75" t="str">
-        <v>Streudiagramm</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tone response curve</v>
+        <v>Raw Output</v>
       </c>
       <c r="B76" t="str">
-        <v>Tonwertkurve</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Curve table</v>
+        <v>XML</v>
       </c>
       <c r="B77" t="str">
-        <v>Kurventabelle</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tables</v>
+        <v>JSON</v>
       </c>
       <c r="B78" t="str">
-        <v>Tabellen</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Data</v>
+        <v>Curves</v>
       </c>
       <c r="B79" t="str">
-        <v>Daten</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Evaluate</v>
+        <v>Input curves</v>
       </c>
       <c r="B80" t="str">
-        <v>Auswerten</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Loading…</v>
+        <v>Output curves</v>
       </c>
       <c r="B81" t="str">
-        <v>Wird geladen…</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Input</v>
+        <v>CLUT image</v>
       </c>
       <c r="B82" t="str">
-        <v>Eingang</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B83" t="str">
-        <v>Ausgang</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Floating point</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B84" t="str">
-        <v>Gleitkomma</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Grid point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B85" t="str">
-        <v>Gitterpunkt</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Normalized</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B86" t="str">
-        <v>Normalisiert</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Human</v>
+        <v>Curve table</v>
       </c>
       <c r="B87" t="str">
-        <v>Lesbar</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Device → PCS</v>
+        <v>Tables</v>
       </c>
       <c r="B88" t="str">
-        <v>Gerät → PCS</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PCS → Device</v>
+        <v>Data</v>
       </c>
       <c r="B89" t="str">
-        <v>PCS → Gerät</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>No CLUT grid</v>
+        <v>Evaluate</v>
       </c>
       <c r="B90" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="91">
@@ -1133,799 +1133,879 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Input</v>
       </c>
       <c r="B92" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Output</v>
       </c>
       <c r="B93" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Floating point</v>
       </c>
       <c r="B94" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Grid point</v>
       </c>
       <c r="B95" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Normalized</v>
       </c>
       <c r="B96" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Human</v>
       </c>
       <c r="B97" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B98" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Security</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B99" t="str">
-        <v>Sicherheit</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Conformance</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B100" t="str">
-        <v>Konformität</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Quality</v>
+        <v>Loading…</v>
       </c>
       <c r="B101" t="str">
-        <v>Qualität</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>REPORT</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B102" t="str">
-        <v>BERICHT</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>FAIL</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B103" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>checks</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B104" t="str">
-        <v>Prüfungen</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B105" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B106" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B107" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Powered by {lib}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B108" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Subscribe</v>
+        <v>Security</v>
       </c>
       <c r="B109" t="str">
-        <v>Abonnieren</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Conformance</v>
       </c>
       <c r="B110" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Get notified about new releases</v>
+        <v>Quality</v>
       </c>
       <c r="B111" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B112" t="str">
-        <v>Schließen</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B113" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B114" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B115" t="str">
-        <v>sie@example.com</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B116" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B117" t="str">
-        <v>(optional)</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B118" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B119" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B120" t="str">
-        <v>Abbrechen</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B121" t="str">
-        <v>Abonnieren</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B122" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B123" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B124" t="str">
-        <v>Schließen</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B125" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B126" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B127" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B128" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B129" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B130" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B131" t="str">
-        <v>Fehler:</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B132" t="str">
-        <v>In XML konvertieren</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B133" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B134" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B135" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B136" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B137" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B138" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B139" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B140" t="str">
-        <v>Profil-ID</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B141" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B142" t="str">
-        <v>Tag-Name</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B143" t="str">
-        <v>ID</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B144" t="str">
-        <v>Offset</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B145" t="str">
-        <v>Größe</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B146" t="str">
-        <v>Auffüllung</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B147" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B148" t="str">
-        <v>Typ</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B149" t="str">
-        <v>Array von {type}</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B150" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B151" t="str">
-        <v>Bytes</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B152" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B153" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B154" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B155" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B156" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B157" t="str">
-        <v>Profil ist gültig</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B158" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B159" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B160" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B161" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B162" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B163" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B164" t="str">
-        <v>Gültig</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B165" t="str">
-        <v>Warnung</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B166" t="str">
-        <v>Fehler</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B167" t="str">
-        <v>Unbekannt</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B168" t="str">
-        <v>Bestanden</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B169" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B170" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B171" t="str">
-        <v>Validierungsdetail</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B172" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B173" t="str">
-        <v>Feld</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B174" t="str">
-        <v>Aktueller Wert</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B175" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B176" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B177" t="str">
-        <v>Ungültig</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B178" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B179" t="str">
-        <v>Schließen</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B180" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B181" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B182" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B183" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B184" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B185" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B186" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B187" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B188" t="str">
-        <v>Einrückung</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B189" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B194" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B195" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B190" t="str">
+      <c r="B200" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B200"/>
+  <dimension ref="A1:B188"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -877,474 +877,474 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Analysing…</v>
       </c>
       <c r="B60" t="str">
-        <v>Kanäle mit vielen Umkehrungen zeigen nur die {shown} größten nach ΔL*.</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Show more ({n})</v>
+        <v>Analysis</v>
       </c>
       <c r="B61" t="str">
-        <v>Mehr anzeigen ({n})</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>All</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B62" t="str">
-        <v>Alle</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B63" t="str">
-        <v>Analyse läuft…</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B64" t="str">
-        <v>Analyse</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B65" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>L* Tone Reversal</v>
+        <v>JSON</v>
       </c>
       <c r="B66" t="str">
-        <v>L*-Tonwertumkehr</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Curves</v>
       </c>
       <c r="B67" t="str">
-        <v>Mehr Farbe sollte eine Farbe nie heller machen. Jeder Gerätekanal wird durchlaufen, die anderen bleiben fest; jeder Schritt, in dem L* steigt, wird markiert. Algorithmus ursprünglich von Harold Boll.</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Input curves</v>
       </c>
       <c r="B68" t="str">
-        <v>Keine Gerät→PCS-CLUT in diesem Profil – die L*-Umkehrprüfung ist nicht anwendbar (z. B. ein Matrix-/TRC-Anzeigeprofil).</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>LUT table</v>
+        <v>Output curves</v>
       </c>
       <c r="B69" t="str">
-        <v>LUT-Tabelle</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>CLUT image</v>
       </c>
       <c r="B70" t="str">
-        <v>ΔL*-Schwelle (ε)</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Gamut image</v>
       </c>
       <c r="B71" t="str">
-        <v>{n} Umkehrungen über ε = {eps}</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B72" t="str">
-        <v>Keine L*-Umkehrungen über ε = {eps}</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Channel</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B73" t="str">
-        <v>Kanal</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ink (low → high)</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B74" t="str">
-        <v>Farbe (niedrig → hoch)</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Plot</v>
+        <v>Curve table</v>
       </c>
       <c r="B75" t="str">
-        <v>Diagramm</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Raw Output</v>
+        <v>Tables</v>
       </c>
       <c r="B76" t="str">
-        <v>Rohausgabe</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>XML</v>
+        <v>Data</v>
       </c>
       <c r="B77" t="str">
-        <v>XML</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>JSON</v>
+        <v>Evaluate</v>
       </c>
       <c r="B78" t="str">
-        <v>JSON</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Curves</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>Kurven</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input curves</v>
+        <v>Input</v>
       </c>
       <c r="B80" t="str">
-        <v>Eingangskurven</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output curves</v>
+        <v>Output</v>
       </c>
       <c r="B81" t="str">
-        <v>Ausgangskurven</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CLUT image</v>
+        <v>Floating point</v>
       </c>
       <c r="B82" t="str">
-        <v>CLUT-Bild</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Gamut image</v>
+        <v>Grid point</v>
       </c>
       <c r="B83" t="str">
-        <v>Gamut-Bild</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Chromaticity</v>
+        <v>Normalized</v>
       </c>
       <c r="B84" t="str">
-        <v>Chromazität</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Scatter plot</v>
+        <v>Human</v>
       </c>
       <c r="B85" t="str">
-        <v>Streudiagramm</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Tone response curve</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B86" t="str">
-        <v>Tonwertkurve</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Curve table</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B87" t="str">
-        <v>Kurventabelle</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Tables</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B88" t="str">
-        <v>Tabellen</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Data</v>
+        <v>Loading…</v>
       </c>
       <c r="B89" t="str">
-        <v>Daten</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Evaluate</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B90" t="str">
-        <v>Auswerten</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B91" t="str">
-        <v>Wird geladen…</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Input</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B92" t="str">
-        <v>Eingang</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Output</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B93" t="str">
-        <v>Ausgang</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Floating point</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B94" t="str">
-        <v>Gleitkomma</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grid point</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B95" t="str">
-        <v>Gitterpunkt</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Normalized</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B96" t="str">
-        <v>Normalisiert</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Human</v>
+        <v>Security</v>
       </c>
       <c r="B97" t="str">
-        <v>Lesbar</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Device → PCS</v>
+        <v>Conformance</v>
       </c>
       <c r="B98" t="str">
-        <v>Gerät → PCS</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>PCS → Device</v>
+        <v>Quality</v>
       </c>
       <c r="B99" t="str">
-        <v>PCS → Gerät</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No CLUT grid</v>
+        <v>REPORT</v>
       </c>
       <c r="B100" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Loading…</v>
+        <v>FAIL</v>
       </c>
       <c r="B101" t="str">
-        <v>Wird geladen…</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>checks</v>
       </c>
       <c r="B102" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B103" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B104" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B105" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B106" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Subscribe</v>
       </c>
       <c r="B107" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B108" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Security</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B109" t="str">
-        <v>Sicherheit</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Conformance</v>
+        <v>Close</v>
       </c>
       <c r="B110" t="str">
-        <v>Konformität</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Quality</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B111" t="str">
-        <v>Qualität</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>REPORT</v>
+        <v>Email address</v>
       </c>
       <c r="B112" t="str">
-        <v>BERICHT</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>FAIL</v>
+        <v>you@example.com</v>
       </c>
       <c r="B113" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>checks</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B114" t="str">
-        <v>Prüfungen</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>(optional)</v>
       </c>
       <c r="B115" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B116" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ICC Profile Tool</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B117" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Powered by {lib}</v>
+        <v>Cancel</v>
       </c>
       <c r="B118" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="119">
@@ -1357,18 +1357,18 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B120" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Get notified about new releases</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B121" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="122">
@@ -1381,631 +1381,535 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B123" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Email address</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B124" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>you@example.com</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B125" t="str">
-        <v>sie@example.com</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B126" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>(optional)</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>(optional)</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Error:</v>
       </c>
       <c r="B129" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Cancel</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B130" t="str">
-        <v>Abbrechen</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Subscribe</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B131" t="str">
-        <v>Abonnieren</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B132" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B133" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Close</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B134" t="str">
-        <v>Schließen</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Privacy notice</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B135" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B136" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B137" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B138" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B139" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B140" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Error:</v>
+        <v>ID</v>
       </c>
       <c r="B141" t="str">
-        <v>Fehler:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Convert to XML</v>
+        <v>Offset</v>
       </c>
       <c r="B142" t="str">
-        <v>In XML konvertieren</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Convert to JSON</v>
+        <v>Size</v>
       </c>
       <c r="B143" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Convert to ICC</v>
+        <v>Pad</v>
       </c>
       <c r="B144" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Converting to XML…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B145" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Converting to JSON…</v>
+        <v>Type</v>
       </c>
       <c r="B146" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Converting to ICC…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B147" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Load ICC profile</v>
+        <v>(No content)</v>
       </c>
       <c r="B148" t="str">
-        <v>ICC-Profil laden</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>bytes</v>
       </c>
       <c r="B149" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile ID</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B150" t="str">
-        <v>Profil-ID</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>No tags found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B151" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Tag Name</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B152" t="str">
-        <v>Tag-Name</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ID</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B153" t="str">
-        <v>ID</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Offset</v>
+        <v>No validation output</v>
       </c>
       <c r="B154" t="str">
-        <v>Offset</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Size</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B155" t="str">
-        <v>Größe</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Pad</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B156" t="str">
-        <v>Auffüllung</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B157" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Type</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B158" t="str">
-        <v>Typ</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Array of {type}</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B159" t="str">
-        <v>Array von {type}</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>(No content)</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B160" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>bytes</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B161" t="str">
-        <v>Bytes</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Loading full description…</v>
+        <v>Valid</v>
       </c>
       <c r="B162" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Could not load full description:</v>
+        <v>Warning</v>
       </c>
       <c r="B163" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error</v>
       </c>
       <c r="B164" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Unknown</v>
       </c>
       <c r="B165" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>No validation output</v>
+        <v>Pass</v>
       </c>
       <c r="B166" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Profile is valid</v>
+        <v>Fail</v>
       </c>
       <c r="B167" t="str">
-        <v>Profil ist gültig</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Profile has warning(s)</v>
+        <v>View in context</v>
       </c>
       <c r="B168" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Validation detail</v>
       </c>
       <c r="B169" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Critical validation error</v>
+        <v>Triggered by</v>
       </c>
       <c r="B170" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Unknown validation status</v>
+        <v>Field</v>
       </c>
       <c r="B171" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Current value</v>
       </c>
       <c r="B172" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B173" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Valid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B174" t="str">
-        <v>Gültig</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Warning</v>
+        <v>Invalid</v>
       </c>
       <c r="B175" t="str">
-        <v>Warnung</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Error</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B176" t="str">
-        <v>Fehler</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Unknown</v>
+        <v>Close</v>
       </c>
       <c r="B177" t="str">
-        <v>Unbekannt</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Pass</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B178" t="str">
-        <v>Bestanden</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Fail</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>View in context</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B180" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Validation detail</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>Validierungsdetail</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Triggered by</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B182" t="str">
-        <v>Ausgelöst durch</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Field</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B183" t="str">
-        <v>Feld</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Current value</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B184" t="str">
-        <v>Aktueller Wert</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Required: 0</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Expected: {value}</v>
+        <v>indent</v>
       </c>
       <c r="B186" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Einrückung</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Invalid</v>
+        <v>sort keys</v>
       </c>
       <c r="B187" t="str">
-        <v>Ungültig</v>
+        <v>Schlüssel sortieren</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B188" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>Close</v>
-      </c>
-      <c r="B189" t="str">
-        <v>Schließen</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Loading XML editor…</v>
-      </c>
-      <c r="B190" t="str">
-        <v>Lade XML-Editor…</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Loading JSON editor…</v>
-      </c>
-      <c r="B191" t="str">
-        <v>Lade JSON-Editor…</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B192" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B193" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>● unsaved XML edits</v>
-      </c>
-      <c r="B194" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>● unsaved JSON edits</v>
-      </c>
-      <c r="B195" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B196" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B197" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B198" t="str">
-        <v>Einrückung</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B199" t="str">
-        <v>Schlüssel sortieren</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B200" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B188"/>
+  <dimension ref="A1:B189"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -853,1063 +853,1071 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B57" t="str">
-        <v>Mittel</v>
+        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B58" t="str">
-        <v>P90</v>
+        <v>Mittel</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B59" t="str">
-        <v>Max.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B60" t="str">
-        <v>Analyse läuft…</v>
+        <v>Max.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B61" t="str">
-        <v>Analyse</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B62" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B63" t="str">
-        <v>Diagramm</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B64" t="str">
-        <v>Rohausgabe</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B65" t="str">
-        <v>XML</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B67" t="str">
-        <v>Kurven</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B68" t="str">
-        <v>Eingangskurven</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Ausgangskurven</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B70" t="str">
-        <v>CLUT-Bild</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B71" t="str">
-        <v>Gamut-Bild</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B72" t="str">
-        <v>Chromazität</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B73" t="str">
-        <v>Streudiagramm</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B74" t="str">
-        <v>Tonwertkurve</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B75" t="str">
-        <v>Kurventabelle</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B76" t="str">
-        <v>Tabellen</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B77" t="str">
-        <v>Daten</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B78" t="str">
-        <v>Auswerten</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B79" t="str">
-        <v>Wird geladen…</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B80" t="str">
-        <v>Eingang</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B81" t="str">
-        <v>Ausgang</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B82" t="str">
-        <v>Gleitkomma</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B83" t="str">
-        <v>Gitterpunkt</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B84" t="str">
-        <v>Normalisiert</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B85" t="str">
-        <v>Lesbar</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B86" t="str">
-        <v>Gerät → PCS</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B87" t="str">
-        <v>PCS → Gerät</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B88" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B89" t="str">
-        <v>Wird geladen…</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B90" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B91" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B92" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B93" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B94" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B95" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B96" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B97" t="str">
-        <v>Sicherheit</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B98" t="str">
-        <v>Konformität</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B99" t="str">
-        <v>Qualität</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B100" t="str">
-        <v>BERICHT</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B101" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B102" t="str">
-        <v>Prüfungen</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B103" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B104" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B105" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B106" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B107" t="str">
-        <v>Abonnieren</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B108" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B109" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B110" t="str">
-        <v>Schließen</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B111" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B112" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B113" t="str">
-        <v>sie@example.com</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B114" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B115" t="str">
-        <v>(optional)</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B116" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B117" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B118" t="str">
-        <v>Abbrechen</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B119" t="str">
-        <v>Abonnieren</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B120" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B121" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B122" t="str">
-        <v>Schließen</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B123" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B124" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B125" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B126" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>Fehler:</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B130" t="str">
-        <v>In XML konvertieren</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B131" t="str">
-        <v>In JSON konvertieren</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B132" t="str">
-        <v>In ICC konvertieren</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B133" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B134" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B135" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B136" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B137" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B138" t="str">
-        <v>Profil-ID</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B139" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B140" t="str">
-        <v>Tag-Name</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B141" t="str">
-        <v>ID</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B142" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B143" t="str">
-        <v>Größe</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B144" t="str">
-        <v>Auffüllung</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B145" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B146" t="str">
-        <v>Typ</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B147" t="str">
-        <v>Array von {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B148" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B149" t="str">
-        <v>Bytes</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B150" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B151" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B152" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B153" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B154" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B155" t="str">
-        <v>Profil ist gültig</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B156" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B157" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B158" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B159" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B160" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B161" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B162" t="str">
-        <v>Gültig</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B163" t="str">
-        <v>Warnung</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B164" t="str">
-        <v>Fehler</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B165" t="str">
-        <v>Unbekannt</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B166" t="str">
-        <v>Bestanden</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B167" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B168" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B169" t="str">
-        <v>Validierungsdetail</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B170" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B171" t="str">
-        <v>Feld</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B172" t="str">
-        <v>Aktueller Wert</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B173" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B174" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B175" t="str">
-        <v>Ungültig</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B176" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B177" t="str">
-        <v>Schließen</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B178" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B182" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B183" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B184" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B186" t="str">
-        <v>Einrückung</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B187" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Einrückung</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B188" t="str">
+      <c r="B189" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B236"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,1511 +413,1887 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Settings</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B2" t="str">
-        <v>Einstellungen</v>
+        <v>Rundlauf (PRMG)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Display</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B3" t="str">
-        <v>Anzeige</v>
+        <v>Rundlauf über den Gerätewürfel des Profils, entsprechend dem Referenzwerkzeug iccRoundTrip. Rundlauf 1 ist der Fehler Gerät→PCS→Gerät (ΔE*ab); Rundlauf 2 misst die Stabilität des PCS-Rundlaufs. Das PRMG-Histogramm zeigt die Interoperabilität gegenüber dem Perceptual Reference Medium Gamut.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Background</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B4" t="str">
-        <v>Hintergrund</v>
+        <v>MPE-(Farb-)Tags verwenden</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Language</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B5" t="str">
-        <v>Sprache</v>
+        <v>Für dieses Profil ist kein Rundlauf möglich – es fehlen die dafür nötigen Gerät↔PCS-Transformationen (z. B. ein Einweg- oder abstraktes Profil).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>System</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B6" t="str">
-        <v>System</v>
+        <v>Rundlauf übersprungen: Der Gerätefarbraum ist zu groß für die Auswertung (zu viele Abtastwerte).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Light</v>
+        <v>Metric</v>
       </c>
       <c r="B7" t="str">
-        <v>Hell</v>
+        <v>Metrik</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dark</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B8" t="str">
-        <v>Dunkel</v>
+        <v>Rundlauf 1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>System default</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B9" t="str">
-        <v>Systemstandard</v>
+        <v>Rundlauf 2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Number format</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B10" t="str">
-        <v>Zahlenformat</v>
+        <v>Gerät → PCS → Gerät</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Hexadecimal</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B11" t="str">
-        <v>Hexadezimal</v>
+        <v>Stabilität des PCS-Rundlaufs</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Decimal</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B12" t="str">
-        <v>Dezimal</v>
+        <v>Min ΔE</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Help</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>Hilfe</v>
+        <v>Mittel ΔE</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Contact</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>Kontakt</v>
+        <v>Max ΔE</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>User guide</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B15" t="str">
-        <v>Benutzerhandbuch</v>
+        <v>Schlechteste L, a, b</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Search guide</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B16" t="str">
-        <v>Handbuch durchsuchen</v>
+        <v>Angegebener Gamut</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Search the user guide</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>Benutzerhandbuch durchsuchen</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Previous match</v>
+        <v>Not specified</v>
       </c>
       <c r="B18" t="str">
-        <v>Vorheriger Treffer</v>
+        <v>Nicht angegeben</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Next match</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B19" t="str">
-        <v>Nächster Treffer</v>
+        <v>Nicht ausgewertet</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Close user guide</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B20" t="str">
-        <v>Handbuch schließen</v>
+        <v>PRMG-Interoperabilität</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B21" t="str">
-        <v>Wird geladen…</v>
+        <v>Rundlauf-ΔE</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Count</v>
       </c>
       <c r="B22" t="str">
-        <v>Benutzerhandbuch konnte nicht geladen werden.</v>
+        <v>Anzahl</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>None</v>
+        <v>Share</v>
       </c>
       <c r="B23" t="str">
-        <v>Keine</v>
+        <v>Anteil</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Total</v>
       </c>
       <c r="B24" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Gesamt</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B25" t="str">
-        <v>Laden Sie ein ICC-Profil hoch, um es gegen die Spezifikation</v>
+        <v>PRMG nicht ausgewertet</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>specification using the</v>
+        <v>Settings</v>
       </c>
       <c r="B26" t="str">
-        <v>mit der Demo-Implementierung</v>
+        <v>Einstellungen</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>demo implementation.</v>
+        <v>Display</v>
       </c>
       <c r="B27" t="str">
-        <v>zu validieren.</v>
+        <v>Anzeige</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Based on</v>
+        <v>Background</v>
       </c>
       <c r="B28" t="str">
-        <v>Basierend auf der</v>
+        <v>Hintergrund</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>demo implementation</v>
+        <v>Language</v>
       </c>
       <c r="B29" t="str">
-        <v>Demo-Implementierung</v>
+        <v>Sprache</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validating…</v>
+        <v>System</v>
       </c>
       <c r="B30" t="str">
-        <v>Validierung…</v>
+        <v>System</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Save ICC profile</v>
+        <v>Light</v>
       </c>
       <c r="B31" t="str">
-        <v>ICC-Profil speichern</v>
+        <v>Hell</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Dark</v>
       </c>
       <c r="B32" t="str">
-        <v>● Geändert — nicht gespeichert</v>
+        <v>Dunkel</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>System default</v>
       </c>
       <c r="B33" t="str">
-        <v>ICC-Profil hierher ziehen</v>
+        <v>Systemstandard</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>or</v>
+        <v>Number format</v>
       </c>
       <c r="B34" t="str">
-        <v>oder</v>
+        <v>Zahlenformat</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Choose file</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B35" t="str">
-        <v>Datei wählen</v>
+        <v>Hexadezimal</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>.icc and .icm files</v>
+        <v>Decimal</v>
       </c>
       <c r="B36" t="str">
-        <v>.icc- und .icm-Dateien</v>
+        <v>Dezimal</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Header</v>
+        <v>Help</v>
       </c>
       <c r="B37" t="str">
-        <v>Header</v>
+        <v>Hilfe</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tags</v>
+        <v>Contact</v>
       </c>
       <c r="B38" t="str">
-        <v>Tags</v>
+        <v>Kontakt</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Validation</v>
+        <v>User guide</v>
       </c>
       <c r="B39" t="str">
-        <v>Validierung</v>
+        <v>Benutzerhandbuch</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Analysis</v>
+        <v>Search guide</v>
       </c>
       <c r="B40" t="str">
-        <v>Analyse</v>
+        <v>Handbuch durchsuchen</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B41" t="str">
-        <v>Neutralachsen-Einfärbung</v>
+        <v>Benutzerhandbuch durchsuchen</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Previous match</v>
       </c>
       <c r="B42" t="str">
-        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
+        <v>Vorheriger Treffer</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Next match</v>
       </c>
       <c r="B43" t="str">
-        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Nächster Treffer</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Close user guide</v>
       </c>
       <c r="B44" t="str">
-        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
+        <v>Handbuch schließen</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Rendering intent</v>
+        <v>Loading…</v>
       </c>
       <c r="B45" t="str">
-        <v>Render-Intent</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>% ink</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B46" t="str">
-        <v>% Farbe</v>
+        <v>Benutzerhandbuch konnte nicht geladen werden.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Perceptual</v>
+        <v>None</v>
       </c>
       <c r="B47" t="str">
-        <v>Perzeptiv</v>
+        <v>Keine</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Relative Colorimetric</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B48" t="str">
-        <v>Relativ farbmetrisch</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Saturation</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B49" t="str">
-        <v>Sättigung</v>
+        <v>Laden Sie ein ICC-Profil hoch, um es gegen die Spezifikation</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>specification using the</v>
       </c>
       <c r="B50" t="str">
-        <v>Absolut farbmetrisch</v>
+        <v>mit der Demo-Implementierung</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Profile Statistics</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B51" t="str">
-        <v>Profilstatistik</v>
+        <v>zu validieren.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Based on</v>
       </c>
       <c r="B52" t="str">
-        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
+        <v>Basierend auf der</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>demo implementation</v>
       </c>
       <c r="B53" t="str">
-        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
+        <v>Demo-Implementierung</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Rendering intent</v>
+        <v>Validating…</v>
       </c>
       <c r="B54" t="str">
-        <v>Render-Intent</v>
+        <v>Validierung…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B55" t="str">
-        <v>Gamut-Volumen (ΔE³)</v>
+        <v>ICC-Profil speichern</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Round-trip ΔE</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B56" t="str">
-        <v>Roundtrip-ΔE</v>
+        <v>● Geändert — nicht gespeichert</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Profiles</v>
       </c>
       <c r="B57" t="str">
-        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mean</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B58" t="str">
-        <v>Mittel</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>P90</v>
+        <v>Collapse</v>
       </c>
       <c r="B59" t="str">
-        <v>P90</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>max</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B60" t="str">
-        <v>Max.</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysing…</v>
+        <v>Remove</v>
       </c>
       <c r="B61" t="str">
-        <v>Analyse läuft…</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Analysis</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B62" t="str">
-        <v>Analyse</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>or use “Load Profiles” — files stay on your device.</v>
       </c>
       <c r="B63" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Plot</v>
+        <v>Profile</v>
       </c>
       <c r="B64" t="str">
-        <v>Diagramm</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Raw Output</v>
+        <v>Compare</v>
       </c>
       <c r="B65" t="str">
-        <v>Rohausgabe</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>XML</v>
+        <v>Link</v>
       </c>
       <c r="B66" t="str">
-        <v>XML</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>JSON</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B67" t="str">
-        <v>JSON</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curves</v>
+        <v>Remove</v>
       </c>
       <c r="B68" t="str">
-        <v>Kurven</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Input curves</v>
+        <v>No profile selected</v>
       </c>
       <c r="B69" t="str">
-        <v>Eingangskurven</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Output curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B70" t="str">
-        <v>Ausgangskurven</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>CLUT image</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B71" t="str">
-        <v>CLUT-Bild</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Gamut image</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B72" t="str">
-        <v>Gamut-Bild</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B73" t="str">
-        <v>Chromazität</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Scatter plot</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B74" t="str">
-        <v>Streudiagramm</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tone response curve</v>
+        <v>Linking</v>
       </c>
       <c r="B75" t="str">
-        <v>Tonwertkurve</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Curve table</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B76" t="str">
-        <v>Kurventabelle</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Tables</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B77" t="str">
-        <v>Tabellen</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Data</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B78" t="str">
-        <v>Daten</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Evaluate</v>
+        <v>OK</v>
       </c>
       <c r="B79" t="str">
-        <v>Auswerten</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Loading…</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B80" t="str">
-        <v>Wird geladen…</v>
+        <v>ICC-Profil hierher ziehen</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Input</v>
+        <v>or</v>
       </c>
       <c r="B81" t="str">
-        <v>Eingang</v>
+        <v>oder</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Output</v>
+        <v>Choose file</v>
       </c>
       <c r="B82" t="str">
-        <v>Ausgang</v>
+        <v>Datei wählen</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Floating point</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B83" t="str">
-        <v>Gleitkomma</v>
+        <v>.icc- und .icm-Dateien</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Grid point</v>
+        <v>Header</v>
       </c>
       <c r="B84" t="str">
-        <v>Gitterpunkt</v>
+        <v>Header</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Normalized</v>
+        <v>Tags</v>
       </c>
       <c r="B85" t="str">
-        <v>Normalisiert</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Human</v>
+        <v>Validation</v>
       </c>
       <c r="B86" t="str">
-        <v>Lesbar</v>
+        <v>Validierung</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Device → PCS</v>
+        <v>Analysis</v>
       </c>
       <c r="B87" t="str">
-        <v>Gerät → PCS</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B88" t="str">
-        <v>PCS → Gerät</v>
+        <v>Neutralachsen-Einfärbung</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>No CLUT grid</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B89" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading…</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B90" t="str">
-        <v>Wird geladen…</v>
+        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B91" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B92" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>% ink</v>
       </c>
       <c r="B93" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>% Farbe</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Perceptual</v>
       </c>
       <c r="B94" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>Perzeptiv</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B95" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Relativ farbmetrisch</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Saturation</v>
       </c>
       <c r="B96" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Sättigung</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B97" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Absolut farbmetrisch</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Security</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B98" t="str">
-        <v>Sicherheit</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Conformance</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B99" t="str">
-        <v>Konformität</v>
+        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Quality</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B100" t="str">
-        <v>Qualität</v>
+        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>REPORT</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B101" t="str">
-        <v>BERICHT</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>FAIL</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B102" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Gamut-Volumen (ΔE³)</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>checks</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B103" t="str">
-        <v>Prüfungen</v>
+        <v>Roundtrip-ΔE</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B104" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>mean</v>
       </c>
       <c r="B105" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Mittel</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool</v>
+        <v>P90</v>
       </c>
       <c r="B106" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Powered by {lib}</v>
+        <v>max</v>
       </c>
       <c r="B107" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Max.</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Subscribe</v>
+        <v>Analysing…</v>
       </c>
       <c r="B108" t="str">
-        <v>Abonnieren</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Analysis</v>
       </c>
       <c r="B109" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new releases</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B110" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Close</v>
+        <v>Plot</v>
       </c>
       <c r="B111" t="str">
-        <v>Schließen</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Raw Output</v>
       </c>
       <c r="B112" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Email address</v>
+        <v>XML</v>
       </c>
       <c r="B113" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>you@example.com</v>
+        <v>JSON</v>
       </c>
       <c r="B114" t="str">
-        <v>sie@example.com</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Curves</v>
       </c>
       <c r="B115" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>(optional)</v>
+        <v>Input curves</v>
       </c>
       <c r="B116" t="str">
-        <v>(optional)</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Output curves</v>
       </c>
       <c r="B117" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B118" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Cancel</v>
+        <v>Gamut image</v>
       </c>
       <c r="B119" t="str">
-        <v>Abbrechen</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Subscribe</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B120" t="str">
-        <v>Abonnieren</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B121" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B122" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Close</v>
+        <v>Curve table</v>
       </c>
       <c r="B123" t="str">
-        <v>Schließen</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Privacy notice</v>
+        <v>Tables</v>
       </c>
       <c r="B124" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Data</v>
       </c>
       <c r="B125" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B126" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Loading…</v>
       </c>
       <c r="B127" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Input</v>
       </c>
       <c r="B128" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Output</v>
       </c>
       <c r="B129" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Error:</v>
+        <v>Floating point</v>
       </c>
       <c r="B130" t="str">
-        <v>Fehler:</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to XML</v>
+        <v>Grid point</v>
       </c>
       <c r="B131" t="str">
-        <v>In XML konvertieren</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to JSON</v>
+        <v>Normalized</v>
       </c>
       <c r="B132" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to ICC</v>
+        <v>Human</v>
       </c>
       <c r="B133" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to XML…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B134" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to JSON…</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B135" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to ICC…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B136" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Load ICC profile</v>
+        <v>Loading…</v>
       </c>
       <c r="B137" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B138" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Profile ID</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B139" t="str">
-        <v>Profil-ID</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>No tags found.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B140" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Tag Name</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B141" t="str">
-        <v>Tag-Name</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>ID</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B142" t="str">
-        <v>ID</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Offset</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B143" t="str">
-        <v>Offset</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Size</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B144" t="str">
-        <v>Größe</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Pad</v>
+        <v>Security</v>
       </c>
       <c r="B145" t="str">
-        <v>Auffüllung</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Bytes changed since load</v>
+        <v>Conformance</v>
       </c>
       <c r="B146" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Type</v>
+        <v>Quality</v>
       </c>
       <c r="B147" t="str">
-        <v>Typ</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Array of {type}</v>
+        <v>REPORT</v>
       </c>
       <c r="B148" t="str">
-        <v>Array von {type}</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>(No content)</v>
+        <v>FAIL</v>
       </c>
       <c r="B149" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>bytes</v>
+        <v>checks</v>
       </c>
       <c r="B150" t="str">
-        <v>Bytes</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Loading full description…</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B151" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Could not load full description:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B152" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B153" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B154" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>No validation output</v>
+        <v>Subscribe</v>
       </c>
       <c r="B155" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile is valid</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B156" t="str">
-        <v>Profil ist gültig</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B157" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Close</v>
       </c>
       <c r="B158" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Critical validation error</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B159" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Unknown validation status</v>
+        <v>Email address</v>
       </c>
       <c r="B160" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>you@example.com</v>
       </c>
       <c r="B161" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>No warnings or errors found.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B162" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Valid</v>
+        <v>(optional)</v>
       </c>
       <c r="B163" t="str">
-        <v>Gültig</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Warning</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B164" t="str">
-        <v>Warnung</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Error</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B165" t="str">
-        <v>Fehler</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Unknown</v>
+        <v>Cancel</v>
       </c>
       <c r="B166" t="str">
-        <v>Unbekannt</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Pass</v>
+        <v>Subscribe</v>
       </c>
       <c r="B167" t="str">
-        <v>Bestanden</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Fail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B168" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>View in context</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B169" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Validation detail</v>
+        <v>Close</v>
       </c>
       <c r="B170" t="str">
-        <v>Validierungsdetail</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Triggered by</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B171" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Field</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B172" t="str">
-        <v>Feld</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Current value</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B173" t="str">
-        <v>Aktueller Wert</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Required: 0</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B174" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B175" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Invalid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B176" t="str">
-        <v>Ungültig</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error:</v>
       </c>
       <c r="B177" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Close</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B178" t="str">
-        <v>Schließen</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading XML editor…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B179" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B180" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B181" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B182" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B183" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B184" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B185" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B186" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>indent</v>
+        <v>No tags found.</v>
       </c>
       <c r="B187" t="str">
-        <v>Einrückung</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>sort keys</v>
+        <v>Tag Name</v>
       </c>
       <c r="B188" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Größe</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Auffüllung</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Bytes seit dem Laden geändert</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Typ</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Array von {type}</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B196" t="str">
+        <v>(Kein Inhalt)</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Bytes</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Lade vollständige Beschreibung…</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Keine Validierungsausgabe</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Profil ist gültig</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Profil hat Warnung(en)</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Profil ist nicht konform</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Kritischer Validierungsfehler</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Unbekannter Validierungsstatus</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Keine Warnungen oder Fehler gefunden.</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Gültig</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Warnung</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Fehler</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Unbekannt</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Bestanden</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Fehlgeschlagen</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Im Kontext anzeigen</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Validierungsdetail</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Ausgelöst durch</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Feld</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Aktueller Wert</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Erforderlich: 0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Erwartet: {value}</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B230" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B231" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B189" t="str">
+      <c r="B236" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B236"/>
+  <dimension ref="A1:B319"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,1695 +605,2365 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Settings</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B26" t="str">
-        <v>Einstellungen</v>
+        <v>Profilweite Kennzahlen für einen Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und eine Kennzahl für die Rundlauf-Genauigkeit. Wählen Sie den Render-Intent und den Rundlauf-Typ — Tabelle und Histogramm passen sich an.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Display</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B27" t="str">
-        <v>Anzeige</v>
+        <v>Rundlauf-Typ</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Background</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>Hintergrund</v>
+        <v>Hat auf diesen Rundlauf-Typ keine Auswirkung</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Language</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B29" t="str">
-        <v>Sprache</v>
+        <v>Dieser Rundlauf-Typ ist für dieses Profil nicht verfügbar.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>System</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B30" t="str">
-        <v>System</v>
+        <v>Verteilung des Rundlauf-ΔE</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Light</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B31" t="str">
-        <v>Hell</v>
+        <v>Keine Rundlauf-Abtastwerte lagen innerhalb des ausgewerteten Bereichs.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dark</v>
+        <v>Std Dev</v>
       </c>
       <c r="B32" t="str">
-        <v>Dunkel</v>
+        <v>Std.-Abw.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>System default</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B33" t="str">
-        <v>Systemstandard</v>
+        <v>Relative Häufigkeit</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Number format</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>Zahlenformat</v>
+        <v>Kumulative Häufigkeit</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Hexadecimal</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B35" t="str">
-        <v>Hexadezimal</v>
+        <v>Horizontale Skala</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Decimal</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B36" t="str">
-        <v>Dezimal</v>
+        <v>Ganzzahliges ΔE</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Help</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B37" t="str">
-        <v>Hilfe</v>
+        <v>Auto-Skalierung</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Contact</v>
+        <v>Bins</v>
       </c>
       <c r="B38" t="str">
-        <v>Kontakt</v>
+        <v>Klassen</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>User guide</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B39" t="str">
-        <v>Benutzerhandbuch</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Search guide</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B40" t="str">
-        <v>Handbuch durchsuchen</v>
+        <v>Die Farbtabelle (CLUT) eines Gerät↔PCS-Transforms, als Kacheln zu einem Bild angeordnet. Wählen Sie die anzuzeigende Render-Intent-Tabelle.</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Search the user guide</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B41" t="str">
-        <v>Benutzerhandbuch durchsuchen</v>
+        <v>Dieses Profil hat keine CLUT-basierten Gerät↔PCS-Tabellen zur Visualisierung.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Previous match</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B42" t="str">
-        <v>Vorheriger Treffer</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Next match</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B43" t="str">
-        <v>Nächster Treffer</v>
+        <v>Die In-/Außerhalb-Gamut-Karte des Gamut-Tags: neutral, wo eine PCS-Farbe reproduzierbar ist, rot, wo sie außerhalb des Gerätegamuts liegt.</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Close user guide</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B44" t="str">
-        <v>Handbuch schließen</v>
+        <v>Dieses Profil hat kein Gamut-Tag zur Visualisierung.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Loading…</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B45" t="str">
-        <v>Wird geladen…</v>
+        <v>Vertikale Skala</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Could not load the user guide.</v>
+        <v>X–Y</v>
       </c>
       <c r="B46" t="str">
-        <v>Benutzerhandbuch konnte nicht geladen werden.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>None</v>
+        <v>Tone increase</v>
       </c>
       <c r="B47" t="str">
-        <v>Keine</v>
+        <v>Tonwertzunahme</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B48" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Tonwertzunahme (Ausgang − Eingang)</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Show full dump</v>
       </c>
       <c r="B49" t="str">
-        <v>Laden Sie ein ICC-Profil hoch, um es gegen die Spezifikation</v>
+        <v>Vollständige Ausgabe anzeigen</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>specification using the</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B50" t="str">
-        <v>mit der Demo-Implementierung</v>
+        <v>Ausgabe aus Leistungsgründen gekürzt.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>demo implementation.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B51" t="str">
-        <v>zu validieren.</v>
+        <v>In-Gamut-Übersicht (RT0)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Based on</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B52" t="str">
-        <v>Basierend auf der</v>
+        <v>Inversion + Gamut (RT1)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>demo implementation</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B53" t="str">
-        <v>Demo-Implementierung</v>
+        <v>Reproduzierbarkeit (RT2)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Validating…</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B54" t="str">
-        <v>Validierung…</v>
+        <v>PRMG-Interoperabilität</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Save ICC profile</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B55" t="str">
-        <v>ICC-Profil speichern</v>
+        <v>iccviz-Übersicht: Ein Gitter aus Gerätewerten wird nach PCS, zurück zum Gerät und erneut nach PCS überführt; ΔE*ab wird zwischen den beiden PCS-Durchläufen gemessen. Eine schnelle In-Gamut-Stabilitätsprüfung.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B56" t="str">
-        <v>● Geändert — nicht gespeichert</v>
+        <v>iccRoundTrip Rundlauf 1: ΔE*ab zwischen dem PCS jeder Gerätefarbe und ihrem PCS nach einem Rundlauf Lab → Gerät → Lab. Spiegelt Inversionsgenauigkeit und Gamut-Mapping wider.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profiles</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>iccRoundTrip Rundlauf 2: ΔE*ab zwischen dem ersten und zweiten Rundlauf — wie stabil ein wiederholter PCS-Rundlauf ist (Reproduzierbarkeit, unabhängig vom Gamut-Clipping des ersten Durchlaufs).</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Show profile pool</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>iccRoundTrip PRMG: PCS-Farben innerhalb des Perceptual Reference Medium Gamut durchlaufen einen einzelnen Rundlauf (Lab → Gerät → Lab); die ΔE*ab-Verteilung zeigt die profilübergreifende Interoperabilität.</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Collapse</v>
+        <v>Settings</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Einstellungen</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Load Profiles</v>
+        <v>Display</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Anzeige</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Remove</v>
+        <v>Background</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Hintergrund</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Language</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Sprache</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>or use “Load Profiles” — files stay on your device.</v>
+        <v>System</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>System</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile</v>
+        <v>Light</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Hell</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Compare</v>
+        <v>Dark</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>Dunkel</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Link</v>
+        <v>System default</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Systemstandard</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Number format</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Zahlenformat</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Remove</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Hexadezimal</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>No profile selected</v>
+        <v>Decimal</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Dezimal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Help</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>Hilfe</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Contact</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>Kontakt</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>User guide</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>Benutzerhandbuch</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut comparison</v>
+        <v>Search guide</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>Handbuch durchsuchen</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>Benutzerhandbuch durchsuchen</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Linking</v>
+        <v>Previous match</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>Vorheriger Treffer</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Next match</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>Nächster Treffer</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Close user guide</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>Handbuch schließen</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Loading…</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>OK</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>Benutzerhandbuch konnte nicht geladen werden.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>None</v>
       </c>
       <c r="B80" t="str">
-        <v>ICC-Profil hierher ziehen</v>
+        <v>Keine</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>or</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B81" t="str">
-        <v>oder</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Choose file</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B82" t="str">
-        <v>Datei wählen</v>
+        <v>Laden Sie ein ICC-Profil hoch, um es gegen die Spezifikation</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>.icc and .icm files</v>
+        <v>specification using the</v>
       </c>
       <c r="B83" t="str">
-        <v>.icc- und .icm-Dateien</v>
+        <v>mit der Demo-Implementierung</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Header</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B84" t="str">
-        <v>Header</v>
+        <v>zu validieren.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tags</v>
+        <v>Based on</v>
       </c>
       <c r="B85" t="str">
-        <v>Tags</v>
+        <v>Basierend auf der</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Validation</v>
+        <v>demo implementation</v>
       </c>
       <c r="B86" t="str">
-        <v>Validierung</v>
+        <v>Demo-Implementierung</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Analysis</v>
+        <v>Validating…</v>
       </c>
       <c r="B87" t="str">
-        <v>Analyse</v>
+        <v>Validierung…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B88" t="str">
-        <v>Neutralachsen-Einfärbung</v>
+        <v>ICC-Profil speichern</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B89" t="str">
-        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
+        <v>● Geändert — nicht gespeichert</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Profile</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B91" t="str">
-        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
+        <v>Profil-Pool anzeigen</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Rendering intent</v>
+        <v>Collapse</v>
       </c>
       <c r="B92" t="str">
-        <v>Render-Intent</v>
+        <v>Einklappen</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>% ink</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B93" t="str">
-        <v>% Farbe</v>
+        <v>Profile laden</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Perceptual</v>
+        <v>Remove</v>
       </c>
       <c r="B94" t="str">
-        <v>Perzeptiv</v>
+        <v>Entfernen</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B95" t="str">
-        <v>Relativ farbmetrisch</v>
+        <v>ICC-Profile hierher ziehen</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Saturation</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B96" t="str">
-        <v>Sättigung</v>
+        <v>oder ein Bild (TIFF/PNG/JPEG), um dessen eingebettetes Profil zu extrahieren — die Dateien bleiben auf Ihrem Gerät.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>New from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>Absolut farbmetrisch</v>
+        <v>Neu aus .cube</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Statistics</v>
+        <v>Sort by name</v>
       </c>
       <c r="B98" t="str">
-        <v>Profilstatistik</v>
+        <v>Nach Namen sortieren</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>A–Z</v>
       </c>
       <c r="B99" t="str">
-        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B100" t="str">
-        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
+        <v>Neues Profil aus .cube</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Rendering intent</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B101" t="str">
-        <v>Render-Intent</v>
+        <v>Erstellen Sie einen ICC-DeviceLink aus einer Adobe/Resolve-.cube-3D-LUT. Das Ergebnis wird Ihrem Pool hinzugefügt und heruntergeladen.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B102" t="str">
-        <v>Gamut-Volumen (ΔE³)</v>
+        <v>.cube-Datei wählen</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Round-trip ΔE</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B103" t="str">
-        <v>Roundtrip-ΔE</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
+        <v>oder hierher ziehen oder unten einfügen</v>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
+      </c>
+      <c r="B104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>mean</v>
+        <v>Cancel</v>
       </c>
       <c r="B105" t="str">
-        <v>Mittel</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>P90</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B106" t="str">
-        <v>P90</v>
+        <v>DeviceLink erstellen</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>max</v>
+        <v>Creating…</v>
       </c>
       <c r="B107" t="str">
-        <v>Max.</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Analysing…</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B108" t="str">
-        <v>Analyse läuft…</v>
+        <v>Diese Datei konnte nicht gelesen werden.</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Analysis</v>
+        <v>Profile</v>
       </c>
       <c r="B109" t="str">
-        <v>Analyse</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Compare</v>
       </c>
       <c r="B110" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v>Vergleichen</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Plot</v>
+        <v>Link</v>
       </c>
       <c r="B111" t="str">
-        <v>Diagramm</v>
+        <v>Verknüpfen</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Raw Output</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B112" t="str">
-        <v>Rohausgabe</v>
+        <v>Ziehen Sie Profile aus dem Pool auf diesen Tab</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>XML</v>
+        <v>Remove</v>
       </c>
       <c r="B113" t="str">
-        <v>XML</v>
+        <v>Entfernen</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>JSON</v>
+        <v>No profile selected</v>
       </c>
       <c r="B114" t="str">
-        <v>JSON</v>
+        <v>Kein Profil ausgewählt</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B115" t="str">
-        <v>Kurven</v>
+        <v>Ziehen Sie ein Profil aus dem Pool auf den Profil-Tab, um es zu untersuchen.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Input curves</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B116" t="str">
-        <v>Eingangskurven</v>
+        <v>Noch nichts zu vergleichen</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Output curves</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B117" t="str">
-        <v>Ausgangskurven</v>
+        <v>Ziehen Sie ein oder mehrere Profile auf den Vergleichen-Tab.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>CLUT image</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B118" t="str">
-        <v>CLUT-Bild</v>
+        <v>Gamut-Vergleich</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut image</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B119" t="str">
-        <v>Gamut-Bild</v>
+        <v>3D-Gamut- und 2D-Schnittansichten kommen hierher. Gesammelt:</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Chromaticity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B120" t="str">
-        <v>Chromazität</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Scatter plot</v>
+        <v>Shell</v>
       </c>
       <c r="B121" t="str">
-        <v>Streudiagramm</v>
+        <v>Hülle</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tone response curve</v>
+        <v>Wireframe</v>
       </c>
       <c r="B122" t="str">
-        <v>Tonwertkurve</v>
+        <v>Drahtgitter</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Curve table</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>Kurventabelle</v>
+        <v>Deckkraft</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tables</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>Tabellen</v>
+        <v>Farbe</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Data</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>Daten</v>
+        <v>Einfarbig</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Evaluate</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>Auswerten</v>
+        <v>Nach Wert</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Loading…</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>Wird geladen…</v>
+        <v>Nach Farbton</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Input</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>Eingang</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Output</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>Ausgang</v>
+        <v>Drehteller</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Floating point</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>Gleitkomma</v>
+        <v>Orbit</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Grid point</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>Gitterpunkt</v>
+        <v>Ziehgeschwindigkeit</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Normalized</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>Normalisiert</v>
+        <v>Rollen</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Human</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Lesbar</v>
+        <v>Rollgeschwindigkeit</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Device → PCS</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>Gerät → PCS</v>
+        <v>Gamut wird erstellt…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>PCS → Device</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>PCS → Gerät</v>
+        <v>kein Gamut</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>No CLUT grid</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>Ein-/ausblenden</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Loading…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>Wird geladen…</v>
+        <v>3D-Gamut-Hülle</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>2D-Gamut-Schnitt</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Ebene</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Keines der ausgewählten Profile hat ein Gerät→PCS-Transform, aus dem sich ein Gamut ableiten lässt.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Verknüpfung</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Security</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>Sicherheit</v>
+        <v>DeviceLink-Erzeugung und Transformationen über mehrere Profile folgen in einer späteren Phase.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Conformance</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>Konformität</v>
+        <v>Weitere Link-Ersteller (DeviceLink, …) folgen hier.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Quality</v>
+        <v>V4 Display Maker</v>
       </c>
       <c r="B147" t="str">
-        <v>Qualität</v>
+        <v>V4-Display-Ersteller</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>REPORT</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>BERICHT</v>
+        <v>Ziehen Sie ein V5-RGB-Display- und ein V5-Beobachterprofil hierher, um ein V4-Displayprofil zu erstellen.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FAIL</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>V5-RGB-Display</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>checks</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>Prüfungen</v>
+        <v>Displayprofil ablegen</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>V5-Beobachter (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Beobachterprofil ablegen</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Ein Profil, das weder ein V5-RGB-Display noch ein Beobachter ist, wurde ignoriert.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Powered by {lib}</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>V4-Displayprofil erstellen</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Subscribe</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>Abonnieren</v>
+        <v>Profilname</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Erstellen</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Get notified about new releases</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Close</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>Schließen</v>
+        <v>„{name}“ erstellt — dem Pool und diesem Tab hinzugefügt.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Cancel</v>
       </c>
       <c r="B159" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Email address</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B160" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>{n} Datei(en) nicht geladen</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>you@example.com</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B161" t="str">
-        <v>sie@example.com</v>
+        <v>Diese Dateien sind keine ICC-Profile und wurden daher nicht zum Pool hinzugefügt:</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>How will you use profiletool?</v>
+        <v>OK</v>
       </c>
       <c r="B162" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>(optional)</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B163" t="str">
-        <v>(optional)</v>
+        <v>ICC-Profil hierher ziehen</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>or</v>
       </c>
       <c r="B164" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>oder</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Choose file</v>
       </c>
       <c r="B165" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>Datei wählen</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cancel</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B166" t="str">
-        <v>Abbrechen</v>
+        <v>.icc- und .icm-Dateien</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Subscribe</v>
+        <v>Header</v>
       </c>
       <c r="B167" t="str">
-        <v>Abonnieren</v>
+        <v>Header</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Tags</v>
       </c>
       <c r="B168" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Validation</v>
       </c>
       <c r="B169" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Validierung</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>Analysis</v>
       </c>
       <c r="B170" t="str">
-        <v>Schließen</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Privacy notice</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B171" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Neutralachsen-Einfärbung</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B172" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B173" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Please check the form and try again.</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B174" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B175" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Network error. Please try again.</v>
+        <v>% ink</v>
       </c>
       <c r="B176" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>% Farbe</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Error:</v>
+        <v>Perceptual</v>
       </c>
       <c r="B177" t="str">
-        <v>Fehler:</v>
+        <v>Perzeptiv</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Convert to XML</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B178" t="str">
-        <v>In XML konvertieren</v>
+        <v>Relativ farbmetrisch</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Convert to JSON</v>
+        <v>Saturation</v>
       </c>
       <c r="B179" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Sättigung</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Convert to ICC</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B180" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Absolut farbmetrisch</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Converting to XML…</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B181" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Converting to JSON…</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B182" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Converting to ICC…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B183" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Load ICC profile</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B184" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B185" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Gamut-Volumen (ΔE³)</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Profile ID</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B186" t="str">
-        <v>Profil-ID</v>
+        <v>Roundtrip-ΔE</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>No tags found.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B187" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Tag Name</v>
+        <v>mean</v>
       </c>
       <c r="B188" t="str">
-        <v>Tag-Name</v>
+        <v>Mittel</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
       <c r="B189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Offset</v>
+        <v>max</v>
       </c>
       <c r="B190" t="str">
-        <v>Offset</v>
+        <v>Max.</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Size</v>
+        <v>Analysing…</v>
       </c>
       <c r="B191" t="str">
-        <v>Größe</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Pad</v>
+        <v>Analysis</v>
       </c>
       <c r="B192" t="str">
-        <v>Auffüllung</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B193" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Type</v>
+        <v>Plot</v>
       </c>
       <c r="B194" t="str">
-        <v>Typ</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Array of {type}</v>
+        <v>Raw Output</v>
       </c>
       <c r="B195" t="str">
-        <v>Array von {type}</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>(No content)</v>
+        <v>XML</v>
       </c>
       <c r="B196" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>bytes</v>
+        <v>JSON</v>
       </c>
       <c r="B197" t="str">
-        <v>Bytes</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Loading full description…</v>
+        <v>Curves</v>
       </c>
       <c r="B198" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not load full description:</v>
+        <v>Input curves</v>
       </c>
       <c r="B199" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Output curves</v>
       </c>
       <c r="B200" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B201" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>No validation output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B202" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Profile is valid</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B203" t="str">
-        <v>Profil ist gültig</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B204" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B205" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Critical validation error</v>
+        <v>Curve table</v>
       </c>
       <c r="B206" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Unknown validation status</v>
+        <v>Tables</v>
       </c>
       <c r="B207" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Data</v>
       </c>
       <c r="B208" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B209" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Valid</v>
+        <v>Loading…</v>
       </c>
       <c r="B210" t="str">
-        <v>Gültig</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Warning</v>
+        <v>Input</v>
       </c>
       <c r="B211" t="str">
-        <v>Warnung</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Error</v>
+        <v>Output</v>
       </c>
       <c r="B212" t="str">
-        <v>Fehler</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Unknown</v>
+        <v>Floating point</v>
       </c>
       <c r="B213" t="str">
-        <v>Unbekannt</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Pass</v>
+        <v>Grid point</v>
       </c>
       <c r="B214" t="str">
-        <v>Bestanden</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Fail</v>
+        <v>Normalized</v>
       </c>
       <c r="B215" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>View in context</v>
+        <v>Human</v>
       </c>
       <c r="B216" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Validation detail</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B217" t="str">
-        <v>Validierungsdetail</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Triggered by</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B218" t="str">
-        <v>Ausgelöst durch</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Field</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B219" t="str">
-        <v>Feld</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Current value</v>
+        <v>Loading…</v>
       </c>
       <c r="B220" t="str">
-        <v>Aktueller Wert</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Required: 0</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B221" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B222" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invalid</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B223" t="str">
-        <v>Ungültig</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B224" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Close</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B225" t="str">
-        <v>Schließen</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Loading XML editor…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B226" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B227" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Security</v>
       </c>
       <c r="B228" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Conformance</v>
       </c>
       <c r="B229" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Quality</v>
       </c>
       <c r="B230" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>REPORT</v>
       </c>
       <c r="B231" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>FAIL</v>
       </c>
       <c r="B232" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>checks</v>
       </c>
       <c r="B233" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>indent</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B234" t="str">
-        <v>Einrückung</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>sort keys</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B235" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B236" t="str">
+        <v>ICC-Profil-Tool</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Betrieben mit {lib}</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Abonnieren</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Bei neuen Releases benachrichtigt werden</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B243" t="str">
+        <v>E-Mail-Adresse</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B244" t="str">
+        <v>sie@example.com</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Wofür werden Sie profiletool nutzen?</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B246" t="str">
+        <v>(optional)</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B247" t="str">
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Abbrechen</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Abonnieren</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Danke — wir melden uns.</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Datenschutzhinweis</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Fehler:</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B261" t="str">
+        <v>In XML konvertieren</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B262" t="str">
+        <v>In JSON konvertieren</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B263" t="str">
+        <v>In ICC konvertieren</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Konvertiere in XML…</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Konvertiere in JSON…</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Konvertiere in ICC…</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B267" t="str">
+        <v>ICC-Profil laden</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Profil-ID</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Keine Tags gefunden.</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Tag-Name</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B272" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Größe</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Auffüllung</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Bytes seit dem Laden geändert</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Typ</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Array von {type}</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B279" t="str">
+        <v>(Kein Inhalt)</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Bytes</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Lade vollständige Beschreibung…</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Keine Validierungsausgabe</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Profil ist gültig</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Profil hat Warnung(en)</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Profil ist nicht konform</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Kritischer Validierungsfehler</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Unbekannter Validierungsstatus</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Keine Warnungen oder Fehler gefunden.</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Gültig</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Warnung</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Fehler</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Unbekannt</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Bestanden</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Fehlgeschlagen</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Im Kontext anzeigen</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Validierungsdetail</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Ausgelöst durch</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Feld</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Aktueller Wert</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Erforderlich: 0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B305" t="str">
+        <v>Erwartet: {value}</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B310" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B313" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B314" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B317" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B318" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B236" t="str">
+      <c r="B319" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B413"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Link</v>
+        <v>Combine</v>
       </c>
       <c r="B111" t="str">
         <v>Verknüpfen</v>
@@ -1299,1671 +1299,2423 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B112" t="str">
-        <v>Ziehen Sie Profile aus dem Pool auf diesen Tab</v>
+        <v>Spektral</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B113" t="str">
-        <v>Entfernen</v>
+        <v>Ziehen Sie Profile aus dem Pool auf diesen Tab</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B114" t="str">
-        <v>Kein Profil ausgewählt</v>
+        <v>Entfernen</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B115" t="str">
-        <v>Ziehen Sie ein Profil aus dem Pool auf den Profil-Tab, um es zu untersuchen.</v>
+        <v>Kein Profil ausgewählt</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B116" t="str">
-        <v>Noch nichts zu vergleichen</v>
+        <v>Ziehen Sie ein Profil aus dem Pool auf den Profil-Tab, um es zu untersuchen.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B117" t="str">
-        <v>Ziehen Sie ein oder mehrere Profile auf den Vergleichen-Tab.</v>
+        <v>Noch nichts zu vergleichen</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B118" t="str">
-        <v>Gamut-Vergleich</v>
+        <v>Ziehen Sie ein oder mehrere Profile auf den Vergleichen-Tab.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B119" t="str">
-        <v>3D-Gamut- und 2D-Schnittansichten kommen hierher. Gesammelt:</v>
+        <v>Gamut-Vergleich</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B120" t="str">
-        <v>Render-Intent</v>
+        <v>3D-Gamut- und 2D-Schnittansichten kommen hierher. Gesammelt:</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B121" t="str">
-        <v>Hülle</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B122" t="str">
-        <v>Drahtgitter</v>
+        <v>Hülle</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Wireframe</v>
       </c>
       <c r="B123" t="str">
-        <v>Deckkraft</v>
+        <v>Drahtgitter</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B124" t="str">
-        <v>Farbe</v>
+        <v>Achsenwerte</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Opacity</v>
       </c>
       <c r="B125" t="str">
-        <v>Einfarbig</v>
+        <v>Deckkraft</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Colour</v>
       </c>
       <c r="B126" t="str">
-        <v>Nach Wert</v>
+        <v>Farbe</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Solid</v>
       </c>
       <c r="B127" t="str">
-        <v>Nach Farbton</v>
+        <v>Einfarbig</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>By value</v>
       </c>
       <c r="B128" t="str">
-        <v>Rotation</v>
+        <v>Nach Wert</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>By hue</v>
       </c>
       <c r="B129" t="str">
-        <v>Drehteller</v>
+        <v>Nach Farbton</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>Rotation</v>
       </c>
       <c r="B130" t="str">
-        <v>Orbit</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B131" t="str">
-        <v>Ziehgeschwindigkeit</v>
+        <v>Drehteller</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Orbit</v>
       </c>
       <c r="B132" t="str">
-        <v>Rollen</v>
+        <v>Orbit</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Drag speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Rollgeschwindigkeit</v>
+        <v>Ziehgeschwindigkeit</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Roll</v>
       </c>
       <c r="B134" t="str">
-        <v>Gamut wird erstellt…</v>
+        <v>Rollen</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Roll speed</v>
       </c>
       <c r="B135" t="str">
-        <v>kein Gamut</v>
+        <v>Rollgeschwindigkeit</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B136" t="str">
-        <v>Ein-/ausblenden</v>
+        <v>Gamut wird erstellt…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>no gamut</v>
       </c>
       <c r="B137" t="str">
-        <v>3D-Gamut-Hülle</v>
+        <v>kein Gamut</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Show / hide</v>
       </c>
       <c r="B138" t="str">
-        <v>2D-Gamut-Schnitt</v>
+        <v>Ein-/ausblenden</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B139" t="str">
-        <v>Ebene</v>
+        <v>3D-Gamut-Hülle</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>2D-Gamut-Schnitt</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>Plane</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>Ebene</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>a*</v>
       </c>
       <c r="B143" t="str">
-        <v>Keines der ausgewählten Profile hat ein Gerät→PCS-Transform, aus dem sich ein Gamut ableiten lässt.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>b*</v>
       </c>
       <c r="B144" t="str">
-        <v>Verknüpfung</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B145" t="str">
-        <v>DeviceLink-Erzeugung und Transformationen über mehrere Profile folgen in einer späteren Phase.</v>
+        <v>Keines der ausgewählten Profile hat ein Gerät→PCS-Transform, aus dem sich ein Gamut ableiten lässt.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>Linking</v>
       </c>
       <c r="B146" t="str">
-        <v>Weitere Link-Ersteller (DeviceLink, …) folgen hier.</v>
+        <v>Verknüpfung</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>V4 Display Maker</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B147" t="str">
-        <v>V4-Display-Ersteller</v>
+        <v>DeviceLink-Erzeugung und Transformationen über mehrere Profile folgen in einer späteren Phase.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B148" t="str">
-        <v>Ziehen Sie ein V5-RGB-Display- und ein V5-Beobachterprofil hierher, um ein V4-Displayprofil zu erstellen.</v>
+        <v>Weitere Link-Ersteller (DeviceLink, …) folgen hier.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>Observer Change</v>
       </c>
       <c r="B149" t="str">
-        <v>V5-RGB-Display</v>
+        <v>V4-Display-Ersteller</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B150" t="str">
-        <v>Displayprofil ablegen</v>
+        <v>Ziehen Sie ein V5-RGB-Display- und ein V5-Beobachterprofil hierher, um ein V4-Displayprofil zu erstellen.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B151" t="str">
-        <v>V5-Beobachter (PCC)</v>
+        <v>V5-RGB-Display</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B152" t="str">
-        <v>Beobachterprofil ablegen</v>
+        <v>Displayprofil ablegen</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B153" t="str">
-        <v>Ein Profil, das weder ein V5-RGB-Display noch ein Beobachter ist, wurde ignoriert.</v>
+        <v>V5-Beobachter (PCC)</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B154" t="str">
-        <v>V4-Displayprofil erstellen</v>
+        <v>Beobachterprofil ablegen</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B155" t="str">
-        <v>Profilname</v>
+        <v>Ein Profil, das weder ein V5-RGB-Display noch ein Beobachter ist, wurde ignoriert.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B156" t="str">
-        <v>Erstellen</v>
+        <v>V4-Displayprofil erstellen</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Profile name</v>
       </c>
       <c r="B157" t="str">
-        <v>Wird erstellt…</v>
+        <v>Profilname</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Create</v>
       </c>
       <c r="B158" t="str">
-        <v>„{name}“ erstellt — dem Pool und diesem Tab hinzugefügt.</v>
+        <v>Erstellen</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Cancel</v>
+        <v>Making…</v>
       </c>
       <c r="B159" t="str">
-        <v>Abbrechen</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B160" t="str">
-        <v>{n} Datei(en) nicht geladen</v>
+        <v>„{name}“ erstellt — dem Pool und diesem Tab hinzugefügt.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B161" t="str">
-        <v>Diese Dateien sind keine ICC-Profile und wurden daher nicht zum Pool hinzugefügt:</v>
+        <v>Link-Pipeline</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>OK</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B162" t="str">
-        <v>OK</v>
+        <v>Erstellen Sie eine Kette aus Profilen und erzeugen Sie daraus einen DeviceLink, transformieren Sie ein Bild oder einen Farbdatensatz.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Done</v>
       </c>
       <c r="B163" t="str">
-        <v>ICC-Profil hierher ziehen</v>
+        <v>Fertig</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>or</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B164" t="str">
-        <v>oder</v>
+        <v>Bild zum Transformieren ablegen (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Choose file</v>
+        <v>Checking image…</v>
       </c>
       <c r="B165" t="str">
-        <v>Datei wählen</v>
+        <v>Bild wird geprüft…</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>.icc and .icm files</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B166" t="str">
-        <v>.icc- und .icm-Dateien</v>
+        <v>Kein unterstütztes Bildformat (TIFF, PNG oder JPEG).</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Header</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B167" t="str">
-        <v>Header</v>
+        <v>Bild zu groß ({mp} MP; Grenzwert {max} MP).</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Tags</v>
+        <v>Transform Image</v>
       </c>
       <c r="B168" t="str">
-        <v>Tags</v>
+        <v>Bild transformieren</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation</v>
+        <v>Transforming…</v>
       </c>
       <c r="B169" t="str">
-        <v>Validierung</v>
+        <v>Wird transformiert…</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Analysis</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B170" t="str">
-        <v>Analyse</v>
+        <v>Profile ablegen, um die Kette zu starten</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>removed</v>
       </c>
       <c r="B171" t="str">
-        <v>Neutralachsen-Einfärbung</v>
+        <v>entfernt</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Move earlier</v>
       </c>
       <c r="B172" t="str">
-        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
+        <v>Nach vorne verschieben</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Move later</v>
       </c>
       <c r="B173" t="str">
-        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Nach hinten verschieben</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Move up</v>
       </c>
       <c r="B174" t="str">
-        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
+        <v>Nach oben verschieben</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent</v>
+        <v>Move down</v>
       </c>
       <c r="B175" t="str">
-        <v>Render-Intent</v>
+        <v>Nach unten verschieben</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>% ink</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B176" t="str">
-        <v>% Farbe</v>
+        <v>Rendering-Priorität (alle)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Perceptual</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B177" t="str">
-        <v>Perzeptiv</v>
+        <v>Rendering-Priorität für diese Transformation</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B178" t="str">
-        <v>Relativ farbmetrisch</v>
+        <v>Die Transformationen verwenden unterschiedliche Rendering-Prioritäten</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Saturation</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B179" t="str">
-        <v>Sättigung</v>
+        <v>Kettenrichtung umkehren (kehrt die erste Transformation um und wirkt sich auf die gesamte Kette aus)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B180" t="str">
-        <v>Absolut farbmetrisch</v>
+        <v>Ein verkettetes Profil wurde aus dem Pool entfernt — entfernen Sie es, um fortzufahren.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Profile Statistics</v>
+        <v>Chain</v>
       </c>
       <c r="B181" t="str">
-        <v>Profilstatistik</v>
+        <v>Kette</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B182" t="str">
-        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
+        <v>Die Kette konnte nicht analysiert werden.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B183" t="str">
-        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
+        <v>Kette wird geprüft…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Rendering intent</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B184" t="str">
-        <v>Render-Intent</v>
+        <v>Die Kette verbindet sich nicht ({detail}).</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B185" t="str">
-        <v>Gamut-Volumen (ΔE³)</v>
+        <v>Profil {n} verbindet sich nicht mit der vorherigen Stufe ({detail}).</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B186" t="str">
-        <v>Roundtrip-ΔE</v>
+        <v>Beheben Sie die Kette, bevor Sie Bilder verarbeiten</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Clear</v>
       </c>
       <c r="B187" t="str">
-        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
+        <v>Leeren</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>mean</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B188" t="str">
-        <v>Mittel</v>
+        <v>DeviceLink erstellen</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>P90</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B189" t="str">
-        <v>P90</v>
+        <v>DeviceLink-Name</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>max</v>
+        <v>Making…</v>
       </c>
       <c r="B190" t="str">
-        <v>Max.</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Analysing…</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B191" t="str">
-        <v>Analyse läuft…</v>
+        <v>„{name}“ erstellt — zum Pool und zu diesem Tab hinzugefügt.</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Analysis</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B192" t="str">
-        <v>Analyse</v>
+        <v>{src}-Bilder ablegen, um sie in {dst} zu konvertieren — Ergebnisse werden heruntergeladen, nichts wird gespeichert.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B193" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v>Erstellen Sie eine Kette, um Bilder zu verarbeiten</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Plot</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B194" t="str">
-        <v>Diagramm</v>
+        <v>Diese Kette beginnt und endet nicht in einem Bildfarbraum</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Raw Output</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B195" t="str">
-        <v>Rohausgabe</v>
+        <v>Transformiertes Bild gespeichert.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>XML</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B196" t="str">
-        <v>XML</v>
+        <v>Farbdatensatz ablegen (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>JSON</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B197" t="str">
-        <v>JSON</v>
+        <v>Diese Datei konnte nicht gelesen werden.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Curves</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B198" t="str">
-        <v>Kurven</v>
+        <v>Datendatei zu groß.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Input curves</v>
+        <v>Transform Data</v>
       </c>
       <c r="B199" t="str">
-        <v>Eingangskurven</v>
+        <v>Daten transformieren</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Output curves</v>
+        <v>Transforming…</v>
       </c>
       <c r="B200" t="str">
-        <v>Ausgangskurven</v>
+        <v>Wird transformiert…</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>CLUT image</v>
+        <v>Prefer</v>
       </c>
       <c r="B201" t="str">
-        <v>CLUT-Bild</v>
+        <v>Bevorzugen</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Gamut image</v>
+        <v>Observer</v>
       </c>
       <c r="B202" t="str">
-        <v>Gamut-Bild</v>
+        <v>Beobachter</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Chromaticity</v>
+        <v>Illuminant</v>
       </c>
       <c r="B203" t="str">
-        <v>Chromazität</v>
+        <v>Lichtart</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Scatter plot</v>
+        <v>Condition</v>
       </c>
       <c r="B204" t="str">
-        <v>Streudiagramm</v>
+        <v>Bedingung</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Tone response curve</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B205" t="str">
-        <v>Tonwertkurve</v>
+        <v>{n} Duplikat(e) filtern</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Curve table</v>
+        <v>median</v>
       </c>
       <c r="B206" t="str">
-        <v>Kurventabelle</v>
+        <v>Median</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Tables</v>
+        <v>mean</v>
       </c>
       <c r="B207" t="str">
-        <v>Tabellen</v>
+        <v>Mittelwert</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Data</v>
+        <v>patches</v>
       </c>
       <c r="B208" t="str">
-        <v>Daten</v>
+        <v>Farbfelder</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Evaluate</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B209" t="str">
-        <v>Auswerten</v>
+        <v>{n} Duplikate</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Loading…</v>
+        <v>Transform result</v>
       </c>
       <c r="B210" t="str">
-        <v>Wird geladen…</v>
+        <v>Transformationsergebnis</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Input</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B211" t="str">
-        <v>Eingang</v>
+        <v>{src} → {dst} · {n} Farbfelder</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Output</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B212" t="str">
-        <v>Ausgang</v>
+        <v>Zeigt die ersten {shown} von {total} — Speichern schreibt alle.</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Floating point</v>
+        <v>Save as</v>
       </c>
       <c r="B213" t="str">
-        <v>Gleitkomma</v>
+        <v>Speichern unter</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Grid point</v>
+        <v>Save</v>
       </c>
       <c r="B214" t="str">
-        <v>Gitterpunkt</v>
+        <v>Speichern</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Normalized</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B215" t="str">
-        <v>Normalisiert</v>
+        <v>Transformation umkehren</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Human</v>
+        <v>Inverting…</v>
       </c>
       <c r="B216" t="str">
-        <v>Lesbar</v>
+        <v>Wird umgekehrt…</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Device → PCS</v>
+        <v>Invert</v>
       </c>
       <c r="B217" t="str">
-        <v>Gerät → PCS</v>
+        <v>Umkehren</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PCS → Device</v>
+        <v>last stage</v>
       </c>
       <c r="B218" t="str">
-        <v>PCS → Gerät</v>
+        <v>letzte Stufe</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>No CLUT grid</v>
+        <v>first stage</v>
       </c>
       <c r="B219" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>erste Stufe</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Loading…</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B220" t="str">
-        <v>Wird geladen…</v>
+        <v>Daten in {in} → Suche {out}</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B221" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>Die Umkehrung benötigt eine Kette aus 2–3 Profilen</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Invalid profile URL:</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B222" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Der Datensatz muss in {in} vorliegen; die inverse Suche liefert {out} sowie einen Invertierbarkeits-Kostenwert pro Farbfeld.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B223" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>ΔE-Kosten</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B224" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>Dieses Bild enthält ein eingebettetes ICC-Profil.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B225" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Extrahieren &amp; zur Kette hinzufügen</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Extracting…</v>
       </c>
       <c r="B226" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Wird extrahiert…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Dismiss</v>
       </c>
       <c r="B227" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Verwerfen</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Security</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B228" t="str">
-        <v>Sicherheit</v>
+        <v>Eingebettetes Profil extrahiert — zum Pool hinzugefügt und an den Anfang der Kette gesetzt.</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Conformance</v>
+        <v>Image output options</v>
       </c>
       <c r="B229" t="str">
-        <v>Konformität</v>
+        <v>Bildausgabeoptionen</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Quality</v>
+        <v>Encoding</v>
       </c>
       <c r="B230" t="str">
-        <v>Qualität</v>
+        <v>Kodierung</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>REPORT</v>
+        <v>Same as source</v>
       </c>
       <c r="B231" t="str">
-        <v>BERICHT</v>
+        <v>Wie Quelle</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>FAIL</v>
+        <v>8-bit</v>
       </c>
       <c r="B232" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>8 Bit</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>checks</v>
+        <v>16-bit</v>
       </c>
       <c r="B233" t="str">
-        <v>Prüfungen</v>
+        <v>16 Bit</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B234" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Gleitkomma (32 Bit)</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Compression</v>
       </c>
       <c r="B235" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Komprimierung</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B236" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Keine</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Powered by {lib}</v>
+        <v>Planar</v>
       </c>
       <c r="B237" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Subscribe</v>
+        <v>Composite</v>
       </c>
       <c r="B238" t="str">
-        <v>Abonnieren</v>
+        <v>Verschachtelt</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Separated</v>
       </c>
       <c r="B239" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Getrennt</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Get notified about new releases</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B240" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>CMM-Interpolation</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Close</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B241" t="str">
-        <v>Schließen</v>
+        <v>Tetraedrisch</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Linear</v>
       </c>
       <c r="B242" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Linear</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Email address</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B243" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>ICC-Profil einbetten</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>you@example.com</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B244" t="str">
-        <v>sie@example.com</v>
+        <v>Kodierung, Komprimierung und Planaranordnung bestimmen das gespeicherte TIFF. Die RGB-/Gray-Ausgabe bleibt PNG, sofern keine TIFF-spezifische Option (Gleitkomma, LZW/ZIP, Getrennt) gewählt wird.</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B245" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Spektrales TIFF zusammenstellen</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>(optional)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B246" t="str">
-        <v>(optional)</v>
+        <v>Einkanalige Spektralbilder in Kanalreihenfolge ablegen und zu einem mehrkanaligen TIFF zusammenfügen.</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B247" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Spektralbilder hier ablegen (oder klicken, um auszuwählen)</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ch</v>
       </c>
       <c r="B248" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>Kan</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B249" t="str">
-        <v>Abbrechen</v>
+        <v>Zusammenfügen &amp; Speichern</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Subscribe</v>
+        <v>Assembling…</v>
       </c>
       <c r="B250" t="str">
-        <v>Abonnieren</v>
+        <v>Wird zusammengefügt…</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B251" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>{n} Kanäle zusammengefügt.</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B252" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Keine dieser Dateien sieht wie ein Bild aus (TIFF, PNG oder JPEG).</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B253" t="str">
-        <v>Schließen</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Privacy notice</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B254" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>{n} Datei(en) nicht geladen</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B255" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Diese Dateien sind keine ICC-Profile und wurden daher nicht zum Pool hinzugefügt:</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>OK</v>
       </c>
       <c r="B256" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B257" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>ICC-Profil hierher ziehen</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>or</v>
       </c>
       <c r="B258" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>oder</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Choose file</v>
       </c>
       <c r="B259" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Datei wählen</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Error:</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B260" t="str">
-        <v>Fehler:</v>
+        <v>.icc- und .icm-Dateien</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Convert to XML</v>
+        <v>Header</v>
       </c>
       <c r="B261" t="str">
-        <v>In XML konvertieren</v>
+        <v>Header</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Convert to JSON</v>
+        <v>Tags</v>
       </c>
       <c r="B262" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Convert to ICC</v>
+        <v>Validation</v>
       </c>
       <c r="B263" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Validierung</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Converting to XML…</v>
+        <v>Analysis</v>
       </c>
       <c r="B264" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Converting to JSON…</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B265" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Neutralachsen-Einfärbung</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B266" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Load ICC profile</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B267" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B268" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Profile ID</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B269" t="str">
-        <v>Profil-ID</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>No tags found.</v>
+        <v>% ink</v>
       </c>
       <c r="B270" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>% Farbe</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Tag Name</v>
+        <v>Perceptual</v>
       </c>
       <c r="B271" t="str">
-        <v>Tag-Name</v>
+        <v>Perzeptiv</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>ID</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>ID</v>
+        <v>Relativ farbmetrisch</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Offset</v>
+        <v>Saturation</v>
       </c>
       <c r="B273" t="str">
-        <v>Offset</v>
+        <v>Sättigung</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Size</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B274" t="str">
-        <v>Größe</v>
+        <v>Absolut farbmetrisch</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Pad</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B275" t="str">
-        <v>Auffüllung</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Bytes changed since load</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B276" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Type</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B277" t="str">
-        <v>Typ</v>
+        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Array of {type}</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B278" t="str">
-        <v>Array von {type}</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>(No content)</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B279" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Gamut-Volumen (ΔE³)</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>bytes</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B280" t="str">
-        <v>Bytes</v>
+        <v>Roundtrip-ΔE</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Loading full description…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B281" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Could not load full description:</v>
+        <v>mean</v>
       </c>
       <c r="B282" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Mittel</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>P90</v>
       </c>
       <c r="B283" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>max</v>
       </c>
       <c r="B284" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Max.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>No validation output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B285" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Profile is valid</v>
+        <v>Analysis</v>
       </c>
       <c r="B286" t="str">
-        <v>Profil ist gültig</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B287" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Plot</v>
       </c>
       <c r="B288" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Critical validation error</v>
+        <v>Raw Output</v>
       </c>
       <c r="B289" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Unknown validation status</v>
+        <v>XML</v>
       </c>
       <c r="B290" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>JSON</v>
       </c>
       <c r="B291" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Curves</v>
       </c>
       <c r="B292" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Valid</v>
+        <v>Input curves</v>
       </c>
       <c r="B293" t="str">
-        <v>Gültig</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Warning</v>
+        <v>Output curves</v>
       </c>
       <c r="B294" t="str">
-        <v>Warnung</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Error</v>
+        <v>CLUT image</v>
       </c>
       <c r="B295" t="str">
-        <v>Fehler</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Unknown</v>
+        <v>Gamut image</v>
       </c>
       <c r="B296" t="str">
-        <v>Unbekannt</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Pass</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B297" t="str">
-        <v>Bestanden</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Fail</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B298" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>View in context</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B299" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Validation detail</v>
+        <v>Curve table</v>
       </c>
       <c r="B300" t="str">
-        <v>Validierungsdetail</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Triggered by</v>
+        <v>Tables</v>
       </c>
       <c r="B301" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Field</v>
+        <v>Data</v>
       </c>
       <c r="B302" t="str">
-        <v>Feld</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Current value</v>
+        <v>Evaluate</v>
       </c>
       <c r="B303" t="str">
-        <v>Aktueller Wert</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Required: 0</v>
+        <v>Loading…</v>
       </c>
       <c r="B304" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Expected: {value}</v>
+        <v>Input</v>
       </c>
       <c r="B305" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Invalid</v>
+        <v>Output</v>
       </c>
       <c r="B306" t="str">
-        <v>Ungültig</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Floating point</v>
       </c>
       <c r="B307" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Close</v>
+        <v>Grid point</v>
       </c>
       <c r="B308" t="str">
-        <v>Schließen</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Loading XML editor…</v>
+        <v>Normalized</v>
       </c>
       <c r="B309" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Human</v>
       </c>
       <c r="B310" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B311" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B312" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>● unsaved XML edits</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B313" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading…</v>
       </c>
       <c r="B314" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B315" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B316" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>indent</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B317" t="str">
-        <v>Einrückung</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>sort keys</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B318" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
+        <v>Loading Profile Assessment WG report…</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Running Profile Assessment WG checks…</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Profile Assessment WG Report</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Profile-Assessment-WG-Bericht</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Security</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Sicherheit</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Conformance</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Konformität</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Quality</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Qualität</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>REPORT</v>
+      </c>
+      <c r="B325" t="str">
+        <v>BERICHT</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="B326" t="str">
+        <v>FEHLGESCHLAGEN</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>checks</v>
+      </c>
+      <c r="B327" t="str">
+        <v>Prüfungen</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>ICC Profile Tool · powered by IccProfLib</v>
+      </c>
+      <c r="B329" t="str">
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B330" t="str">
+        <v>ICC-Profil-Tool</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Betrieben mit {lib}</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Abonnieren</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Bei neuen Releases benachrichtigt werden</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B337" t="str">
+        <v>E-Mail-Adresse</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B338" t="str">
+        <v>sie@example.com</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B339" t="str">
+        <v>Wofür werden Sie profiletool nutzen?</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B340" t="str">
+        <v>(optional)</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B341" t="str">
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Abbrechen</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Abonnieren</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B345" t="str">
+        <v>Danke — wir melden uns.</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B346" t="str">
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Datenschutzhinweis</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B350" t="str">
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B351" t="str">
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B352" t="str">
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Fehler:</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B355" t="str">
+        <v>In XML konvertieren</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B356" t="str">
+        <v>In JSON konvertieren</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B357" t="str">
+        <v>In ICC konvertieren</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B358" t="str">
+        <v>Konvertiere in XML…</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B359" t="str">
+        <v>Konvertiere in JSON…</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B360" t="str">
+        <v>Konvertiere in ICC…</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B361" t="str">
+        <v>ICC-Profil laden</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B363" t="str">
+        <v>Profil-ID</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B364" t="str">
+        <v>Keine Tags gefunden.</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B365" t="str">
+        <v>Tag-Name</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B366" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Größe</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Auffüllung</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Bytes seit dem Laden geändert</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Typ</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Array von {type}</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B373" t="str">
+        <v>(Kein Inhalt)</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B374" t="str">
+        <v>Bytes</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Lade vollständige Beschreibung…</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B376" t="str">
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B377" t="str">
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Keine Validierungsausgabe</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B380" t="str">
+        <v>Profil ist gültig</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B381" t="str">
+        <v>Profil hat Warnung(en)</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B382" t="str">
+        <v>Profil ist nicht konform</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B383" t="str">
+        <v>Kritischer Validierungsfehler</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B384" t="str">
+        <v>Unbekannter Validierungsstatus</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Keine Warnungen oder Fehler gefunden.</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Gültig</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Warnung</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Fehler</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B390" t="str">
+        <v>Unbekannt</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Bestanden</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Fehlgeschlagen</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Im Kontext anzeigen</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B394" t="str">
+        <v>Validierungsdetail</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Ausgelöst durch</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B396" t="str">
+        <v>Feld</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B397" t="str">
+        <v>Aktueller Wert</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Erforderlich: 0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B399" t="str">
+        <v>Erwartet: {value}</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B400" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B401" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B402" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B403" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B404" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B405" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B406" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B407" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B408" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B409" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B410" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B411" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B412" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B319" t="str">
+      <c r="B413" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B413"/>
+  <dimension ref="A1:B410"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1053,2669 +1053,2645 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Based on</v>
       </c>
       <c r="B82" t="str">
-        <v>Laden Sie ein ICC-Profil hoch, um es gegen die Spezifikation</v>
+        <v>Basierend auf der</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>specification using the</v>
+        <v>demo implementation</v>
       </c>
       <c r="B83" t="str">
-        <v>mit der Demo-Implementierung</v>
+        <v>Demo-Implementierung</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation.</v>
+        <v>Validating…</v>
       </c>
       <c r="B84" t="str">
-        <v>zu validieren.</v>
+        <v>Validierung…</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Based on</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B85" t="str">
-        <v>Basierend auf der</v>
+        <v>ICC-Profil speichern</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>demo implementation</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B86" t="str">
-        <v>Demo-Implementierung</v>
+        <v>● Geändert — nicht gespeichert</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Validating…</v>
+        <v>Profiles</v>
       </c>
       <c r="B87" t="str">
-        <v>Validierung…</v>
+        <v>Profile</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Save ICC profile</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B88" t="str">
-        <v>ICC-Profil speichern</v>
+        <v>Profil-Pool anzeigen</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Collapse</v>
       </c>
       <c r="B89" t="str">
-        <v>● Geändert — nicht gespeichert</v>
+        <v>Einklappen</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Profiles</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>Profile</v>
+        <v>Profile laden</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Show profile pool</v>
+        <v>Remove</v>
       </c>
       <c r="B91" t="str">
-        <v>Profil-Pool anzeigen</v>
+        <v>Entfernen</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Collapse</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B92" t="str">
-        <v>Einklappen</v>
+        <v>ICC-Profile hierher ziehen</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load Profiles</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B93" t="str">
-        <v>Profile laden</v>
+        <v>oder ein Bild (TIFF/PNG/JPEG), um dessen eingebettetes Profil zu extrahieren — die Dateien bleiben auf Ihrem Gerät.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Remove</v>
+        <v>New from .cube</v>
       </c>
       <c r="B94" t="str">
-        <v>Entfernen</v>
+        <v>Neu aus .cube</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Sort by name</v>
       </c>
       <c r="B95" t="str">
-        <v>ICC-Profile hierher ziehen</v>
+        <v>Nach Namen sortieren</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>A–Z</v>
       </c>
       <c r="B96" t="str">
-        <v>oder ein Bild (TIFF/PNG/JPEG), um dessen eingebettetes Profil zu extrahieren — die Dateien bleiben auf Ihrem Gerät.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New from .cube</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>Neu aus .cube</v>
+        <v>Neues Profil aus .cube</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Sort by name</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B98" t="str">
-        <v>Nach Namen sortieren</v>
+        <v>Erstellen Sie einen ICC-DeviceLink aus einer Adobe/Resolve-.cube-3D-LUT. Das Ergebnis wird Ihrem Pool hinzugefügt und heruntergeladen.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>A–Z</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B99" t="str">
-        <v>A–Z</v>
+        <v>.cube-Datei wählen</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>New profile from .cube</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B100" t="str">
-        <v>Neues Profil aus .cube</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Erstellen Sie einen ICC-DeviceLink aus einer Adobe/Resolve-.cube-3D-LUT. Das Ergebnis wird Ihrem Pool hinzugefügt und heruntergeladen.</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Choose .cube file</v>
-      </c>
-      <c r="B102" t="str">
-        <v>.cube-Datei wählen</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>or drop it here, or paste below</v>
-      </c>
-      <c r="B103" t="str">
         <v>oder hierher ziehen oder unten einfügen</v>
       </c>
     </row>
-    <row r="104" xml:space="preserve">
-      <c r="A104" t="str" xml:space="preserve">
+    <row r="101" xml:space="preserve">
+      <c r="A101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B104" t="str" xml:space="preserve">
+      <c r="B101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Abbrechen</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Create DeviceLink</v>
+      </c>
+      <c r="B103" t="str">
+        <v>DeviceLink erstellen</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Creating…</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Wird erstellt…</v>
+      </c>
+    </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Cancel</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B105" t="str">
-        <v>Abbrechen</v>
+        <v>Diese Datei konnte nicht gelesen werden.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Create DeviceLink</v>
+        <v>Profile</v>
       </c>
       <c r="B106" t="str">
-        <v>DeviceLink erstellen</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Creating…</v>
+        <v>Compare</v>
       </c>
       <c r="B107" t="str">
-        <v>Wird erstellt…</v>
+        <v>Vergleichen</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Could not read that file.</v>
+        <v>Combine</v>
       </c>
       <c r="B108" t="str">
-        <v>Diese Datei konnte nicht gelesen werden.</v>
+        <v>Verknüpfen</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Profile</v>
+        <v>Spectral</v>
       </c>
       <c r="B109" t="str">
-        <v>Profil</v>
+        <v>Spektral</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Compare</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B110" t="str">
-        <v>Vergleichen</v>
+        <v>Ziehen Sie Profile aus dem Pool auf diesen Tab</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Combine</v>
+        <v>Remove</v>
       </c>
       <c r="B111" t="str">
-        <v>Verknüpfen</v>
+        <v>Entfernen</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Spectral</v>
+        <v>No profile selected</v>
       </c>
       <c r="B112" t="str">
-        <v>Spektral</v>
+        <v>Kein Profil ausgewählt</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B113" t="str">
-        <v>Ziehen Sie Profile aus dem Pool auf diesen Tab</v>
+        <v>Ziehen Sie ein Profil aus dem Pool auf den Profil-Tab, um es zu untersuchen.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Remove</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B114" t="str">
-        <v>Entfernen</v>
+        <v>Noch nichts zu vergleichen</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>No profile selected</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B115" t="str">
-        <v>Kein Profil ausgewählt</v>
+        <v>Ziehen Sie ein oder mehrere Profile auf den Vergleichen-Tab.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B116" t="str">
-        <v>Ziehen Sie ein Profil aus dem Pool auf den Profil-Tab, um es zu untersuchen.</v>
+        <v>Gamut-Vergleich</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Nothing to compare yet</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B117" t="str">
-        <v>Noch nichts zu vergleichen</v>
+        <v>3D-Gamut- und 2D-Schnittansichten kommen hierher. Gesammelt:</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B118" t="str">
-        <v>Ziehen Sie ein oder mehrere Profile auf den Vergleichen-Tab.</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut comparison</v>
+        <v>Shell</v>
       </c>
       <c r="B119" t="str">
-        <v>Gamut-Vergleich</v>
+        <v>Hülle</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Wireframe</v>
       </c>
       <c r="B120" t="str">
-        <v>3D-Gamut- und 2D-Schnittansichten kommen hierher. Gesammelt:</v>
+        <v>Drahtgitter</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Rendering intent</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B121" t="str">
-        <v>Render-Intent</v>
+        <v>Achsenwerte</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Shell</v>
+        <v>Opacity</v>
       </c>
       <c r="B122" t="str">
-        <v>Hülle</v>
+        <v>Deckkraft</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Wireframe</v>
+        <v>Colour</v>
       </c>
       <c r="B123" t="str">
-        <v>Drahtgitter</v>
+        <v>Farbe</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Axis numbers</v>
+        <v>Solid</v>
       </c>
       <c r="B124" t="str">
-        <v>Achsenwerte</v>
+        <v>Einfarbig</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Opacity</v>
+        <v>By value</v>
       </c>
       <c r="B125" t="str">
-        <v>Deckkraft</v>
+        <v>Nach Wert</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Colour</v>
+        <v>By hue</v>
       </c>
       <c r="B126" t="str">
-        <v>Farbe</v>
+        <v>Nach Farbton</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Solid</v>
+        <v>Rotation</v>
       </c>
       <c r="B127" t="str">
-        <v>Einfarbig</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>By value</v>
+        <v>Turntable</v>
       </c>
       <c r="B128" t="str">
-        <v>Nach Wert</v>
+        <v>Drehteller</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>By hue</v>
+        <v>Orbit</v>
       </c>
       <c r="B129" t="str">
-        <v>Nach Farbton</v>
+        <v>Orbit</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Rotation</v>
+        <v>Drag speed</v>
       </c>
       <c r="B130" t="str">
-        <v>Rotation</v>
+        <v>Ziehgeschwindigkeit</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Turntable</v>
+        <v>Roll</v>
       </c>
       <c r="B131" t="str">
-        <v>Drehteller</v>
+        <v>Rollen</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Orbit</v>
+        <v>Roll speed</v>
       </c>
       <c r="B132" t="str">
-        <v>Orbit</v>
+        <v>Rollgeschwindigkeit</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Drag speed</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B133" t="str">
-        <v>Ziehgeschwindigkeit</v>
+        <v>Gamut wird erstellt…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Roll</v>
+        <v>no gamut</v>
       </c>
       <c r="B134" t="str">
-        <v>Rollen</v>
+        <v>kein Gamut</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Roll speed</v>
+        <v>Show / hide</v>
       </c>
       <c r="B135" t="str">
-        <v>Rollgeschwindigkeit</v>
+        <v>Ein-/ausblenden</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Building gamut…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B136" t="str">
-        <v>Gamut wird erstellt…</v>
+        <v>3D-Gamut-Hülle</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>no gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B137" t="str">
-        <v>kein Gamut</v>
+        <v>2D-Gamut-Schnitt</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Show / hide</v>
+        <v>Plane</v>
       </c>
       <c r="B138" t="str">
-        <v>Ein-/ausblenden</v>
+        <v>Ebene</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>3-D gamut shell</v>
+        <v>L*</v>
       </c>
       <c r="B139" t="str">
-        <v>3D-Gamut-Hülle</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>2-D gamut slice</v>
+        <v>a*</v>
       </c>
       <c r="B140" t="str">
-        <v>2D-Gamut-Schnitt</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Plane</v>
+        <v>b*</v>
       </c>
       <c r="B141" t="str">
-        <v>Ebene</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>L*</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B142" t="str">
-        <v>L*</v>
+        <v>Keines der ausgewählten Profile hat ein Gerät→PCS-Transform, aus dem sich ein Gamut ableiten lässt.</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>a*</v>
+        <v>Linking</v>
       </c>
       <c r="B143" t="str">
-        <v>a*</v>
+        <v>Verknüpfung</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>b*</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B144" t="str">
-        <v>b*</v>
+        <v>DeviceLink-Erzeugung und Transformationen über mehrere Profile folgen in einer späteren Phase.</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B145" t="str">
-        <v>Keines der ausgewählten Profile hat ein Gerät→PCS-Transform, aus dem sich ein Gamut ableiten lässt.</v>
+        <v>Weitere Link-Ersteller (DeviceLink, …) folgen hier.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Linking</v>
+        <v>Observer Change</v>
       </c>
       <c r="B146" t="str">
-        <v>Verknüpfung</v>
+        <v>V4-Display-Ersteller</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B147" t="str">
-        <v>DeviceLink-Erzeugung und Transformationen über mehrere Profile folgen in einer späteren Phase.</v>
+        <v>Ziehen Sie ein V5-RGB-Display- und ein V5-Beobachterprofil hierher, um ein V4-Displayprofil zu erstellen.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B148" t="str">
-        <v>Weitere Link-Ersteller (DeviceLink, …) folgen hier.</v>
+        <v>V5-RGB-Display</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Observer Change</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B149" t="str">
-        <v>V4-Display-Ersteller</v>
+        <v>Displayprofil ablegen</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B150" t="str">
-        <v>Ziehen Sie ein V5-RGB-Display- und ein V5-Beobachterprofil hierher, um ein V4-Displayprofil zu erstellen.</v>
+        <v>V5-Beobachter (PCC)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 RGB display</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B151" t="str">
-        <v>V5-RGB-Display</v>
+        <v>Beobachterprofil ablegen</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop a display profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B152" t="str">
-        <v>Displayprofil ablegen</v>
+        <v>Ein Profil, das weder ein V5-RGB-Display noch ein Beobachter ist, wurde ignoriert.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B153" t="str">
-        <v>V5-Beobachter (PCC)</v>
+        <v>V4-Displayprofil erstellen</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop an observer profile</v>
+        <v>Profile name</v>
       </c>
       <c r="B154" t="str">
-        <v>Beobachterprofil ablegen</v>
+        <v>Profilname</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>Create</v>
       </c>
       <c r="B155" t="str">
-        <v>Ein Profil, das weder ein V5-RGB-Display noch ein Beobachter ist, wurde ignoriert.</v>
+        <v>Erstellen</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Making…</v>
       </c>
       <c r="B156" t="str">
-        <v>V4-Displayprofil erstellen</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile name</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B157" t="str">
-        <v>Profilname</v>
+        <v>„{name}“ erstellt — dem Pool und diesem Tab hinzugefügt.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Create</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B158" t="str">
-        <v>Erstellen</v>
+        <v>Link-Pipeline</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Making…</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B159" t="str">
-        <v>Wird erstellt…</v>
+        <v>Erstellen Sie eine Kette aus Profilen und erzeugen Sie daraus einen DeviceLink, transformieren Sie ein Bild oder einen Farbdatensatz.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Done</v>
       </c>
       <c r="B160" t="str">
-        <v>„{name}“ erstellt — dem Pool und diesem Tab hinzugefügt.</v>
+        <v>Fertig</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Link Pipeline</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B161" t="str">
-        <v>Link-Pipeline</v>
+        <v>Bild zum Transformieren ablegen (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Checking image…</v>
       </c>
       <c r="B162" t="str">
-        <v>Erstellen Sie eine Kette aus Profilen und erzeugen Sie daraus einen DeviceLink, transformieren Sie ein Bild oder einen Farbdatensatz.</v>
+        <v>Bild wird geprüft…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Done</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B163" t="str">
-        <v>Fertig</v>
+        <v>Kein unterstütztes Bildformat (TIFF, PNG oder JPEG).</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B164" t="str">
-        <v>Bild zum Transformieren ablegen (TIFF/PNG/JPEG)</v>
+        <v>Bild zu groß ({mp} MP; Grenzwert {max} MP).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Checking image…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B165" t="str">
-        <v>Bild wird geprüft…</v>
+        <v>Bild transformieren</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Transforming…</v>
       </c>
       <c r="B166" t="str">
-        <v>Kein unterstütztes Bildformat (TIFF, PNG oder JPEG).</v>
+        <v>Wird transformiert…</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B167" t="str">
-        <v>Bild zu groß ({mp} MP; Grenzwert {max} MP).</v>
+        <v>Profile ablegen, um die Kette zu starten</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Transform Image</v>
+        <v>removed</v>
       </c>
       <c r="B168" t="str">
-        <v>Bild transformieren</v>
+        <v>entfernt</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Transforming…</v>
+        <v>Move earlier</v>
       </c>
       <c r="B169" t="str">
-        <v>Wird transformiert…</v>
+        <v>Nach vorne verschieben</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Move later</v>
       </c>
       <c r="B170" t="str">
-        <v>Profile ablegen, um die Kette zu starten</v>
+        <v>Nach hinten verschieben</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>removed</v>
+        <v>Move up</v>
       </c>
       <c r="B171" t="str">
-        <v>entfernt</v>
+        <v>Nach oben verschieben</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move earlier</v>
+        <v>Move down</v>
       </c>
       <c r="B172" t="str">
-        <v>Nach vorne verschieben</v>
+        <v>Nach unten verschieben</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move later</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B173" t="str">
-        <v>Nach hinten verschieben</v>
+        <v>Rendering-Priorität (alle)</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move up</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B174" t="str">
-        <v>Nach oben verschieben</v>
+        <v>Rendering-Priorität für diese Transformation</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move down</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B175" t="str">
-        <v>Nach unten verschieben</v>
+        <v>Die Transformationen verwenden unterschiedliche Rendering-Prioritäten</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B176" t="str">
-        <v>Rendering-Priorität (alle)</v>
+        <v>Kettenrichtung umkehren (kehrt die erste Transformation um und wirkt sich auf die gesamte Kette aus)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B177" t="str">
-        <v>Rendering-Priorität für diese Transformation</v>
+        <v>Ein verkettetes Profil wurde aus dem Pool entfernt — entfernen Sie es, um fortzufahren.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Chain</v>
       </c>
       <c r="B178" t="str">
-        <v>Die Transformationen verwenden unterschiedliche Rendering-Prioritäten</v>
+        <v>Kette</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B179" t="str">
-        <v>Kettenrichtung umkehren (kehrt die erste Transformation um und wirkt sich auf die gesamte Kette aus)</v>
+        <v>Die Kette konnte nicht analysiert werden.</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B180" t="str">
-        <v>Ein verkettetes Profil wurde aus dem Pool entfernt — entfernen Sie es, um fortzufahren.</v>
+        <v>Kette wird geprüft…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Chain</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B181" t="str">
-        <v>Kette</v>
+        <v>Die Kette verbindet sich nicht ({detail}).</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>Die Kette konnte nicht analysiert werden.</v>
+        <v>Profil {n} verbindet sich nicht mit der vorherigen Stufe ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Checking chain…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B183" t="str">
-        <v>Kette wird geprüft…</v>
+        <v>Beheben Sie die Kette, bevor Sie Bilder verarbeiten</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Clear</v>
       </c>
       <c r="B184" t="str">
-        <v>Die Kette verbindet sich nicht ({detail}).</v>
+        <v>Leeren</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B185" t="str">
-        <v>Profil {n} verbindet sich nicht mit der vorherigen Stufe ({detail}).</v>
+        <v>DeviceLink erstellen</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B186" t="str">
-        <v>Beheben Sie die Kette, bevor Sie Bilder verarbeiten</v>
+        <v>DeviceLink-Name</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Clear</v>
+        <v>Making…</v>
       </c>
       <c r="B187" t="str">
-        <v>Leeren</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Make DeviceLink</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B188" t="str">
-        <v>DeviceLink erstellen</v>
+        <v>„{name}“ erstellt — zum Pool und zu diesem Tab hinzugefügt.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>DeviceLink name</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B189" t="str">
-        <v>DeviceLink-Name</v>
+        <v>{src}-Bilder ablegen, um sie in {dst} zu konvertieren — Ergebnisse werden heruntergeladen, nichts wird gespeichert.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Making…</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B190" t="str">
-        <v>Wird erstellt…</v>
+        <v>Erstellen Sie eine Kette, um Bilder zu verarbeiten</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B191" t="str">
-        <v>„{name}“ erstellt — zum Pool und zu diesem Tab hinzugefügt.</v>
+        <v>Diese Kette beginnt und endet nicht in einem Bildfarbraum</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B192" t="str">
-        <v>{src}-Bilder ablegen, um sie in {dst} zu konvertieren — Ergebnisse werden heruntergeladen, nichts wird gespeichert.</v>
+        <v>Transformiertes Bild gespeichert.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B193" t="str">
-        <v>Erstellen Sie eine Kette, um Bilder zu verarbeiten</v>
+        <v>Farbdatensatz ablegen (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B194" t="str">
-        <v>Diese Kette beginnt und endet nicht in einem Bildfarbraum</v>
+        <v>Diese Datei konnte nicht gelesen werden.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B195" t="str">
-        <v>Transformiertes Bild gespeichert.</v>
+        <v>Datendatei zu groß.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Transform Data</v>
       </c>
       <c r="B196" t="str">
-        <v>Farbdatensatz ablegen (CGATS/CSV/CxF/JSON)</v>
+        <v>Daten transformieren</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Could not read that file.</v>
+        <v>Transforming…</v>
       </c>
       <c r="B197" t="str">
-        <v>Diese Datei konnte nicht gelesen werden.</v>
+        <v>Wird transformiert…</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Data file too large.</v>
+        <v>Prefer</v>
       </c>
       <c r="B198" t="str">
-        <v>Datendatei zu groß.</v>
+        <v>Bevorzugen</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Transform Data</v>
+        <v>Observer</v>
       </c>
       <c r="B199" t="str">
-        <v>Daten transformieren</v>
+        <v>Beobachter</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Transforming…</v>
+        <v>Illuminant</v>
       </c>
       <c r="B200" t="str">
-        <v>Wird transformiert…</v>
+        <v>Lichtart</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Prefer</v>
+        <v>Condition</v>
       </c>
       <c r="B201" t="str">
-        <v>Bevorzugen</v>
+        <v>Bedingung</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Observer</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B202" t="str">
-        <v>Beobachter</v>
+        <v>{n} Duplikat(e) filtern</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Illuminant</v>
+        <v>median</v>
       </c>
       <c r="B203" t="str">
-        <v>Lichtart</v>
+        <v>Median</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Condition</v>
+        <v>mean</v>
       </c>
       <c r="B204" t="str">
-        <v>Bedingung</v>
+        <v>Mittelwert</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>patches</v>
       </c>
       <c r="B205" t="str">
-        <v>{n} Duplikat(e) filtern</v>
+        <v>Farbfelder</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>median</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B206" t="str">
-        <v>Median</v>
+        <v>{n} Duplikate</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>mean</v>
+        <v>Transform result</v>
       </c>
       <c r="B207" t="str">
-        <v>Mittelwert</v>
+        <v>Transformationsergebnis</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>patches</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B208" t="str">
-        <v>Farbfelder</v>
+        <v>{src} → {dst} · {n} Farbfelder</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{n} duplicates</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B209" t="str">
-        <v>{n} Duplikate</v>
+        <v>Zeigt die ersten {shown} von {total} — Speichern schreibt alle.</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Transform result</v>
+        <v>Save as</v>
       </c>
       <c r="B210" t="str">
-        <v>Transformationsergebnis</v>
+        <v>Speichern unter</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Save</v>
       </c>
       <c r="B211" t="str">
-        <v>{src} → {dst} · {n} Farbfelder</v>
+        <v>Speichern</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B212" t="str">
-        <v>Zeigt die ersten {shown} von {total} — Speichern schreibt alle.</v>
+        <v>Transformation umkehren</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Save as</v>
+        <v>Inverting…</v>
       </c>
       <c r="B213" t="str">
-        <v>Speichern unter</v>
+        <v>Wird umgekehrt…</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Save</v>
+        <v>Invert</v>
       </c>
       <c r="B214" t="str">
-        <v>Speichern</v>
+        <v>Umkehren</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert Transform</v>
+        <v>last stage</v>
       </c>
       <c r="B215" t="str">
-        <v>Transformation umkehren</v>
+        <v>letzte Stufe</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Inverting…</v>
+        <v>first stage</v>
       </c>
       <c r="B216" t="str">
-        <v>Wird umgekehrt…</v>
+        <v>erste Stufe</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B217" t="str">
-        <v>Umkehren</v>
+        <v>Daten in {in} → Suche {out}</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>last stage</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B218" t="str">
-        <v>letzte Stufe</v>
+        <v>Die Umkehrung benötigt eine Kette aus 2–3 Profilen</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>first stage</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B219" t="str">
-        <v>erste Stufe</v>
+        <v>Der Datensatz muss in {in} vorliegen; die inverse Suche liefert {out} sowie einen Invertierbarkeits-Kostenwert pro Farbfeld.</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B220" t="str">
-        <v>Daten in {in} → Suche {out}</v>
+        <v>ΔE-Kosten</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B221" t="str">
-        <v>Die Umkehrung benötigt eine Kette aus 2–3 Profilen</v>
+        <v>Dieses Bild enthält ein eingebettetes ICC-Profil.</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B222" t="str">
-        <v>Der Datensatz muss in {in} vorliegen; die inverse Suche liefert {out} sowie einen Invertierbarkeits-Kostenwert pro Farbfeld.</v>
+        <v>Extrahieren &amp; zur Kette hinzufügen</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>ΔE cost</v>
+        <v>Extracting…</v>
       </c>
       <c r="B223" t="str">
-        <v>ΔE-Kosten</v>
+        <v>Wird extrahiert…</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B224" t="str">
-        <v>Dieses Bild enthält ein eingebettetes ICC-Profil.</v>
+        <v>Verwerfen</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B225" t="str">
-        <v>Extrahieren &amp; zur Kette hinzufügen</v>
+        <v>Eingebettetes Profil extrahiert — zum Pool hinzugefügt und an den Anfang der Kette gesetzt.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracting…</v>
+        <v>Image output options</v>
       </c>
       <c r="B226" t="str">
-        <v>Wird extrahiert…</v>
+        <v>Bildausgabeoptionen</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Dismiss</v>
+        <v>Encoding</v>
       </c>
       <c r="B227" t="str">
-        <v>Verwerfen</v>
+        <v>Kodierung</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Same as source</v>
       </c>
       <c r="B228" t="str">
-        <v>Eingebettetes Profil extrahiert — zum Pool hinzugefügt und an den Anfang der Kette gesetzt.</v>
+        <v>Wie Quelle</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Image output options</v>
+        <v>8-bit</v>
       </c>
       <c r="B229" t="str">
-        <v>Bildausgabeoptionen</v>
+        <v>8 Bit</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Encoding</v>
+        <v>16-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>Kodierung</v>
+        <v>16 Bit</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Same as source</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B231" t="str">
-        <v>Wie Quelle</v>
+        <v>Gleitkomma (32 Bit)</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>8-bit</v>
+        <v>Compression</v>
       </c>
       <c r="B232" t="str">
-        <v>8 Bit</v>
+        <v>Komprimierung</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>16-bit</v>
+        <v>None</v>
       </c>
       <c r="B233" t="str">
-        <v>16 Bit</v>
+        <v>Keine</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Float (32-bit)</v>
+        <v>Planar</v>
       </c>
       <c r="B234" t="str">
-        <v>Gleitkomma (32 Bit)</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Compression</v>
+        <v>Composite</v>
       </c>
       <c r="B235" t="str">
-        <v>Komprimierung</v>
+        <v>Verschachtelt</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>None</v>
+        <v>Separated</v>
       </c>
       <c r="B236" t="str">
-        <v>Keine</v>
+        <v>Getrennt</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Planar</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B237" t="str">
-        <v>Planar</v>
+        <v>CMM-Interpolation</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Composite</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B238" t="str">
-        <v>Verschachtelt</v>
+        <v>Tetraedrisch</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Separated</v>
+        <v>Linear</v>
       </c>
       <c r="B239" t="str">
-        <v>Getrennt</v>
+        <v>Linear</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>CMM interpolation</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B240" t="str">
-        <v>CMM-Interpolation</v>
+        <v>ICC-Profil einbetten</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Tetrahedral</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B241" t="str">
-        <v>Tetraedrisch</v>
+        <v>Kodierung, Komprimierung und Planaranordnung bestimmen das gespeicherte TIFF. Die RGB-/Gray-Ausgabe bleibt PNG, sofern keine TIFF-spezifische Option (Gleitkomma, LZW/ZIP, Getrennt) gewählt wird.</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Linear</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B242" t="str">
-        <v>Linear</v>
+        <v>Spektrales TIFF zusammenstellen</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Embed ICC</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B243" t="str">
-        <v>ICC-Profil einbetten</v>
+        <v>Einkanalige Spektralbilder in Kanalreihenfolge ablegen und zu einem mehrkanaligen TIFF zusammenfügen.</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B244" t="str">
-        <v>Kodierung, Komprimierung und Planaranordnung bestimmen das gespeicherte TIFF. Die RGB-/Gray-Ausgabe bleibt PNG, sofern keine TIFF-spezifische Option (Gleitkomma, LZW/ZIP, Getrennt) gewählt wird.</v>
+        <v>Spektralbilder hier ablegen (oder klicken, um auszuwählen)</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>ch</v>
       </c>
       <c r="B245" t="str">
-        <v>Spektrales TIFF zusammenstellen</v>
+        <v>Kan</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B246" t="str">
-        <v>Einkanalige Spektralbilder in Kanalreihenfolge ablegen und zu einem mehrkanaligen TIFF zusammenfügen.</v>
+        <v>Zusammenfügen &amp; Speichern</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Assembling…</v>
       </c>
       <c r="B247" t="str">
-        <v>Spektralbilder hier ablegen (oder klicken, um auszuwählen)</v>
+        <v>Wird zusammengefügt…</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>ch</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B248" t="str">
-        <v>Kan</v>
+        <v>{n} Kanäle zusammengefügt.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B249" t="str">
-        <v>Zusammenfügen &amp; Speichern</v>
+        <v>Keine dieser Dateien sieht wie ein Bild aus (TIFF, PNG oder JPEG).</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Assembling…</v>
+        <v>Cancel</v>
       </c>
       <c r="B250" t="str">
-        <v>Wird zusammengefügt…</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B251" t="str">
-        <v>{n} Kanäle zusammengefügt.</v>
+        <v>{n} Datei(en) nicht geladen</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B252" t="str">
-        <v>Keine dieser Dateien sieht wie ein Bild aus (TIFF, PNG oder JPEG).</v>
+        <v>Diese Dateien sind keine ICC-Profile und wurden daher nicht zum Pool hinzugefügt:</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Cancel</v>
+        <v>OK</v>
       </c>
       <c r="B253" t="str">
-        <v>Abbrechen</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B254" t="str">
-        <v>{n} Datei(en) nicht geladen</v>
+        <v>ICC-Profil hierher ziehen</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>or</v>
       </c>
       <c r="B255" t="str">
-        <v>Diese Dateien sind keine ICC-Profile und wurden daher nicht zum Pool hinzugefügt:</v>
+        <v>oder</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>OK</v>
+        <v>Choose file</v>
       </c>
       <c r="B256" t="str">
-        <v>OK</v>
+        <v>Datei wählen</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B257" t="str">
-        <v>ICC-Profil hierher ziehen</v>
+        <v>.icc- und .icm-Dateien</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>or</v>
+        <v>Header</v>
       </c>
       <c r="B258" t="str">
-        <v>oder</v>
+        <v>Header</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Choose file</v>
+        <v>Tags</v>
       </c>
       <c r="B259" t="str">
-        <v>Datei wählen</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>.icc and .icm files</v>
+        <v>Validation</v>
       </c>
       <c r="B260" t="str">
-        <v>.icc- und .icm-Dateien</v>
+        <v>Validierung</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Header</v>
+        <v>Analysis</v>
       </c>
       <c r="B261" t="str">
-        <v>Header</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Tags</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B262" t="str">
-        <v>Tags</v>
+        <v>Neutralachsen-Einfärbung</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Validation</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B263" t="str">
-        <v>Validierung</v>
+        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Analysis</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B264" t="str">
-        <v>Analyse</v>
+        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B265" t="str">
-        <v>Neutralachsen-Einfärbung</v>
+        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B266" t="str">
-        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>% ink</v>
       </c>
       <c r="B267" t="str">
-        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>% Farbe</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Perceptual</v>
       </c>
       <c r="B268" t="str">
-        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
+        <v>Perzeptiv</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Rendering intent</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B269" t="str">
-        <v>Render-Intent</v>
+        <v>Relativ farbmetrisch</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>% ink</v>
+        <v>Saturation</v>
       </c>
       <c r="B270" t="str">
-        <v>% Farbe</v>
+        <v>Sättigung</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Perceptual</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B271" t="str">
-        <v>Perzeptiv</v>
+        <v>Absolut farbmetrisch</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B272" t="str">
-        <v>Relativ farbmetrisch</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Saturation</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B273" t="str">
-        <v>Sättigung</v>
+        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B274" t="str">
-        <v>Absolut farbmetrisch</v>
+        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Profile Statistics</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B275" t="str">
-        <v>Profilstatistik</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B276" t="str">
-        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
+        <v>Gamut-Volumen (ΔE³)</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B277" t="str">
-        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
+        <v>Roundtrip-ΔE</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Rendering intent</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B278" t="str">
-        <v>Render-Intent</v>
+        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>mean</v>
       </c>
       <c r="B279" t="str">
-        <v>Gamut-Volumen (ΔE³)</v>
+        <v>Mittel</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Round-trip ΔE</v>
+        <v>P90</v>
       </c>
       <c r="B280" t="str">
-        <v>Roundtrip-ΔE</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>max</v>
       </c>
       <c r="B281" t="str">
-        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
+        <v>Max.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>mean</v>
+        <v>Analysing…</v>
       </c>
       <c r="B282" t="str">
-        <v>Mittel</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>P90</v>
+        <v>Analysis</v>
       </c>
       <c r="B283" t="str">
-        <v>P90</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>max</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B284" t="str">
-        <v>Max.</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B285" t="str">
-        <v>Analyse läuft…</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B286" t="str">
-        <v>Analyse</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B287" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Plot</v>
+        <v>JSON</v>
       </c>
       <c r="B288" t="str">
-        <v>Diagramm</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Raw Output</v>
+        <v>Curves</v>
       </c>
       <c r="B289" t="str">
-        <v>Rohausgabe</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>XML</v>
+        <v>Input curves</v>
       </c>
       <c r="B290" t="str">
-        <v>XML</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>JSON</v>
+        <v>Output curves</v>
       </c>
       <c r="B291" t="str">
-        <v>JSON</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Curves</v>
+        <v>CLUT image</v>
       </c>
       <c r="B292" t="str">
-        <v>Kurven</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Input curves</v>
+        <v>Gamut image</v>
       </c>
       <c r="B293" t="str">
-        <v>Eingangskurven</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Output curves</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B294" t="str">
-        <v>Ausgangskurven</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>CLUT image</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B295" t="str">
-        <v>CLUT-Bild</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Gamut image</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B296" t="str">
-        <v>Gamut-Bild</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Chromaticity</v>
+        <v>Curve table</v>
       </c>
       <c r="B297" t="str">
-        <v>Chromazität</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Scatter plot</v>
+        <v>Tables</v>
       </c>
       <c r="B298" t="str">
-        <v>Streudiagramm</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tone response curve</v>
+        <v>Data</v>
       </c>
       <c r="B299" t="str">
-        <v>Tonwertkurve</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Curve table</v>
+        <v>Evaluate</v>
       </c>
       <c r="B300" t="str">
-        <v>Kurventabelle</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Tables</v>
+        <v>Loading…</v>
       </c>
       <c r="B301" t="str">
-        <v>Tabellen</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Data</v>
+        <v>Input</v>
       </c>
       <c r="B302" t="str">
-        <v>Daten</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Evaluate</v>
+        <v>Output</v>
       </c>
       <c r="B303" t="str">
-        <v>Auswerten</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Loading…</v>
+        <v>Floating point</v>
       </c>
       <c r="B304" t="str">
-        <v>Wird geladen…</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Input</v>
+        <v>Grid point</v>
       </c>
       <c r="B305" t="str">
-        <v>Eingang</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Output</v>
+        <v>Normalized</v>
       </c>
       <c r="B306" t="str">
-        <v>Ausgang</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Floating point</v>
+        <v>Human</v>
       </c>
       <c r="B307" t="str">
-        <v>Gleitkomma</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Grid point</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B308" t="str">
-        <v>Gitterpunkt</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Normalized</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B309" t="str">
-        <v>Normalisiert</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Human</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B310" t="str">
-        <v>Lesbar</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Device → PCS</v>
+        <v>Loading…</v>
       </c>
       <c r="B311" t="str">
-        <v>Gerät → PCS</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B312" t="str">
-        <v>PCS → Gerät</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No CLUT grid</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B313" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Loading…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B314" t="str">
-        <v>Wird geladen…</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B315" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B316" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B317" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B318" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Security</v>
       </c>
       <c r="B319" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Conformance</v>
       </c>
       <c r="B320" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Quality</v>
       </c>
       <c r="B321" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Security</v>
+        <v>REPORT</v>
       </c>
       <c r="B322" t="str">
-        <v>Sicherheit</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Conformance</v>
+        <v>FAIL</v>
       </c>
       <c r="B323" t="str">
-        <v>Konformität</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Quality</v>
+        <v>checks</v>
       </c>
       <c r="B324" t="str">
-        <v>Qualität</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>REPORT</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B325" t="str">
-        <v>BERICHT</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>FAIL</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B326" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>checks</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B327" t="str">
-        <v>Prüfungen</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B328" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Subscribe</v>
       </c>
       <c r="B329" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B330" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Powered by {lib}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B331" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B332" t="str">
-        <v>Abonnieren</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B333" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Get notified about new releases</v>
+        <v>Email address</v>
       </c>
       <c r="B334" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B335" t="str">
-        <v>Schließen</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B336" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Email address</v>
+        <v>(optional)</v>
       </c>
       <c r="B337" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>you@example.com</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B338" t="str">
-        <v>sie@example.com</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>How will you use profiletool?</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B339" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>(optional)</v>
+        <v>Cancel</v>
       </c>
       <c r="B340" t="str">
-        <v>(optional)</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B341" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B342" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Cancel</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B343" t="str">
-        <v>Abbrechen</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B344" t="str">
-        <v>Abonnieren</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B345" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B346" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Close</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B347" t="str">
-        <v>Schließen</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Privacy notice</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B348" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Error:</v>
       </c>
       <c r="B351" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B352" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B353" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Error:</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B354" t="str">
-        <v>Fehler:</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to XML</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B355" t="str">
-        <v>In XML konvertieren</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Convert to JSON</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B356" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B357" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to XML…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B358" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Converting to JSON…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B359" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Converting to ICC…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B360" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Load ICC profile</v>
+        <v>No tags found.</v>
       </c>
       <c r="B361" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Tag Name</v>
       </c>
       <c r="B362" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Profile ID</v>
+        <v>ID</v>
       </c>
       <c r="B363" t="str">
-        <v>Profil-ID</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>No tags found.</v>
+        <v>Offset</v>
       </c>
       <c r="B364" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Tag Name</v>
+        <v>Size</v>
       </c>
       <c r="B365" t="str">
-        <v>Tag-Name</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ID</v>
+        <v>Pad</v>
       </c>
       <c r="B366" t="str">
-        <v>ID</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Offset</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B367" t="str">
-        <v>Offset</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Size</v>
+        <v>Type</v>
       </c>
       <c r="B368" t="str">
-        <v>Größe</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Pad</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B369" t="str">
-        <v>Auffüllung</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Bytes changed since load</v>
+        <v>(No content)</v>
       </c>
       <c r="B370" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Type</v>
+        <v>bytes</v>
       </c>
       <c r="B371" t="str">
-        <v>Typ</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Array of {type}</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B372" t="str">
-        <v>Array von {type}</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>(No content)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B373" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>bytes</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B374" t="str">
-        <v>Bytes</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Loading full description…</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B375" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Could not load full description:</v>
+        <v>No validation output</v>
       </c>
       <c r="B376" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B377" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B378" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>No validation output</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B379" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B380" t="str">
-        <v>Profil ist gültig</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B381" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B382" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical validation error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B383" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Unknown validation status</v>
+        <v>Valid</v>
       </c>
       <c r="B384" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Warning</v>
       </c>
       <c r="B385" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Error</v>
       </c>
       <c r="B386" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Valid</v>
+        <v>Unknown</v>
       </c>
       <c r="B387" t="str">
-        <v>Gültig</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Warning</v>
+        <v>Pass</v>
       </c>
       <c r="B388" t="str">
-        <v>Warnung</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Error</v>
+        <v>Fail</v>
       </c>
       <c r="B389" t="str">
-        <v>Fehler</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Unknown</v>
+        <v>View in context</v>
       </c>
       <c r="B390" t="str">
-        <v>Unbekannt</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Pass</v>
+        <v>Validation detail</v>
       </c>
       <c r="B391" t="str">
-        <v>Bestanden</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Fail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B392" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>View in context</v>
+        <v>Field</v>
       </c>
       <c r="B393" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Validation detail</v>
+        <v>Current value</v>
       </c>
       <c r="B394" t="str">
-        <v>Validierungsdetail</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Triggered by</v>
+        <v>Required: 0</v>
       </c>
       <c r="B395" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Field</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B396" t="str">
-        <v>Feld</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Current value</v>
+        <v>Invalid</v>
       </c>
       <c r="B397" t="str">
-        <v>Aktueller Wert</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Required: 0</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B398" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Expected: {value}</v>
+        <v>Close</v>
       </c>
       <c r="B399" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Invalid</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B400" t="str">
-        <v>Ungültig</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Close</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B402" t="str">
-        <v>Schließen</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Loading XML editor…</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Loading JSON editor…</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B404" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B405" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B406" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>indent</v>
       </c>
       <c r="B408" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Einrückung</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>sort keys</v>
       </c>
       <c r="B409" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Schlüssel sortieren</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B410" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B411" t="str">
-        <v>Einrückung</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B412" t="str">
-        <v>Schlüssel sortieren</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B413" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B410"/>
+  <dimension ref="A1:B411"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,3285 +413,3293 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Round-Trip (PRMG)</v>
+        <v>{pct}% of samples were out of range and were clamped.</v>
       </c>
       <c r="B2" t="str">
-        <v>Rundlauf (PRMG)</v>
+        <v>{pct} % der Abtastwerte lagen außerhalb des Bereichs und wurden begrenzt.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B3" t="str">
-        <v>Rundlauf über den Gerätewürfel des Profils, entsprechend dem Referenzwerkzeug iccRoundTrip. Rundlauf 1 ist der Fehler Gerät→PCS→Gerät (ΔE*ab); Rundlauf 2 misst die Stabilität des PCS-Rundlaufs. Das PRMG-Histogramm zeigt die Interoperabilität gegenüber dem Perceptual Reference Medium Gamut.</v>
+        <v>Rundlauf (PRMG)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Use MPE (color) tags</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B4" t="str">
-        <v>MPE-(Farb-)Tags verwenden</v>
+        <v>Rundlauf über den Gerätewürfel des Profils, entsprechend dem Referenzwerkzeug iccRoundTrip. Rundlauf 1 ist der Fehler Gerät→PCS→Gerät (ΔE*ab); Rundlauf 2 misst die Stabilität des PCS-Rundlaufs. Das PRMG-Histogramm zeigt die Interoperabilität gegenüber dem Perceptual Reference Medium Gamut.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B5" t="str">
-        <v>Für dieses Profil ist kein Rundlauf möglich – es fehlen die dafür nötigen Gerät↔PCS-Transformationen (z. B. ein Einweg- oder abstraktes Profil).</v>
+        <v>MPE-(Farb-)Tags verwenden</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B6" t="str">
-        <v>Rundlauf übersprungen: Der Gerätefarbraum ist zu groß für die Auswertung (zu viele Abtastwerte).</v>
+        <v>Für dieses Profil ist kein Rundlauf möglich – es fehlen die dafür nötigen Gerät↔PCS-Transformationen (z. B. ein Einweg- oder abstraktes Profil).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Metric</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B7" t="str">
-        <v>Metrik</v>
+        <v>Rundlauf übersprungen: Der Gerätefarbraum ist zu groß für die Auswertung (zu viele Abtastwerte).</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Round Trip 1</v>
+        <v>Metric</v>
       </c>
       <c r="B8" t="str">
-        <v>Rundlauf 1</v>
+        <v>Metrik</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Round Trip 2</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B9" t="str">
-        <v>Rundlauf 2</v>
+        <v>Rundlauf 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>device → PCS → device</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B10" t="str">
-        <v>Gerät → PCS → Gerät</v>
+        <v>Rundlauf 2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>PCS round-trip stability</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B11" t="str">
-        <v>Stabilität des PCS-Rundlaufs</v>
+        <v>Gerät → PCS → Gerät</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Min ΔE</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B12" t="str">
-        <v>Min ΔE</v>
+        <v>Stabilität des PCS-Rundlaufs</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Mean ΔE</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>Mittel ΔE</v>
+        <v>Min ΔE</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Max ΔE</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>Max ΔE</v>
+        <v>Mittel ΔE</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Worst L, a, b</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B15" t="str">
-        <v>Schlechteste L, a, b</v>
+        <v>Max ΔE</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Specified gamut</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B16" t="str">
-        <v>Angegebener Gamut</v>
+        <v>Schlechteste L, a, b</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Angegebener Gamut</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Not specified</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B18" t="str">
-        <v>Nicht angegeben</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not evaluated</v>
+        <v>Not specified</v>
       </c>
       <c r="B19" t="str">
-        <v>Nicht ausgewertet</v>
+        <v>Nicht angegeben</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>PRMG interoperability</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B20" t="str">
-        <v>PRMG-Interoperabilität</v>
+        <v>Nicht ausgewertet</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Round-trip ΔE</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B21" t="str">
-        <v>Rundlauf-ΔE</v>
+        <v>PRMG-Interoperabilität</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Count</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B22" t="str">
-        <v>Anzahl</v>
+        <v>Rundlauf-ΔE</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Share</v>
+        <v>Count</v>
       </c>
       <c r="B23" t="str">
-        <v>Anteil</v>
+        <v>Anzahl</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Total</v>
+        <v>Share</v>
       </c>
       <c r="B24" t="str">
-        <v>Gesamt</v>
+        <v>Anteil</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Total</v>
       </c>
       <c r="B25" t="str">
-        <v>PRMG nicht ausgewertet</v>
+        <v>Gesamt</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B26" t="str">
-        <v>Profilweite Kennzahlen für einen Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und eine Kennzahl für die Rundlauf-Genauigkeit. Wählen Sie den Render-Intent und den Rundlauf-Typ — Tabelle und Histogramm passen sich an.</v>
+        <v>PRMG nicht ausgewertet</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Round-trip type</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B27" t="str">
-        <v>Rundlauf-Typ</v>
+        <v>Profilweite Kennzahlen für einen Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und eine Kennzahl für die Rundlauf-Genauigkeit. Wählen Sie den Render-Intent und den Rundlauf-Typ — Tabelle und Histogramm passen sich an.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>Hat auf diesen Rundlauf-Typ keine Auswirkung</v>
+        <v>Rundlauf-Typ</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B29" t="str">
-        <v>Dieser Rundlauf-Typ ist für dieses Profil nicht verfügbar.</v>
+        <v>Hat auf diesen Rundlauf-Typ keine Auswirkung</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B30" t="str">
-        <v>Verteilung des Rundlauf-ΔE</v>
+        <v>Dieser Rundlauf-Typ ist für dieses Profil nicht verfügbar.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B31" t="str">
-        <v>Keine Rundlauf-Abtastwerte lagen innerhalb des ausgewerteten Bereichs.</v>
+        <v>Verteilung des Rundlauf-ΔE</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Std Dev</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B32" t="str">
-        <v>Std.-Abw.</v>
+        <v>Keine Rundlauf-Abtastwerte lagen innerhalb des ausgewerteten Bereichs.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Relative frequency</v>
+        <v>Std Dev</v>
       </c>
       <c r="B33" t="str">
-        <v>Relative Häufigkeit</v>
+        <v>Std.-Abw.</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cumulative frequency</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>Kumulative Häufigkeit</v>
+        <v>Relative Häufigkeit</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Horizontal scale</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B35" t="str">
-        <v>Horizontale Skala</v>
+        <v>Kumulative Häufigkeit</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Integer ΔE</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B36" t="str">
-        <v>Ganzzahliges ΔE</v>
+        <v>Horizontale Skala</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Auto-scale</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B37" t="str">
-        <v>Auto-Skalierung</v>
+        <v>Ganzzahliges ΔE</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Bins</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B38" t="str">
-        <v>Klassen</v>
+        <v>Auto-Skalierung</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>CLUT Image</v>
+        <v>Bins</v>
       </c>
       <c r="B39" t="str">
-        <v>CLUT-Bild</v>
+        <v>Klassen</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B40" t="str">
-        <v>Die Farbtabelle (CLUT) eines Gerät↔PCS-Transforms, als Kacheln zu einem Bild angeordnet. Wählen Sie die anzuzeigende Render-Intent-Tabelle.</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B41" t="str">
-        <v>Dieses Profil hat keine CLUT-basierten Gerät↔PCS-Tabellen zur Visualisierung.</v>
+        <v>Die Farbtabelle (CLUT) eines Gerät↔PCS-Transforms, als Kacheln zu einem Bild angeordnet. Wählen Sie die anzuzeigende Render-Intent-Tabelle.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Gamut Image</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B42" t="str">
-        <v>Gamut-Bild</v>
+        <v>Dieses Profil hat keine CLUT-basierten Gerät↔PCS-Tabellen zur Visualisierung.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B43" t="str">
-        <v>Die In-/Außerhalb-Gamut-Karte des Gamut-Tags: neutral, wo eine PCS-Farbe reproduzierbar ist, rot, wo sie außerhalb des Gerätegamuts liegt.</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B44" t="str">
-        <v>Dieses Profil hat kein Gamut-Tag zur Visualisierung.</v>
+        <v>Die In-/Außerhalb-Gamut-Karte des Gamut-Tags: neutral, wo eine PCS-Farbe reproduzierbar ist, rot, wo sie außerhalb des Gerätegamuts liegt.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B45" t="str">
-        <v>Vertikale Skala</v>
+        <v>Dieses Profil hat kein Gamut-Tag zur Visualisierung.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>X–Y</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B46" t="str">
-        <v>X–Y</v>
+        <v>Vertikale Skala</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Tone increase</v>
+        <v>X–Y</v>
       </c>
       <c r="B47" t="str">
-        <v>Tonwertzunahme</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B48" t="str">
-        <v>Tonwertzunahme (Ausgang − Eingang)</v>
+        <v>Tonwertzunahme</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Show full dump</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B49" t="str">
-        <v>Vollständige Ausgabe anzeigen</v>
+        <v>Tonwertzunahme (Ausgang − Eingang)</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Output truncated for performance.</v>
+        <v>Show full dump</v>
       </c>
       <c r="B50" t="str">
-        <v>Ausgabe aus Leistungsgründen gekürzt.</v>
+        <v>Vollständige Ausgabe anzeigen</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B51" t="str">
-        <v>In-Gamut-Übersicht (RT0)</v>
+        <v>Ausgabe aus Leistungsgründen gekürzt.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B52" t="str">
-        <v>Inversion + Gamut (RT1)</v>
+        <v>In-Gamut-Übersicht (RT0)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B53" t="str">
-        <v>Reproduzierbarkeit (RT2)</v>
+        <v>Inversion + Gamut (RT1)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PRMG interoperability</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B54" t="str">
-        <v>PRMG-Interoperabilität</v>
+        <v>Reproduzierbarkeit (RT2)</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B55" t="str">
-        <v>iccviz-Übersicht: Ein Gitter aus Gerätewerten wird nach PCS, zurück zum Gerät und erneut nach PCS überführt; ΔE*ab wird zwischen den beiden PCS-Durchläufen gemessen. Eine schnelle In-Gamut-Stabilitätsprüfung.</v>
+        <v>PRMG-Interoperabilität</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B56" t="str">
-        <v>iccRoundTrip Rundlauf 1: ΔE*ab zwischen dem PCS jeder Gerätefarbe und ihrem PCS nach einem Rundlauf Lab → Gerät → Lab. Spiegelt Inversionsgenauigkeit und Gamut-Mapping wider.</v>
+        <v>iccviz-Übersicht: Ein Gitter aus Gerätewerten wird nach PCS, zurück zum Gerät und erneut nach PCS überführt; ΔE*ab wird zwischen den beiden PCS-Durchläufen gemessen. Eine schnelle In-Gamut-Stabilitätsprüfung.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip Rundlauf 2: ΔE*ab zwischen dem ersten und zweiten Rundlauf — wie stabil ein wiederholter PCS-Rundlauf ist (Reproduzierbarkeit, unabhängig vom Gamut-Clipping des ersten Durchlaufs).</v>
+        <v>iccRoundTrip Rundlauf 1: ΔE*ab zwischen dem PCS jeder Gerätefarbe und ihrem PCS nach einem Rundlauf Lab → Gerät → Lab. Spiegelt Inversionsgenauigkeit und Gamut-Mapping wider.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip PRMG: PCS-Farben innerhalb des Perceptual Reference Medium Gamut durchlaufen einen einzelnen Rundlauf (Lab → Gerät → Lab); die ΔE*ab-Verteilung zeigt die profilübergreifende Interoperabilität.</v>
+        <v>iccRoundTrip Rundlauf 2: ΔE*ab zwischen dem ersten und zweiten Rundlauf — wie stabil ein wiederholter PCS-Rundlauf ist (Reproduzierbarkeit, unabhängig vom Gamut-Clipping des ersten Durchlaufs).</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Settings</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B59" t="str">
-        <v>Einstellungen</v>
+        <v>iccRoundTrip PRMG: PCS-Farben innerhalb des Perceptual Reference Medium Gamut durchlaufen einen einzelnen Rundlauf (Lab → Gerät → Lab); die ΔE*ab-Verteilung zeigt die profilübergreifende Interoperabilität.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Display</v>
+        <v>Settings</v>
       </c>
       <c r="B60" t="str">
-        <v>Anzeige</v>
+        <v>Einstellungen</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Background</v>
+        <v>Display</v>
       </c>
       <c r="B61" t="str">
-        <v>Hintergrund</v>
+        <v>Anzeige</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Language</v>
+        <v>Background</v>
       </c>
       <c r="B62" t="str">
-        <v>Sprache</v>
+        <v>Hintergrund</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>System</v>
+        <v>Language</v>
       </c>
       <c r="B63" t="str">
-        <v>System</v>
+        <v>Sprache</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Light</v>
+        <v>System</v>
       </c>
       <c r="B64" t="str">
-        <v>Hell</v>
+        <v>System</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dark</v>
+        <v>Light</v>
       </c>
       <c r="B65" t="str">
-        <v>Dunkel</v>
+        <v>Hell</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>System default</v>
+        <v>Dark</v>
       </c>
       <c r="B66" t="str">
-        <v>Systemstandard</v>
+        <v>Dunkel</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Number format</v>
+        <v>System default</v>
       </c>
       <c r="B67" t="str">
-        <v>Zahlenformat</v>
+        <v>Systemstandard</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Hexadecimal</v>
+        <v>Number format</v>
       </c>
       <c r="B68" t="str">
-        <v>Hexadezimal</v>
+        <v>Zahlenformat</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Decimal</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B69" t="str">
-        <v>Dezimal</v>
+        <v>Hexadezimal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Help</v>
+        <v>Decimal</v>
       </c>
       <c r="B70" t="str">
-        <v>Hilfe</v>
+        <v>Dezimal</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Contact</v>
+        <v>Help</v>
       </c>
       <c r="B71" t="str">
-        <v>Kontakt</v>
+        <v>Hilfe</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>User guide</v>
+        <v>Contact</v>
       </c>
       <c r="B72" t="str">
-        <v>Benutzerhandbuch</v>
+        <v>Kontakt</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Search guide</v>
+        <v>User guide</v>
       </c>
       <c r="B73" t="str">
-        <v>Handbuch durchsuchen</v>
+        <v>Benutzerhandbuch</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search the user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B74" t="str">
-        <v>Benutzerhandbuch durchsuchen</v>
+        <v>Handbuch durchsuchen</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Previous match</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B75" t="str">
-        <v>Vorheriger Treffer</v>
+        <v>Benutzerhandbuch durchsuchen</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Next match</v>
+        <v>Previous match</v>
       </c>
       <c r="B76" t="str">
-        <v>Nächster Treffer</v>
+        <v>Vorheriger Treffer</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Close user guide</v>
+        <v>Next match</v>
       </c>
       <c r="B77" t="str">
-        <v>Handbuch schließen</v>
+        <v>Nächster Treffer</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading…</v>
+        <v>Close user guide</v>
       </c>
       <c r="B78" t="str">
-        <v>Wird geladen…</v>
+        <v>Handbuch schließen</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>Benutzerhandbuch konnte nicht geladen werden.</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>None</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B80" t="str">
-        <v>Keine</v>
+        <v>Benutzerhandbuch konnte nicht geladen werden.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B81" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Keine</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Based on</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B82" t="str">
-        <v>Basierend auf der</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>demo implementation</v>
+        <v>Based on</v>
       </c>
       <c r="B83" t="str">
-        <v>Demo-Implementierung</v>
+        <v>Basierend auf der</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Validating…</v>
+        <v>demo implementation</v>
       </c>
       <c r="B84" t="str">
-        <v>Validierung…</v>
+        <v>Demo-Implementierung</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Save ICC profile</v>
+        <v>Validating…</v>
       </c>
       <c r="B85" t="str">
-        <v>ICC-Profil speichern</v>
+        <v>Validierung…</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B86" t="str">
-        <v>● Geändert — nicht gespeichert</v>
+        <v>ICC-Profil speichern</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B87" t="str">
-        <v>Profile</v>
+        <v>● Geändert — nicht gespeichert</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Show profile pool</v>
+        <v>Profiles</v>
       </c>
       <c r="B88" t="str">
-        <v>Profil-Pool anzeigen</v>
+        <v>Profile</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Collapse</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B89" t="str">
-        <v>Einklappen</v>
+        <v>Profil-Pool anzeigen</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Load Profiles</v>
+        <v>Collapse</v>
       </c>
       <c r="B90" t="str">
-        <v>Profile laden</v>
+        <v>Einklappen</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Remove</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B91" t="str">
-        <v>Entfernen</v>
+        <v>Profile laden</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Remove</v>
       </c>
       <c r="B92" t="str">
-        <v>ICC-Profile hierher ziehen</v>
+        <v>Entfernen</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B93" t="str">
-        <v>oder ein Bild (TIFF/PNG/JPEG), um dessen eingebettetes Profil zu extrahieren — die Dateien bleiben auf Ihrem Gerät.</v>
+        <v>ICC-Profile hierher ziehen</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>New from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B94" t="str">
-        <v>Neu aus .cube</v>
+        <v>oder ein Bild (TIFF/PNG/JPEG), um dessen eingebettetes Profil zu extrahieren — die Dateien bleiben auf Ihrem Gerät.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Sort by name</v>
+        <v>New from .cube</v>
       </c>
       <c r="B95" t="str">
-        <v>Nach Namen sortieren</v>
+        <v>Neu aus .cube</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B96" t="str">
-        <v>A–Z</v>
+        <v>Nach Namen sortieren</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B97" t="str">
-        <v>Neues Profil aus .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B98" t="str">
-        <v>Erstellen Sie einen ICC-DeviceLink aus einer Adobe/Resolve-.cube-3D-LUT. Das Ergebnis wird Ihrem Pool hinzugefügt und heruntergeladen.</v>
+        <v>Neues Profil aus .cube</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B99" t="str">
-        <v>.cube-Datei wählen</v>
+        <v>Erstellen Sie einen ICC-DeviceLink aus einer Adobe/Resolve-.cube-3D-LUT. Das Ergebnis wird Ihrem Pool hinzugefügt und heruntergeladen.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B100" t="str">
+        <v>.cube-Datei wählen</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B101" t="str">
         <v>oder hierher ziehen oder unten einfügen</v>
       </c>
     </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101" t="str" xml:space="preserve">
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B101" t="str" xml:space="preserve">
+      <c r="B102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Abbrechen</v>
-      </c>
-    </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B103" t="str">
-        <v>DeviceLink erstellen</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B104" t="str">
-        <v>Wird erstellt…</v>
+        <v>DeviceLink erstellen</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B105" t="str">
-        <v>Diese Datei konnte nicht gelesen werden.</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B106" t="str">
-        <v>Profil</v>
+        <v>Diese Datei konnte nicht gelesen werden.</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B107" t="str">
-        <v>Vergleichen</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B108" t="str">
-        <v>Verknüpfen</v>
+        <v>Vergleichen</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B109" t="str">
-        <v>Spektral</v>
+        <v>Verknüpfen</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B110" t="str">
-        <v>Ziehen Sie Profile aus dem Pool auf diesen Tab</v>
+        <v>Spektral</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B111" t="str">
-        <v>Entfernen</v>
+        <v>Ziehen Sie Profile aus dem Pool auf diesen Tab</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B112" t="str">
-        <v>Kein Profil ausgewählt</v>
+        <v>Entfernen</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B113" t="str">
-        <v>Ziehen Sie ein Profil aus dem Pool auf den Profil-Tab, um es zu untersuchen.</v>
+        <v>Kein Profil ausgewählt</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B114" t="str">
-        <v>Noch nichts zu vergleichen</v>
+        <v>Ziehen Sie ein Profil aus dem Pool auf den Profil-Tab, um es zu untersuchen.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B115" t="str">
-        <v>Ziehen Sie ein oder mehrere Profile auf den Vergleichen-Tab.</v>
+        <v>Noch nichts zu vergleichen</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B116" t="str">
-        <v>Gamut-Vergleich</v>
+        <v>Ziehen Sie ein oder mehrere Profile auf den Vergleichen-Tab.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B117" t="str">
-        <v>3D-Gamut- und 2D-Schnittansichten kommen hierher. Gesammelt:</v>
+        <v>Gamut-Vergleich</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B118" t="str">
-        <v>Render-Intent</v>
+        <v>3D-Gamut- und 2D-Schnittansichten kommen hierher. Gesammelt:</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B119" t="str">
-        <v>Hülle</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B120" t="str">
-        <v>Drahtgitter</v>
+        <v>Hülle</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B121" t="str">
-        <v>Achsenwerte</v>
+        <v>Drahtgitter</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B122" t="str">
-        <v>Deckkraft</v>
+        <v>Achsenwerte</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>Farbe</v>
+        <v>Deckkraft</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>Einfarbig</v>
+        <v>Farbe</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>Nach Wert</v>
+        <v>Einfarbig</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>Nach Farbton</v>
+        <v>Nach Wert</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>Rotation</v>
+        <v>Nach Farbton</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>Drehteller</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>Orbit</v>
+        <v>Drehteller</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>Ziehgeschwindigkeit</v>
+        <v>Orbit</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>Rollen</v>
+        <v>Ziehgeschwindigkeit</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>Rollgeschwindigkeit</v>
+        <v>Rollen</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Gamut wird erstellt…</v>
+        <v>Rollgeschwindigkeit</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>kein Gamut</v>
+        <v>Gamut wird erstellt…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>Ein-/ausblenden</v>
+        <v>kein Gamut</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>3D-Gamut-Hülle</v>
+        <v>Ein-/ausblenden</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>2D-Gamut-Schnitt</v>
+        <v>3D-Gamut-Hülle</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>Ebene</v>
+        <v>2D-Gamut-Schnitt</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>L*</v>
+        <v>Ebene</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>Keines der ausgewählten Profile hat ein Gerät→PCS-Transform, aus dem sich ein Gamut ableiten lässt.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>Verknüpfung</v>
+        <v>Keines der ausgewählten Profile hat ein Gerät→PCS-Transform, aus dem sich ein Gamut ableiten lässt.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>DeviceLink-Erzeugung und Transformationen über mehrere Profile folgen in einer späteren Phase.</v>
+        <v>Verknüpfung</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>Weitere Link-Ersteller (DeviceLink, …) folgen hier.</v>
+        <v>DeviceLink-Erzeugung und Transformationen über mehrere Profile folgen in einer späteren Phase.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>V4-Display-Ersteller</v>
+        <v>Weitere Link-Ersteller (DeviceLink, …) folgen hier.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B147" t="str">
-        <v>Ziehen Sie ein V5-RGB-Display- und ein V5-Beobachterprofil hierher, um ein V4-Displayprofil zu erstellen.</v>
+        <v>V4-Display-Ersteller</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>V5-RGB-Display</v>
+        <v>Ziehen Sie ein V5-RGB-Display- und ein V5-Beobachterprofil hierher, um ein V4-Displayprofil zu erstellen.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>Displayprofil ablegen</v>
+        <v>V5-RGB-Display</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>V5-Beobachter (PCC)</v>
+        <v>Displayprofil ablegen</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>Beobachterprofil ablegen</v>
+        <v>V5-Beobachter (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>Ein Profil, das weder ein V5-RGB-Display noch ein Beobachter ist, wurde ignoriert.</v>
+        <v>Beobachterprofil ablegen</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>V4-Displayprofil erstellen</v>
+        <v>Ein Profil, das weder ein V5-RGB-Display noch ein Beobachter ist, wurde ignoriert.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Profilname</v>
+        <v>V4-Displayprofil erstellen</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>Erstellen</v>
+        <v>Profilname</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>Wird erstellt…</v>
+        <v>Erstellen</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>„{name}“ erstellt — dem Pool und diesem Tab hinzugefügt.</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>Link-Pipeline</v>
+        <v>„{name}“ erstellt — dem Pool und diesem Tab hinzugefügt.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B159" t="str">
-        <v>Erstellen Sie eine Kette aus Profilen und erzeugen Sie daraus einen DeviceLink, transformieren Sie ein Bild oder einen Farbdatensatz.</v>
+        <v>Link-Pipeline</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B160" t="str">
-        <v>Fertig</v>
+        <v>Erstellen Sie eine Kette aus Profilen und erzeugen Sie daraus einen DeviceLink, transformieren Sie ein Bild oder einen Farbdatensatz.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B161" t="str">
-        <v>Bild zum Transformieren ablegen (TIFF/PNG/JPEG)</v>
+        <v>Fertig</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B162" t="str">
-        <v>Bild wird geprüft…</v>
+        <v>Bild zum Transformieren ablegen (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B163" t="str">
-        <v>Kein unterstütztes Bildformat (TIFF, PNG oder JPEG).</v>
+        <v>Bild wird geprüft…</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B164" t="str">
-        <v>Bild zu groß ({mp} MP; Grenzwert {max} MP).</v>
+        <v>Kein unterstütztes Bildformat (TIFF, PNG oder JPEG).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B165" t="str">
-        <v>Bild transformieren</v>
+        <v>Bild zu groß ({mp} MP; Grenzwert {max} MP).</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B166" t="str">
-        <v>Wird transformiert…</v>
+        <v>Bild transformieren</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B167" t="str">
-        <v>Profile ablegen, um die Kette zu starten</v>
+        <v>Wird transformiert…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B168" t="str">
-        <v>entfernt</v>
+        <v>Profile ablegen, um die Kette zu starten</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B169" t="str">
-        <v>Nach vorne verschieben</v>
+        <v>entfernt</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B170" t="str">
-        <v>Nach hinten verschieben</v>
+        <v>Nach vorne verschieben</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B171" t="str">
-        <v>Nach oben verschieben</v>
+        <v>Nach hinten verschieben</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B172" t="str">
-        <v>Nach unten verschieben</v>
+        <v>Nach oben verschieben</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B173" t="str">
-        <v>Rendering-Priorität (alle)</v>
+        <v>Nach unten verschieben</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B174" t="str">
-        <v>Rendering-Priorität für diese Transformation</v>
+        <v>Rendering-Priorität (alle)</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B175" t="str">
-        <v>Die Transformationen verwenden unterschiedliche Rendering-Prioritäten</v>
+        <v>Rendering-Priorität für diese Transformation</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B176" t="str">
-        <v>Kettenrichtung umkehren (kehrt die erste Transformation um und wirkt sich auf die gesamte Kette aus)</v>
+        <v>Die Transformationen verwenden unterschiedliche Rendering-Prioritäten</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B177" t="str">
-        <v>Ein verkettetes Profil wurde aus dem Pool entfernt — entfernen Sie es, um fortzufahren.</v>
+        <v>Kettenrichtung umkehren (kehrt die erste Transformation um und wirkt sich auf die gesamte Kette aus)</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B178" t="str">
-        <v>Kette</v>
+        <v>Ein verkettetes Profil wurde aus dem Pool entfernt — entfernen Sie es, um fortzufahren.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B179" t="str">
-        <v>Die Kette konnte nicht analysiert werden.</v>
+        <v>Kette</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B180" t="str">
-        <v>Kette wird geprüft…</v>
+        <v>Die Kette konnte nicht analysiert werden.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B181" t="str">
-        <v>Die Kette verbindet sich nicht ({detail}).</v>
+        <v>Kette wird geprüft…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>Profil {n} verbindet sich nicht mit der vorherigen Stufe ({detail}).</v>
+        <v>Die Kette verbindet sich nicht ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B183" t="str">
-        <v>Beheben Sie die Kette, bevor Sie Bilder verarbeiten</v>
+        <v>Profil {n} verbindet sich nicht mit der vorherigen Stufe ({detail}).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B184" t="str">
-        <v>Leeren</v>
+        <v>Beheben Sie die Kette, bevor Sie Bilder verarbeiten</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B185" t="str">
-        <v>DeviceLink erstellen</v>
+        <v>Leeren</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B186" t="str">
-        <v>DeviceLink-Name</v>
+        <v>DeviceLink erstellen</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B187" t="str">
-        <v>Wird erstellt…</v>
+        <v>DeviceLink-Name</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B188" t="str">
-        <v>„{name}“ erstellt — zum Pool und zu diesem Tab hinzugefügt.</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B189" t="str">
-        <v>{src}-Bilder ablegen, um sie in {dst} zu konvertieren — Ergebnisse werden heruntergeladen, nichts wird gespeichert.</v>
+        <v>„{name}“ erstellt — zum Pool und zu diesem Tab hinzugefügt.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B190" t="str">
-        <v>Erstellen Sie eine Kette, um Bilder zu verarbeiten</v>
+        <v>{src}-Bilder ablegen, um sie in {dst} zu konvertieren — Ergebnisse werden heruntergeladen, nichts wird gespeichert.</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B191" t="str">
-        <v>Diese Kette beginnt und endet nicht in einem Bildfarbraum</v>
+        <v>Erstellen Sie eine Kette, um Bilder zu verarbeiten</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B192" t="str">
-        <v>Transformiertes Bild gespeichert.</v>
+        <v>Diese Kette beginnt und endet nicht in einem Bildfarbraum</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B193" t="str">
-        <v>Farbdatensatz ablegen (CGATS/CSV/CxF/JSON)</v>
+        <v>Transformiertes Bild gespeichert.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B194" t="str">
-        <v>Diese Datei konnte nicht gelesen werden.</v>
+        <v>Farbdatensatz ablegen (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B195" t="str">
-        <v>Datendatei zu groß.</v>
+        <v>Diese Datei konnte nicht gelesen werden.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B196" t="str">
-        <v>Daten transformieren</v>
+        <v>Datendatei zu groß.</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B197" t="str">
-        <v>Wird transformiert…</v>
+        <v>Daten transformieren</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B198" t="str">
-        <v>Bevorzugen</v>
+        <v>Wird transformiert…</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B199" t="str">
-        <v>Beobachter</v>
+        <v>Bevorzugen</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B200" t="str">
-        <v>Lichtart</v>
+        <v>Beobachter</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B201" t="str">
-        <v>Bedingung</v>
+        <v>Lichtart</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B202" t="str">
-        <v>{n} Duplikat(e) filtern</v>
+        <v>Bedingung</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B203" t="str">
-        <v>Median</v>
+        <v>{n} Duplikat(e) filtern</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B204" t="str">
-        <v>Mittelwert</v>
+        <v>Median</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B205" t="str">
-        <v>Farbfelder</v>
+        <v>Mittelwert</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B206" t="str">
-        <v>{n} Duplikate</v>
+        <v>Farbfelder</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B207" t="str">
-        <v>Transformationsergebnis</v>
+        <v>{n} Duplikate</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B208" t="str">
-        <v>{src} → {dst} · {n} Farbfelder</v>
+        <v>Transformationsergebnis</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B209" t="str">
-        <v>Zeigt die ersten {shown} von {total} — Speichern schreibt alle.</v>
+        <v>{src} → {dst} · {n} Farbfelder</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B210" t="str">
-        <v>Speichern unter</v>
+        <v>Zeigt die ersten {shown} von {total} — Speichern schreibt alle.</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B211" t="str">
-        <v>Speichern</v>
+        <v>Speichern unter</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B212" t="str">
-        <v>Transformation umkehren</v>
+        <v>Speichern</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B213" t="str">
-        <v>Wird umgekehrt…</v>
+        <v>Transformation umkehren</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B214" t="str">
-        <v>Umkehren</v>
+        <v>Wird umgekehrt…</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B215" t="str">
-        <v>letzte Stufe</v>
+        <v>Umkehren</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B216" t="str">
-        <v>erste Stufe</v>
+        <v>letzte Stufe</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B217" t="str">
-        <v>Daten in {in} → Suche {out}</v>
+        <v>erste Stufe</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B218" t="str">
-        <v>Die Umkehrung benötigt eine Kette aus 2–3 Profilen</v>
+        <v>Daten in {in} → Suche {out}</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B219" t="str">
-        <v>Der Datensatz muss in {in} vorliegen; die inverse Suche liefert {out} sowie einen Invertierbarkeits-Kostenwert pro Farbfeld.</v>
+        <v>Die Umkehrung benötigt eine Kette aus 2–3 Profilen</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B220" t="str">
-        <v>ΔE-Kosten</v>
+        <v>Der Datensatz muss in {in} vorliegen; die inverse Suche liefert {out} sowie einen Invertierbarkeits-Kostenwert pro Farbfeld.</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B221" t="str">
-        <v>Dieses Bild enthält ein eingebettetes ICC-Profil.</v>
+        <v>ΔE-Kosten</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B222" t="str">
-        <v>Extrahieren &amp; zur Kette hinzufügen</v>
+        <v>Dieses Bild enthält ein eingebettetes ICC-Profil.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B223" t="str">
-        <v>Wird extrahiert…</v>
+        <v>Extrahieren &amp; zur Kette hinzufügen</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B224" t="str">
-        <v>Verwerfen</v>
+        <v>Wird extrahiert…</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B225" t="str">
-        <v>Eingebettetes Profil extrahiert — zum Pool hinzugefügt und an den Anfang der Kette gesetzt.</v>
+        <v>Verwerfen</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B226" t="str">
-        <v>Bildausgabeoptionen</v>
+        <v>Eingebettetes Profil extrahiert — zum Pool hinzugefügt und an den Anfang der Kette gesetzt.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B227" t="str">
-        <v>Kodierung</v>
+        <v>Bildausgabeoptionen</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B228" t="str">
-        <v>Wie Quelle</v>
+        <v>Kodierung</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B229" t="str">
-        <v>8 Bit</v>
+        <v>Wie Quelle</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>16 Bit</v>
+        <v>8 Bit</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B231" t="str">
-        <v>Gleitkomma (32 Bit)</v>
+        <v>16 Bit</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B232" t="str">
-        <v>Komprimierung</v>
+        <v>Gleitkomma (32 Bit)</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B233" t="str">
-        <v>Keine</v>
+        <v>Komprimierung</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B234" t="str">
-        <v>Planar</v>
+        <v>Keine</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B235" t="str">
-        <v>Verschachtelt</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B236" t="str">
-        <v>Getrennt</v>
+        <v>Verschachtelt</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B237" t="str">
-        <v>CMM-Interpolation</v>
+        <v>Getrennt</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B238" t="str">
-        <v>Tetraedrisch</v>
+        <v>CMM-Interpolation</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B239" t="str">
-        <v>Linear</v>
+        <v>Tetraedrisch</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B240" t="str">
-        <v>ICC-Profil einbetten</v>
+        <v>Linear</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B241" t="str">
-        <v>Kodierung, Komprimierung und Planaranordnung bestimmen das gespeicherte TIFF. Die RGB-/Gray-Ausgabe bleibt PNG, sofern keine TIFF-spezifische Option (Gleitkomma, LZW/ZIP, Getrennt) gewählt wird.</v>
+        <v>ICC-Profil einbetten</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B242" t="str">
-        <v>Spektrales TIFF zusammenstellen</v>
+        <v>Kodierung, Komprimierung und Planaranordnung bestimmen das gespeicherte TIFF. Die RGB-/Gray-Ausgabe bleibt PNG, sofern keine TIFF-spezifische Option (Gleitkomma, LZW/ZIP, Getrennt) gewählt wird.</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B243" t="str">
-        <v>Einkanalige Spektralbilder in Kanalreihenfolge ablegen und zu einem mehrkanaligen TIFF zusammenfügen.</v>
+        <v>Spektrales TIFF zusammenstellen</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B244" t="str">
-        <v>Spektralbilder hier ablegen (oder klicken, um auszuwählen)</v>
+        <v>Einkanalige Spektralbilder in Kanalreihenfolge ablegen und zu einem mehrkanaligen TIFF zusammenfügen.</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B245" t="str">
-        <v>Kan</v>
+        <v>Spektralbilder hier ablegen (oder klicken, um auszuwählen)</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B246" t="str">
-        <v>Zusammenfügen &amp; Speichern</v>
+        <v>Kan</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B247" t="str">
-        <v>Wird zusammengefügt…</v>
+        <v>Zusammenfügen &amp; Speichern</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B248" t="str">
-        <v>{n} Kanäle zusammengefügt.</v>
+        <v>Wird zusammengefügt…</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B249" t="str">
-        <v>Keine dieser Dateien sieht wie ein Bild aus (TIFF, PNG oder JPEG).</v>
+        <v>{n} Kanäle zusammengefügt.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B250" t="str">
-        <v>Abbrechen</v>
+        <v>Keine dieser Dateien sieht wie ein Bild aus (TIFF, PNG oder JPEG).</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B251" t="str">
-        <v>{n} Datei(en) nicht geladen</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B252" t="str">
-        <v>Diese Dateien sind keine ICC-Profile und wurden daher nicht zum Pool hinzugefügt:</v>
+        <v>{n} Datei(en) nicht geladen</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B253" t="str">
-        <v>OK</v>
+        <v>Diese Dateien sind keine ICC-Profile und wurden daher nicht zum Pool hinzugefügt:</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B254" t="str">
-        <v>ICC-Profil hierher ziehen</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B255" t="str">
-        <v>oder</v>
+        <v>ICC-Profil hierher ziehen</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B256" t="str">
-        <v>Datei wählen</v>
+        <v>oder</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B257" t="str">
-        <v>.icc- und .icm-Dateien</v>
+        <v>Datei wählen</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B258" t="str">
-        <v>Header</v>
+        <v>.icc- und .icm-Dateien</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B259" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B260" t="str">
-        <v>Validierung</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B261" t="str">
-        <v>Analyse</v>
+        <v>Validierung</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B262" t="str">
-        <v>Neutralachsen-Einfärbung</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B263" t="str">
-        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
+        <v>Neutralachsen-Einfärbung</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B264" t="str">
-        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B265" t="str">
-        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
+        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B266" t="str">
-        <v>Render-Intent</v>
+        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B267" t="str">
-        <v>% Farbe</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Perceptual</v>
+        <v>% ink</v>
       </c>
       <c r="B268" t="str">
-        <v>Perzeptiv</v>
+        <v>% Farbe</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B269" t="str">
-        <v>Relativ farbmetrisch</v>
+        <v>Perzeptiv</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B270" t="str">
-        <v>Sättigung</v>
+        <v>Relativ farbmetrisch</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B271" t="str">
-        <v>Absolut farbmetrisch</v>
+        <v>Sättigung</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>Profilstatistik</v>
+        <v>Absolut farbmetrisch</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B273" t="str">
-        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B274" t="str">
-        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
+        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B275" t="str">
-        <v>Render-Intent</v>
+        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B276" t="str">
-        <v>Gamut-Volumen (ΔE³)</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B277" t="str">
-        <v>Roundtrip-ΔE</v>
+        <v>Gamut-Volumen (ΔE³)</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B278" t="str">
-        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
+        <v>Roundtrip-ΔE</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B279" t="str">
-        <v>Mittel</v>
+        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B280" t="str">
-        <v>P90</v>
+        <v>Mittel</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B281" t="str">
-        <v>Max.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B282" t="str">
-        <v>Analyse läuft…</v>
+        <v>Max.</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B283" t="str">
-        <v>Analyse</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B284" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B285" t="str">
-        <v>Diagramm</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B286" t="str">
-        <v>Rohausgabe</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B287" t="str">
-        <v>XML</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B289" t="str">
-        <v>Kurven</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B290" t="str">
-        <v>Eingangskurven</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B291" t="str">
-        <v>Ausgangskurven</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B292" t="str">
-        <v>CLUT-Bild</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B293" t="str">
-        <v>Gamut-Bild</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B294" t="str">
-        <v>Chromazität</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B295" t="str">
-        <v>Streudiagramm</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B296" t="str">
-        <v>Tonwertkurve</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B297" t="str">
-        <v>Kurventabelle</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B298" t="str">
-        <v>Tabellen</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B299" t="str">
-        <v>Daten</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B300" t="str">
-        <v>Auswerten</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B301" t="str">
-        <v>Wird geladen…</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B302" t="str">
-        <v>Eingang</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B303" t="str">
-        <v>Ausgang</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B304" t="str">
-        <v>Gleitkomma</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B305" t="str">
-        <v>Gitterpunkt</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B306" t="str">
-        <v>Normalisiert</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B307" t="str">
-        <v>Lesbar</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B308" t="str">
-        <v>Gerät → PCS</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B309" t="str">
-        <v>PCS → Gerät</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B310" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B311" t="str">
-        <v>Wird geladen…</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B312" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B313" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B314" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B315" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B316" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B317" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B318" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B319" t="str">
-        <v>Sicherheit</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B320" t="str">
-        <v>Konformität</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B321" t="str">
-        <v>Qualität</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B322" t="str">
-        <v>BERICHT</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B323" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B324" t="str">
-        <v>Prüfungen</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B325" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B326" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B327" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B328" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B329" t="str">
-        <v>Abonnieren</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B330" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B331" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B332" t="str">
-        <v>Schließen</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B333" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B334" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B335" t="str">
-        <v>sie@example.com</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B336" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B337" t="str">
-        <v>(optional)</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B338" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B339" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B340" t="str">
-        <v>Abbrechen</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B341" t="str">
-        <v>Abonnieren</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B342" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B343" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B344" t="str">
-        <v>Schließen</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B345" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B346" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B347" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B348" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B351" t="str">
-        <v>Fehler:</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B352" t="str">
-        <v>In XML konvertieren</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B353" t="str">
-        <v>In JSON konvertieren</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B354" t="str">
-        <v>In ICC konvertieren</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B355" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B356" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B357" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B358" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B359" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B360" t="str">
-        <v>Profil-ID</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B361" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B362" t="str">
-        <v>Tag-Name</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B363" t="str">
-        <v>ID</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B364" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B365" t="str">
-        <v>Größe</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B366" t="str">
-        <v>Auffüllung</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B367" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B368" t="str">
-        <v>Typ</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B369" t="str">
-        <v>Array von {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B370" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B371" t="str">
-        <v>Bytes</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B372" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B373" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B374" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B375" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B376" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B377" t="str">
-        <v>Profil ist gültig</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B378" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B379" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B380" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B381" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B382" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B383" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B384" t="str">
-        <v>Gültig</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B385" t="str">
-        <v>Warnung</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B386" t="str">
-        <v>Fehler</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B387" t="str">
-        <v>Unbekannt</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B388" t="str">
-        <v>Bestanden</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B389" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B390" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B391" t="str">
-        <v>Validierungsdetail</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B392" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B393" t="str">
-        <v>Feld</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B394" t="str">
-        <v>Aktueller Wert</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B395" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B396" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B397" t="str">
-        <v>Ungültig</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B398" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B399" t="str">
-        <v>Schließen</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B402" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B404" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B405" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B406" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B408" t="str">
-        <v>Einrückung</v>
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B409" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Einrückung</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B410" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B410" t="str">
+      <c r="B411" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B411"/>
+  <dimension ref="A1:B445"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2555,1151 +2555,1423 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Perceptual</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B269" t="str">
-        <v>Perzeptiv</v>
+        <v>L* Ausgabe (Tonwert)</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B270" t="str">
-        <v>Relativ farbmetrisch</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Saturation</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B271" t="str">
-        <v>Sättigung</v>
+        <v>Kolorimetrie der Extremwerte</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B272" t="str">
-        <v>Absolut farbmetrisch</v>
+        <v>Die Enden des Wiedergabeumfangs des Profils: das Weiß des Bedruckstoffs, das dunkelste Schwarz, das es druckt, der Farbauftrag, den dieses Schwarz kostet, und der Punkt, an dem jeder Farbton am gesättigtsten ist.</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Profile Statistics</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B273" t="str">
-        <v>Profilstatistik</v>
+        <v>Der Weißpunkt ist die Farbe bei null Farbmittel — der blanke Bedruckstoff. Der Schwarzpunkt ergibt sich, indem PCS-Schwarz (L*=0, a*=b*=0) durch die gewählte B2A-Tabelle geführt wird, um den Farbauftrag zu erhalten, den das Profil für Schwarz wählt, und dieser Farbauftrag anschließend über A2B1 zurückgelesen wird. Der Gesamtfarbauftrag (TAC) ist die Summe dieses Farbauftrags. Die absolute Kolorimetrie zeigt die Eigenfarbe des Bedruckstoffs; die relative bezieht sie auf ein perfektes Weiß.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative</v>
       </c>
       <c r="B274" t="str">
-        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
+        <v>Relativ</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Absolute</v>
       </c>
       <c r="B275" t="str">
-        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
+        <v>Absolut</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Rendering intent</v>
+        <v>White point</v>
       </c>
       <c r="B276" t="str">
-        <v>Render-Intent</v>
+        <v>Weißpunkt</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Black point</v>
       </c>
       <c r="B277" t="str">
-        <v>Gamut-Volumen (ΔE³)</v>
+        <v>Schwarzpunkt</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B278" t="str">
-        <v>Roundtrip-ΔE</v>
+        <v>Farbauftrag am Schwarzpunkt</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>TAC</v>
       </c>
       <c r="B279" t="str">
-        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>mean</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B280" t="str">
-        <v>Mittel</v>
+        <v>Dieses Profil hat kein Medien-Weißpunkt-Tag, daher ist die absolute Kolorimetrie nicht verfügbar.</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>P90</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B281" t="str">
-        <v>P90</v>
+        <v>Die Kolorimetrie der Extremwerte ist nur für Ausgabeprofile (Drucker) verfügbar — sie setzt voraus, dass null Farbmittel dem blanken Bedruckstoff entspricht.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>max</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B282" t="str">
-        <v>Max.</v>
+        <v>Vollton gegenüber maximalem Chroma</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysing…</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B283" t="str">
-        <v>Analyse läuft…</v>
+        <v>Wo jede Farbecke landet und der farbigste Punkt auf dem Weg dorthin. Gemessen über A2B1, daher ändern sich diese Zeilen nicht mit dem Render-Intent oben. Bei einem gutmütigen Profil stimmen beide Zeilen überein; wird das maximale Chroma vor dem Vollton erreicht, verdunkelt die Farbe darüber hinaus nur noch.</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Analysis</v>
+        <v>Hue</v>
       </c>
       <c r="B284" t="str">
-        <v>Analyse</v>
+        <v>Farbton</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Full tone</v>
       </c>
       <c r="B285" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v>Vollton</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Plot</v>
+        <v>Max C*</v>
       </c>
       <c r="B286" t="str">
-        <v>Diagramm</v>
+        <v>Max. C*</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Raw Output</v>
+        <v>At ink</v>
       </c>
       <c r="B287" t="str">
-        <v>Rohausgabe</v>
+        <v>Bei Farbauftrag</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>XML</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B288" t="str">
-        <v>XML</v>
+        <v>Das maximale Chroma wird vor dem Vollton erreicht — Farbe darüber hinaus verdunkelt nur.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>JSON</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B289" t="str">
-        <v>JSON</v>
+        <v>Farbverbrauch in den Tiefen</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Curves</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B290" t="str">
-        <v>Kurven</v>
+        <v>Vier gerade Pfade durch die a*b*-Ebene bei einer konstanten, bewusst dunklen Helligkeit, geführt durch die gewählte B2A-Tabelle. Alle Abtastwerte teilen dieselbe L*, sodass jeder abrupte Sprung oder jede Umkehr eines Farbmittels allein aus der Behandlung von Farbton und Chroma stammt — die Signatur eines Gamut-Mapping-Artefakts in den Tiefen.</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Input curves</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B291" t="str">
-        <v>Eingangskurven</v>
+        <v>Der Farbverbrauch in den Tiefen ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Output curves</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B292" t="str">
-        <v>Ausgangskurven</v>
+        <v>Ebene konstanter L*</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>CLUT image</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B293" t="str">
-        <v>CLUT-Bild</v>
+        <v>schwarzpunktkompensiert ab</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Gamut image</v>
+        <v>Position along path</v>
       </c>
       <c r="B294" t="str">
-        <v>Gamut-Bild</v>
+        <v>Position entlang des Pfades</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Chromaticity</v>
+        <v>Path</v>
       </c>
       <c r="B295" t="str">
-        <v>Chromazität</v>
+        <v>Pfad</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Scatter plot</v>
+        <v>Cyan</v>
       </c>
       <c r="B296" t="str">
-        <v>Streudiagramm</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Tone response curve</v>
+        <v>Magenta</v>
       </c>
       <c r="B297" t="str">
-        <v>Tonwertkurve</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Curve table</v>
+        <v>Yellow</v>
       </c>
       <c r="B298" t="str">
-        <v>Kurventabelle</v>
+        <v>Gelb</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tables</v>
+        <v>Red</v>
       </c>
       <c r="B299" t="str">
-        <v>Tabellen</v>
+        <v>Rot</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Data</v>
+        <v>Green</v>
       </c>
       <c r="B300" t="str">
-        <v>Daten</v>
+        <v>Grün</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Evaluate</v>
+        <v>Blue</v>
       </c>
       <c r="B301" t="str">
-        <v>Auswerten</v>
+        <v>Blau</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Loading…</v>
+        <v>Black</v>
       </c>
       <c r="B302" t="str">
-        <v>Wird geladen…</v>
+        <v>Schwarz</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Input</v>
+        <v>Perceptual</v>
       </c>
       <c r="B303" t="str">
-        <v>Eingang</v>
+        <v>Perzeptiv</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B304" t="str">
-        <v>Ausgang</v>
+        <v>Relativ farbmetrisch</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Floating point</v>
+        <v>Saturation</v>
       </c>
       <c r="B305" t="str">
-        <v>Gleitkomma</v>
+        <v>Sättigung</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Grid point</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B306" t="str">
-        <v>Gitterpunkt</v>
+        <v>Absolut farbmetrisch</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Normalized</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B307" t="str">
-        <v>Normalisiert</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Human</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B308" t="str">
-        <v>Lesbar</v>
+        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Device → PCS</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B309" t="str">
-        <v>Gerät → PCS</v>
+        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>PCS → Device</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B310" t="str">
-        <v>PCS → Gerät</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B311" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>Gamut-Volumen (ΔE³)</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B312" t="str">
-        <v>Wird geladen…</v>
+        <v>Roundtrip-ΔE</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B313" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Invalid profile URL:</v>
+        <v>mean</v>
       </c>
       <c r="B314" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Mittel</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>P90</v>
       </c>
       <c r="B315" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>max</v>
       </c>
       <c r="B316" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>Max.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Analysing…</v>
       </c>
       <c r="B317" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Analysis</v>
       </c>
       <c r="B318" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B319" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Security</v>
+        <v>Plot</v>
       </c>
       <c r="B320" t="str">
-        <v>Sicherheit</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Conformance</v>
+        <v>Raw Output</v>
       </c>
       <c r="B321" t="str">
-        <v>Konformität</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Quality</v>
+        <v>XML</v>
       </c>
       <c r="B322" t="str">
-        <v>Qualität</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>REPORT</v>
+        <v>JSON</v>
       </c>
       <c r="B323" t="str">
-        <v>BERICHT</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>FAIL</v>
+        <v>Curves</v>
       </c>
       <c r="B324" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>checks</v>
+        <v>Input curves</v>
       </c>
       <c r="B325" t="str">
-        <v>Prüfungen</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Output curves</v>
       </c>
       <c r="B326" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>CLUT image</v>
       </c>
       <c r="B327" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Gamut image</v>
       </c>
       <c r="B328" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Powered by {lib}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B329" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Subscribe</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B330" t="str">
-        <v>Abonnieren</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B331" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Get notified about new releases</v>
+        <v>Curve table</v>
       </c>
       <c r="B332" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Close</v>
+        <v>Tables</v>
       </c>
       <c r="B333" t="str">
-        <v>Schließen</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Data</v>
       </c>
       <c r="B334" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Email address</v>
+        <v>Evaluate</v>
       </c>
       <c r="B335" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>you@example.com</v>
+        <v>Loading…</v>
       </c>
       <c r="B336" t="str">
-        <v>sie@example.com</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Input</v>
       </c>
       <c r="B337" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>(optional)</v>
+        <v>Output</v>
       </c>
       <c r="B338" t="str">
-        <v>(optional)</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Floating point</v>
       </c>
       <c r="B339" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Grid point</v>
       </c>
       <c r="B340" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Cancel</v>
+        <v>Normalized</v>
       </c>
       <c r="B341" t="str">
-        <v>Abbrechen</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Subscribe</v>
+        <v>Human</v>
       </c>
       <c r="B342" t="str">
-        <v>Abonnieren</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B343" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B344" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Close</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B345" t="str">
-        <v>Schließen</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Privacy notice</v>
+        <v>Loading…</v>
       </c>
       <c r="B346" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B347" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B348" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B349" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B350" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B351" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Error:</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B352" t="str">
-        <v>Fehler:</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to XML</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B353" t="str">
-        <v>In XML konvertieren</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to JSON</v>
+        <v>Security</v>
       </c>
       <c r="B354" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to ICC</v>
+        <v>Conformance</v>
       </c>
       <c r="B355" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to XML…</v>
+        <v>Quality</v>
       </c>
       <c r="B356" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to JSON…</v>
+        <v>REPORT</v>
       </c>
       <c r="B357" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to ICC…</v>
+        <v>FAIL</v>
       </c>
       <c r="B358" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Load ICC profile</v>
+        <v>checks</v>
       </c>
       <c r="B359" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B360" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Profile ID</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B361" t="str">
-        <v>Profil-ID</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B362" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Tag Name</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B363" t="str">
-        <v>Tag-Name</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>ID</v>
+        <v>Subscribe</v>
       </c>
       <c r="B364" t="str">
-        <v>ID</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Offset</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B365" t="str">
-        <v>Offset</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Size</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B366" t="str">
-        <v>Größe</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Pad</v>
+        <v>Close</v>
       </c>
       <c r="B367" t="str">
-        <v>Auffüllung</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Bytes changed since load</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B368" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Type</v>
+        <v>Email address</v>
       </c>
       <c r="B369" t="str">
-        <v>Typ</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Array of {type}</v>
+        <v>you@example.com</v>
       </c>
       <c r="B370" t="str">
-        <v>Array von {type}</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>(No content)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B371" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>bytes</v>
+        <v>(optional)</v>
       </c>
       <c r="B372" t="str">
-        <v>Bytes</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Loading full description…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B373" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Could not load full description:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B374" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Cancel</v>
       </c>
       <c r="B375" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B376" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>No validation output</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B377" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile is valid</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B378" t="str">
-        <v>Profil ist gültig</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Close</v>
       </c>
       <c r="B379" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B380" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Critical validation error</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B381" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Unknown validation status</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B382" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B383" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B384" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Valid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B385" t="str">
-        <v>Gültig</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Warning</v>
+        <v>Error:</v>
       </c>
       <c r="B386" t="str">
-        <v>Warnung</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Error</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B387" t="str">
-        <v>Fehler</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Unknown</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B388" t="str">
-        <v>Unbekannt</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Pass</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B389" t="str">
-        <v>Bestanden</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Fail</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B390" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>View in context</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B391" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Validation detail</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B392" t="str">
-        <v>Validierungsdetail</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Triggered by</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B393" t="str">
-        <v>Ausgelöst durch</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Field</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B394" t="str">
-        <v>Feld</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Current value</v>
+        <v>Profile ID</v>
       </c>
       <c r="B395" t="str">
-        <v>Aktueller Wert</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Required: 0</v>
+        <v>No tags found.</v>
       </c>
       <c r="B396" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Expected: {value}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B397" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Invalid</v>
+        <v>ID</v>
       </c>
       <c r="B398" t="str">
-        <v>Ungültig</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Offset</v>
       </c>
       <c r="B399" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Size</v>
       </c>
       <c r="B400" t="str">
-        <v>Schließen</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pad</v>
       </c>
       <c r="B401" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B402" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Type</v>
       </c>
       <c r="B403" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B404" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved XML edits</v>
+        <v>(No content)</v>
       </c>
       <c r="B405" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>bytes</v>
       </c>
       <c r="B406" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B407" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B408" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>indent</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B409" t="str">
-        <v>Einrückung</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>sort keys</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B410" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B411" t="str">
+        <v>Keine Validierungsausgabe</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B412" t="str">
+        <v>Profil ist gültig</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B413" t="str">
+        <v>Profil hat Warnung(en)</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B414" t="str">
+        <v>Profil ist nicht konform</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B415" t="str">
+        <v>Kritischer Validierungsfehler</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B416" t="str">
+        <v>Unbekannter Validierungsstatus</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B417" t="str">
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B418" t="str">
+        <v>Keine Warnungen oder Fehler gefunden.</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B419" t="str">
+        <v>Gültig</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B420" t="str">
+        <v>Warnung</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B421" t="str">
+        <v>Fehler</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B422" t="str">
+        <v>Unbekannt</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B423" t="str">
+        <v>Bestanden</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B424" t="str">
+        <v>Fehlgeschlagen</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B425" t="str">
+        <v>Im Kontext anzeigen</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B426" t="str">
+        <v>Validierungsdetail</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B427" t="str">
+        <v>Ausgelöst durch</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B428" t="str">
+        <v>Feld</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B429" t="str">
+        <v>Aktueller Wert</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B430" t="str">
+        <v>Erforderlich: 0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B431" t="str">
+        <v>Erwartet: {value}</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B432" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B433" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B434" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B435" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B436" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B437" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B438" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B439" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B440" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B441" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B442" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B443" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B444" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B411" t="str">
+      <c r="B445" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B445"/>
+  <dimension ref="A1:B449"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -533,3445 +533,3477 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Specified gamut</v>
+        <v>Round-trip ΔE by lightness</v>
       </c>
       <c r="B17" t="str">
-        <v>Angegebener Gamut</v>
+        <v>Rundlauf-ΔE nach Helligkeit</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (lightness of the requested colour)</v>
       </c>
       <c r="B18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (Helligkeit der angeforderten Farbe)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not specified</v>
+        <v>ΔE*ab</v>
       </c>
       <c r="B19" t="str">
-        <v>Nicht angegeben</v>
+        <v>ΔE*ab</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Not evaluated</v>
+        <v>points, gamut boundary → neutral</v>
       </c>
       <c r="B20" t="str">
-        <v>Nicht ausgewertet</v>
+        <v>Punkte, Gamut-Grenze → Neutral</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PRMG interoperability</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B21" t="str">
-        <v>PRMG-Interoperabilität</v>
+        <v>Angegebener Gamut</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B22" t="str">
-        <v>Rundlauf-ΔE</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Count</v>
+        <v>Not specified</v>
       </c>
       <c r="B23" t="str">
-        <v>Anzahl</v>
+        <v>Nicht angegeben</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Share</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B24" t="str">
-        <v>Anteil</v>
+        <v>Nicht ausgewertet</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Total</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B25" t="str">
-        <v>Gesamt</v>
+        <v>PRMG-Interoperabilität</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B26" t="str">
-        <v>PRMG nicht ausgewertet</v>
+        <v>Rundlauf-ΔE</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>Count</v>
       </c>
       <c r="B27" t="str">
-        <v>Profilweite Kennzahlen für einen Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und eine Kennzahl für die Rundlauf-Genauigkeit. Wählen Sie den Render-Intent und den Rundlauf-Typ — Tabelle und Histogramm passen sich an.</v>
+        <v>Anzahl</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Round-trip type</v>
+        <v>Share</v>
       </c>
       <c r="B28" t="str">
-        <v>Rundlauf-Typ</v>
+        <v>Anteil</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Total</v>
       </c>
       <c r="B29" t="str">
-        <v>Hat auf diesen Rundlauf-Typ keine Auswirkung</v>
+        <v>Gesamt</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B30" t="str">
-        <v>Dieser Rundlauf-Typ ist für dieses Profil nicht verfügbar.</v>
+        <v>PRMG nicht ausgewertet</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B31" t="str">
-        <v>Verteilung des Rundlauf-ΔE</v>
+        <v>Profilweite Kennzahlen für einen Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und eine Kennzahl für die Rundlauf-Genauigkeit. Wählen Sie den Render-Intent und den Rundlauf-Typ — Tabelle und Histogramm passen sich an.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B32" t="str">
-        <v>Keine Rundlauf-Abtastwerte lagen innerhalb des ausgewerteten Bereichs.</v>
+        <v>Rundlauf-Typ</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Std Dev</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B33" t="str">
-        <v>Std.-Abw.</v>
+        <v>Hat auf diesen Rundlauf-Typ keine Auswirkung</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Relative frequency</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B34" t="str">
-        <v>Relative Häufigkeit</v>
+        <v>Dieser Rundlauf-Typ ist für dieses Profil nicht verfügbar.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Cumulative frequency</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B35" t="str">
-        <v>Kumulative Häufigkeit</v>
+        <v>Verteilung des Rundlauf-ΔE</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Horizontal scale</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B36" t="str">
-        <v>Horizontale Skala</v>
+        <v>Keine Rundlauf-Abtastwerte lagen innerhalb des ausgewerteten Bereichs.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Integer ΔE</v>
+        <v>Std Dev</v>
       </c>
       <c r="B37" t="str">
-        <v>Ganzzahliges ΔE</v>
+        <v>Std.-Abw.</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Auto-scale</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B38" t="str">
-        <v>Auto-Skalierung</v>
+        <v>Relative Häufigkeit</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bins</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B39" t="str">
-        <v>Klassen</v>
+        <v>Kumulative Häufigkeit</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>CLUT Image</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B40" t="str">
-        <v>CLUT-Bild</v>
+        <v>Horizontale Skala</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B41" t="str">
-        <v>Die Farbtabelle (CLUT) eines Gerät↔PCS-Transforms, als Kacheln zu einem Bild angeordnet. Wählen Sie die anzuzeigende Render-Intent-Tabelle.</v>
+        <v>Ganzzahliges ΔE</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B42" t="str">
-        <v>Dieses Profil hat keine CLUT-basierten Gerät↔PCS-Tabellen zur Visualisierung.</v>
+        <v>Auto-Skalierung</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Gamut Image</v>
+        <v>Bins</v>
       </c>
       <c r="B43" t="str">
-        <v>Gamut-Bild</v>
+        <v>Klassen</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B44" t="str">
-        <v>Die In-/Außerhalb-Gamut-Karte des Gamut-Tags: neutral, wo eine PCS-Farbe reproduzierbar ist, rot, wo sie außerhalb des Gerätegamuts liegt.</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B45" t="str">
-        <v>Dieses Profil hat kein Gamut-Tag zur Visualisierung.</v>
+        <v>Die Farbtabelle (CLUT) eines Gerät↔PCS-Transforms, als Kacheln zu einem Bild angeordnet. Wählen Sie die anzuzeigende Render-Intent-Tabelle.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B46" t="str">
-        <v>Vertikale Skala</v>
+        <v>Dieses Profil hat keine CLUT-basierten Gerät↔PCS-Tabellen zur Visualisierung.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>X–Y</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B47" t="str">
-        <v>X–Y</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B48" t="str">
-        <v>Tonwertzunahme</v>
+        <v>Die In-/Außerhalb-Gamut-Karte des Gamut-Tags: neutral, wo eine PCS-Farbe reproduzierbar ist, rot, wo sie außerhalb des Gerätegamuts liegt.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B49" t="str">
-        <v>Tonwertzunahme (Ausgang − Eingang)</v>
+        <v>Dieses Profil hat kein Gamut-Tag zur Visualisierung.</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Show full dump</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B50" t="str">
-        <v>Vollständige Ausgabe anzeigen</v>
+        <v>Vertikale Skala</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Output truncated for performance.</v>
+        <v>X–Y</v>
       </c>
       <c r="B51" t="str">
-        <v>Ausgabe aus Leistungsgründen gekürzt.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B52" t="str">
-        <v>In-Gamut-Übersicht (RT0)</v>
+        <v>Tonwertzunahme</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B53" t="str">
-        <v>Inversion + Gamut (RT1)</v>
+        <v>Tonwertzunahme (Ausgang − Eingang)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Show full dump</v>
       </c>
       <c r="B54" t="str">
-        <v>Reproduzierbarkeit (RT2)</v>
+        <v>Vollständige Ausgabe anzeigen</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PRMG interoperability</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B55" t="str">
-        <v>PRMG-Interoperabilität</v>
+        <v>Ausgabe aus Leistungsgründen gekürzt.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B56" t="str">
-        <v>iccviz-Übersicht: Ein Gitter aus Gerätewerten wird nach PCS, zurück zum Gerät und erneut nach PCS überführt; ΔE*ab wird zwischen den beiden PCS-Durchläufen gemessen. Eine schnelle In-Gamut-Stabilitätsprüfung.</v>
+        <v>In-Gamut-Übersicht (RT0)</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip Rundlauf 1: ΔE*ab zwischen dem PCS jeder Gerätefarbe und ihrem PCS nach einem Rundlauf Lab → Gerät → Lab. Spiegelt Inversionsgenauigkeit und Gamut-Mapping wider.</v>
+        <v>Inversion + Gamut (RT1)</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip Rundlauf 2: ΔE*ab zwischen dem ersten und zweiten Rundlauf — wie stabil ein wiederholter PCS-Rundlauf ist (Reproduzierbarkeit, unabhängig vom Gamut-Clipping des ersten Durchlaufs).</v>
+        <v>Reproduzierbarkeit (RT2)</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B59" t="str">
-        <v>iccRoundTrip PRMG: PCS-Farben innerhalb des Perceptual Reference Medium Gamut durchlaufen einen einzelnen Rundlauf (Lab → Gerät → Lab); die ΔE*ab-Verteilung zeigt die profilübergreifende Interoperabilität.</v>
+        <v>PRMG-Interoperabilität</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Settings</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B60" t="str">
-        <v>Einstellungen</v>
+        <v>iccviz-Übersicht: Ein Gitter aus Gerätewerten wird nach PCS, zurück zum Gerät und erneut nach PCS überführt; ΔE*ab wird zwischen den beiden PCS-Durchläufen gemessen. Eine schnelle In-Gamut-Stabilitätsprüfung.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Display</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B61" t="str">
-        <v>Anzeige</v>
+        <v>iccRoundTrip Rundlauf 1: ΔE*ab zwischen dem PCS jeder Gerätefarbe und ihrem PCS nach einem Rundlauf Lab → Gerät → Lab. Spiegelt Inversionsgenauigkeit und Gamut-Mapping wider.</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Background</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B62" t="str">
-        <v>Hintergrund</v>
+        <v>iccRoundTrip Rundlauf 2: ΔE*ab zwischen dem ersten und zweiten Rundlauf — wie stabil ein wiederholter PCS-Rundlauf ist (Reproduzierbarkeit, unabhängig vom Gamut-Clipping des ersten Durchlaufs).</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Language</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B63" t="str">
-        <v>Sprache</v>
+        <v>iccRoundTrip PRMG: PCS-Farben innerhalb des Perceptual Reference Medium Gamut durchlaufen einen einzelnen Rundlauf (Lab → Gerät → Lab); die ΔE*ab-Verteilung zeigt die profilübergreifende Interoperabilität.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>System</v>
+        <v>Settings</v>
       </c>
       <c r="B64" t="str">
-        <v>System</v>
+        <v>Einstellungen</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Light</v>
+        <v>Display</v>
       </c>
       <c r="B65" t="str">
-        <v>Hell</v>
+        <v>Anzeige</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Dark</v>
+        <v>Background</v>
       </c>
       <c r="B66" t="str">
-        <v>Dunkel</v>
+        <v>Hintergrund</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>System default</v>
+        <v>Language</v>
       </c>
       <c r="B67" t="str">
-        <v>Systemstandard</v>
+        <v>Sprache</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Number format</v>
+        <v>System</v>
       </c>
       <c r="B68" t="str">
-        <v>Zahlenformat</v>
+        <v>System</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Hexadecimal</v>
+        <v>Light</v>
       </c>
       <c r="B69" t="str">
-        <v>Hexadezimal</v>
+        <v>Hell</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Decimal</v>
+        <v>Dark</v>
       </c>
       <c r="B70" t="str">
-        <v>Dezimal</v>
+        <v>Dunkel</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Help</v>
+        <v>System default</v>
       </c>
       <c r="B71" t="str">
-        <v>Hilfe</v>
+        <v>Systemstandard</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Contact</v>
+        <v>Number format</v>
       </c>
       <c r="B72" t="str">
-        <v>Kontakt</v>
+        <v>Zahlenformat</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>User guide</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B73" t="str">
-        <v>Benutzerhandbuch</v>
+        <v>Hexadezimal</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search guide</v>
+        <v>Decimal</v>
       </c>
       <c r="B74" t="str">
-        <v>Handbuch durchsuchen</v>
+        <v>Dezimal</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Search the user guide</v>
+        <v>Help</v>
       </c>
       <c r="B75" t="str">
-        <v>Benutzerhandbuch durchsuchen</v>
+        <v>Hilfe</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Previous match</v>
+        <v>Contact</v>
       </c>
       <c r="B76" t="str">
-        <v>Vorheriger Treffer</v>
+        <v>Kontakt</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Next match</v>
+        <v>User guide</v>
       </c>
       <c r="B77" t="str">
-        <v>Nächster Treffer</v>
+        <v>Benutzerhandbuch</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Close user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B78" t="str">
-        <v>Handbuch schließen</v>
+        <v>Handbuch durchsuchen</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B79" t="str">
-        <v>Wird geladen…</v>
+        <v>Benutzerhandbuch durchsuchen</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Previous match</v>
       </c>
       <c r="B80" t="str">
-        <v>Benutzerhandbuch konnte nicht geladen werden.</v>
+        <v>Vorheriger Treffer</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>None</v>
+        <v>Next match</v>
       </c>
       <c r="B81" t="str">
-        <v>Keine</v>
+        <v>Nächster Treffer</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Close user guide</v>
       </c>
       <c r="B82" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Handbuch schließen</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Based on</v>
+        <v>Loading…</v>
       </c>
       <c r="B83" t="str">
-        <v>Basierend auf der</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B84" t="str">
-        <v>Demo-Implementierung</v>
+        <v>Benutzerhandbuch konnte nicht geladen werden.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Validating…</v>
+        <v>None</v>
       </c>
       <c r="B85" t="str">
-        <v>Validierung…</v>
+        <v>Keine</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Save ICC profile</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B86" t="str">
-        <v>ICC-Profil speichern</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Based on</v>
       </c>
       <c r="B87" t="str">
-        <v>● Geändert — nicht gespeichert</v>
+        <v>Basierend auf der</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Profiles</v>
+        <v>demo implementation</v>
       </c>
       <c r="B88" t="str">
-        <v>Profile</v>
+        <v>Demo-Implementierung</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Show profile pool</v>
+        <v>Validating…</v>
       </c>
       <c r="B89" t="str">
-        <v>Profil-Pool anzeigen</v>
+        <v>Validierung…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Collapse</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B90" t="str">
-        <v>Einklappen</v>
+        <v>ICC-Profil speichern</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Load Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B91" t="str">
-        <v>Profile laden</v>
+        <v>● Geändert — nicht gespeichert</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Remove</v>
+        <v>Profiles</v>
       </c>
       <c r="B92" t="str">
-        <v>Entfernen</v>
+        <v>Profile</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B93" t="str">
-        <v>ICC-Profile hierher ziehen</v>
+        <v>Profil-Pool anzeigen</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Collapse</v>
       </c>
       <c r="B94" t="str">
-        <v>oder ein Bild (TIFF/PNG/JPEG), um dessen eingebettetes Profil zu extrahieren — die Dateien bleiben auf Ihrem Gerät.</v>
+        <v>Einklappen</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>New from .cube</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B95" t="str">
-        <v>Neu aus .cube</v>
+        <v>Profile laden</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Sort by name</v>
+        <v>Remove</v>
       </c>
       <c r="B96" t="str">
-        <v>Nach Namen sortieren</v>
+        <v>Entfernen</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>A–Z</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B97" t="str">
-        <v>A–Z</v>
+        <v>ICC-Profile hierher ziehen</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>New profile from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B98" t="str">
-        <v>Neues Profil aus .cube</v>
+        <v>oder ein Bild (TIFF/PNG/JPEG), um dessen eingebettetes Profil zu extrahieren — die Dateien bleiben auf Ihrem Gerät.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New from .cube</v>
       </c>
       <c r="B99" t="str">
-        <v>Erstellen Sie einen ICC-DeviceLink aus einer Adobe/Resolve-.cube-3D-LUT. Das Ergebnis wird Ihrem Pool hinzugefügt und heruntergeladen.</v>
+        <v>Neu aus .cube</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Choose .cube file</v>
+        <v>Sort by name</v>
       </c>
       <c r="B100" t="str">
-        <v>.cube-Datei wählen</v>
+        <v>Nach Namen sortieren</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>A–Z</v>
+      </c>
+      <c r="B101" t="str">
+        <v>A–Z</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>New profile from .cube</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Neues Profil aus .cube</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Erstellen Sie einen ICC-DeviceLink aus einer Adobe/Resolve-.cube-3D-LUT. Das Ergebnis wird Ihrem Pool hinzugefügt und heruntergeladen.</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B104" t="str">
+        <v>.cube-Datei wählen</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B101" t="str">
+      <c r="B105" t="str">
         <v>oder hierher ziehen oder unten einfügen</v>
       </c>
     </row>
-    <row r="102" xml:space="preserve">
-      <c r="A102" t="str" xml:space="preserve">
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B102" t="str" xml:space="preserve">
+      <c r="B106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B103" t="str">
-        <v>Abbrechen</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Create DeviceLink</v>
-      </c>
-      <c r="B104" t="str">
-        <v>DeviceLink erstellen</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Creating…</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Wird erstellt…</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Could not read that file.</v>
-      </c>
-      <c r="B106" t="str">
-        <v>Diese Datei konnte nicht gelesen werden.</v>
-      </c>
-    </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Profile</v>
+        <v>Cancel</v>
       </c>
       <c r="B107" t="str">
-        <v>Profil</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Compare</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B108" t="str">
-        <v>Vergleichen</v>
+        <v>DeviceLink erstellen</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Combine</v>
+        <v>Creating…</v>
       </c>
       <c r="B109" t="str">
-        <v>Verknüpfen</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Spectral</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B110" t="str">
-        <v>Spektral</v>
+        <v>Diese Datei konnte nicht gelesen werden.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Profile</v>
       </c>
       <c r="B111" t="str">
-        <v>Ziehen Sie Profile aus dem Pool auf diesen Tab</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Remove</v>
+        <v>Compare</v>
       </c>
       <c r="B112" t="str">
-        <v>Entfernen</v>
+        <v>Vergleichen</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>No profile selected</v>
+        <v>Combine</v>
       </c>
       <c r="B113" t="str">
-        <v>Kein Profil ausgewählt</v>
+        <v>Verknüpfen</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Spectral</v>
       </c>
       <c r="B114" t="str">
-        <v>Ziehen Sie ein Profil aus dem Pool auf den Profil-Tab, um es zu untersuchen.</v>
+        <v>Spektral</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B115" t="str">
-        <v>Noch nichts zu vergleichen</v>
+        <v>Ziehen Sie Profile aus dem Pool auf diesen Tab</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Remove</v>
       </c>
       <c r="B116" t="str">
-        <v>Ziehen Sie ein oder mehrere Profile auf den Vergleichen-Tab.</v>
+        <v>Entfernen</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Gamut comparison</v>
+        <v>No profile selected</v>
       </c>
       <c r="B117" t="str">
-        <v>Gamut-Vergleich</v>
+        <v>Kein Profil ausgewählt</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B118" t="str">
-        <v>3D-Gamut- und 2D-Schnittansichten kommen hierher. Gesammelt:</v>
+        <v>Ziehen Sie ein Profil aus dem Pool auf den Profil-Tab, um es zu untersuchen.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Rendering intent</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B119" t="str">
-        <v>Render-Intent</v>
+        <v>Noch nichts zu vergleichen</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Shell</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B120" t="str">
-        <v>Hülle</v>
+        <v>Ziehen Sie ein oder mehrere Profile auf den Vergleichen-Tab.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Wireframe</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B121" t="str">
-        <v>Drahtgitter</v>
+        <v>Gamut-Vergleich</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Axis numbers</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B122" t="str">
-        <v>Achsenwerte</v>
+        <v>3D-Gamut- und 2D-Schnittansichten kommen hierher. Gesammelt:</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B123" t="str">
-        <v>Deckkraft</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Shell</v>
       </c>
       <c r="B124" t="str">
-        <v>Farbe</v>
+        <v>Hülle</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Wireframe</v>
       </c>
       <c r="B125" t="str">
-        <v>Einfarbig</v>
+        <v>Drahtgitter</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B126" t="str">
-        <v>Nach Wert</v>
+        <v>Achsenwerte</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Opacity</v>
       </c>
       <c r="B127" t="str">
-        <v>Nach Farbton</v>
+        <v>Deckkraft</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>Colour</v>
       </c>
       <c r="B128" t="str">
-        <v>Rotation</v>
+        <v>Farbe</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>Solid</v>
       </c>
       <c r="B129" t="str">
-        <v>Drehteller</v>
+        <v>Einfarbig</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>By value</v>
       </c>
       <c r="B130" t="str">
-        <v>Orbit</v>
+        <v>Nach Wert</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>By hue</v>
       </c>
       <c r="B131" t="str">
-        <v>Ziehgeschwindigkeit</v>
+        <v>Nach Farbton</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Rotation</v>
       </c>
       <c r="B132" t="str">
-        <v>Rollen</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B133" t="str">
-        <v>Rollgeschwindigkeit</v>
+        <v>Drehteller</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Orbit</v>
       </c>
       <c r="B134" t="str">
-        <v>Gamut wird erstellt…</v>
+        <v>Orbit</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Drag speed</v>
       </c>
       <c r="B135" t="str">
-        <v>kein Gamut</v>
+        <v>Ziehgeschwindigkeit</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Roll</v>
       </c>
       <c r="B136" t="str">
-        <v>Ein-/ausblenden</v>
+        <v>Rollen</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>Roll speed</v>
       </c>
       <c r="B137" t="str">
-        <v>3D-Gamut-Hülle</v>
+        <v>Rollgeschwindigkeit</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B138" t="str">
-        <v>2D-Gamut-Schnitt</v>
+        <v>Gamut wird erstellt…</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>no gamut</v>
       </c>
       <c r="B139" t="str">
-        <v>Ebene</v>
+        <v>kein Gamut</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>Show / hide</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>Ein-/ausblenden</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>3D-Gamut-Hülle</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>2D-Gamut-Schnitt</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>Plane</v>
       </c>
       <c r="B143" t="str">
-        <v>Keines der ausgewählten Profile hat ein Gerät→PCS-Transform, aus dem sich ein Gamut ableiten lässt.</v>
+        <v>Ebene</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>L*</v>
       </c>
       <c r="B144" t="str">
-        <v>Verknüpfung</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>a*</v>
       </c>
       <c r="B145" t="str">
-        <v>DeviceLink-Erzeugung und Transformationen über mehrere Profile folgen in einer späteren Phase.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>b*</v>
       </c>
       <c r="B146" t="str">
-        <v>Weitere Link-Ersteller (DeviceLink, …) folgen hier.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Observer Change</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B147" t="str">
-        <v>V4-Display-Ersteller</v>
+        <v>Keines der ausgewählten Profile hat ein Gerät→PCS-Transform, aus dem sich ein Gamut ableiten lässt.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Linking</v>
       </c>
       <c r="B148" t="str">
-        <v>Ziehen Sie ein V5-RGB-Display- und ein V5-Beobachterprofil hierher, um ein V4-Displayprofil zu erstellen.</v>
+        <v>Verknüpfung</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B149" t="str">
-        <v>V5-RGB-Display</v>
+        <v>DeviceLink-Erzeugung und Transformationen über mehrere Profile folgen in einer späteren Phase.</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B150" t="str">
-        <v>Displayprofil ablegen</v>
+        <v>Weitere Link-Ersteller (DeviceLink, …) folgen hier.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Observer Change</v>
       </c>
       <c r="B151" t="str">
-        <v>V5-Beobachter (PCC)</v>
+        <v>V4-Display-Ersteller</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B152" t="str">
-        <v>Beobachterprofil ablegen</v>
+        <v>Ziehen Sie ein V5-RGB-Display- und ein V5-Beobachterprofil hierher, um ein V4-Displayprofil zu erstellen.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B153" t="str">
-        <v>Ein Profil, das weder ein V5-RGB-Display noch ein Beobachter ist, wurde ignoriert.</v>
+        <v>V5-RGB-Display</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B154" t="str">
-        <v>V4-Displayprofil erstellen</v>
+        <v>Displayprofil ablegen</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B155" t="str">
-        <v>Profilname</v>
+        <v>V5-Beobachter (PCC)</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B156" t="str">
-        <v>Erstellen</v>
+        <v>Beobachterprofil ablegen</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B157" t="str">
-        <v>Wird erstellt…</v>
+        <v>Ein Profil, das weder ein V5-RGB-Display noch ein Beobachter ist, wurde ignoriert.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B158" t="str">
-        <v>„{name}“ erstellt — dem Pool und diesem Tab hinzugefügt.</v>
+        <v>V4-Displayprofil erstellen</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Link Pipeline</v>
+        <v>Profile name</v>
       </c>
       <c r="B159" t="str">
-        <v>Link-Pipeline</v>
+        <v>Profilname</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Create</v>
       </c>
       <c r="B160" t="str">
-        <v>Erstellen Sie eine Kette aus Profilen und erzeugen Sie daraus einen DeviceLink, transformieren Sie ein Bild oder einen Farbdatensatz.</v>
+        <v>Erstellen</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Done</v>
+        <v>Making…</v>
       </c>
       <c r="B161" t="str">
-        <v>Fertig</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B162" t="str">
-        <v>Bild zum Transformieren ablegen (TIFF/PNG/JPEG)</v>
+        <v>„{name}“ erstellt — dem Pool und diesem Tab hinzugefügt.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Checking image…</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B163" t="str">
-        <v>Bild wird geprüft…</v>
+        <v>Link-Pipeline</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B164" t="str">
-        <v>Kein unterstütztes Bildformat (TIFF, PNG oder JPEG).</v>
+        <v>Erstellen Sie eine Kette aus Profilen und erzeugen Sie daraus einen DeviceLink, transformieren Sie ein Bild oder einen Farbdatensatz.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Done</v>
       </c>
       <c r="B165" t="str">
-        <v>Bild zu groß ({mp} MP; Grenzwert {max} MP).</v>
+        <v>Fertig</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transform Image</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B166" t="str">
-        <v>Bild transformieren</v>
+        <v>Bild zum Transformieren ablegen (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Transforming…</v>
+        <v>Checking image…</v>
       </c>
       <c r="B167" t="str">
-        <v>Wird transformiert…</v>
+        <v>Bild wird geprüft…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B168" t="str">
-        <v>Profile ablegen, um die Kette zu starten</v>
+        <v>Kein unterstütztes Bildformat (TIFF, PNG oder JPEG).</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>removed</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B169" t="str">
-        <v>entfernt</v>
+        <v>Bild zu groß ({mp} MP; Grenzwert {max} MP).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move earlier</v>
+        <v>Transform Image</v>
       </c>
       <c r="B170" t="str">
-        <v>Nach vorne verschieben</v>
+        <v>Bild transformieren</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move later</v>
+        <v>Transforming…</v>
       </c>
       <c r="B171" t="str">
-        <v>Nach hinten verschieben</v>
+        <v>Wird transformiert…</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move up</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B172" t="str">
-        <v>Nach oben verschieben</v>
+        <v>Profile ablegen, um die Kette zu starten</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move down</v>
+        <v>removed</v>
       </c>
       <c r="B173" t="str">
-        <v>Nach unten verschieben</v>
+        <v>entfernt</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move earlier</v>
       </c>
       <c r="B174" t="str">
-        <v>Rendering-Priorität (alle)</v>
+        <v>Nach vorne verschieben</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Move later</v>
       </c>
       <c r="B175" t="str">
-        <v>Rendering-Priorität für diese Transformation</v>
+        <v>Nach hinten verschieben</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Move up</v>
       </c>
       <c r="B176" t="str">
-        <v>Die Transformationen verwenden unterschiedliche Rendering-Prioritäten</v>
+        <v>Nach oben verschieben</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Move down</v>
       </c>
       <c r="B177" t="str">
-        <v>Kettenrichtung umkehren (kehrt die erste Transformation um und wirkt sich auf die gesamte Kette aus)</v>
+        <v>Nach unten verschieben</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B178" t="str">
-        <v>Ein verkettetes Profil wurde aus dem Pool entfernt — entfernen Sie es, um fortzufahren.</v>
+        <v>Rendering-Priorität (alle)</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Chain</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B179" t="str">
-        <v>Kette</v>
+        <v>Rendering-Priorität für diese Transformation</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B180" t="str">
-        <v>Die Kette konnte nicht analysiert werden.</v>
+        <v>Die Transformationen verwenden unterschiedliche Rendering-Prioritäten</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Checking chain…</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B181" t="str">
-        <v>Kette wird geprüft…</v>
+        <v>Kettenrichtung umkehren (kehrt die erste Transformation um und wirkt sich auf die gesamte Kette aus)</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B182" t="str">
-        <v>Die Kette verbindet sich nicht ({detail}).</v>
+        <v>Ein verkettetes Profil wurde aus dem Pool entfernt — entfernen Sie es, um fortzufahren.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Chain</v>
       </c>
       <c r="B183" t="str">
-        <v>Profil {n} verbindet sich nicht mit der vorherigen Stufe ({detail}).</v>
+        <v>Kette</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B184" t="str">
-        <v>Beheben Sie die Kette, bevor Sie Bilder verarbeiten</v>
+        <v>Die Kette konnte nicht analysiert werden.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Clear</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B185" t="str">
-        <v>Leeren</v>
+        <v>Kette wird geprüft…</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Make DeviceLink</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B186" t="str">
-        <v>DeviceLink erstellen</v>
+        <v>Die Kette verbindet sich nicht ({detail}).</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>DeviceLink name</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>DeviceLink-Name</v>
+        <v>Profil {n} verbindet sich nicht mit der vorherigen Stufe ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Making…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B188" t="str">
-        <v>Wird erstellt…</v>
+        <v>Beheben Sie die Kette, bevor Sie Bilder verarbeiten</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Clear</v>
       </c>
       <c r="B189" t="str">
-        <v>„{name}“ erstellt — zum Pool und zu diesem Tab hinzugefügt.</v>
+        <v>Leeren</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B190" t="str">
-        <v>{src}-Bilder ablegen, um sie in {dst} zu konvertieren — Ergebnisse werden heruntergeladen, nichts wird gespeichert.</v>
+        <v>DeviceLink erstellen</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Build a chain to process images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B191" t="str">
-        <v>Erstellen Sie eine Kette, um Bilder zu verarbeiten</v>
+        <v>DeviceLink-Name</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Making…</v>
       </c>
       <c r="B192" t="str">
-        <v>Diese Kette beginnt und endet nicht in einem Bildfarbraum</v>
+        <v>Wird erstellt…</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B193" t="str">
-        <v>Transformiertes Bild gespeichert.</v>
+        <v>„{name}“ erstellt — zum Pool und zu diesem Tab hinzugefügt.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B194" t="str">
-        <v>Farbdatensatz ablegen (CGATS/CSV/CxF/JSON)</v>
+        <v>{src}-Bilder ablegen, um sie in {dst} zu konvertieren — Ergebnisse werden heruntergeladen, nichts wird gespeichert.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Could not read that file.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B195" t="str">
-        <v>Diese Datei konnte nicht gelesen werden.</v>
+        <v>Erstellen Sie eine Kette, um Bilder zu verarbeiten</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Data file too large.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B196" t="str">
-        <v>Datendatei zu groß.</v>
+        <v>Diese Kette beginnt und endet nicht in einem Bildfarbraum</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transform Data</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B197" t="str">
-        <v>Daten transformieren</v>
+        <v>Transformiertes Bild gespeichert.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Transforming…</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B198" t="str">
-        <v>Wird transformiert…</v>
+        <v>Farbdatensatz ablegen (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Prefer</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B199" t="str">
-        <v>Bevorzugen</v>
+        <v>Diese Datei konnte nicht gelesen werden.</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Observer</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B200" t="str">
-        <v>Beobachter</v>
+        <v>Datendatei zu groß.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Illuminant</v>
+        <v>Transform Data</v>
       </c>
       <c r="B201" t="str">
-        <v>Lichtart</v>
+        <v>Daten transformieren</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Condition</v>
+        <v>Transforming…</v>
       </c>
       <c r="B202" t="str">
-        <v>Bedingung</v>
+        <v>Wird transformiert…</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Prefer</v>
       </c>
       <c r="B203" t="str">
-        <v>{n} Duplikat(e) filtern</v>
+        <v>Bevorzugen</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>median</v>
+        <v>Observer</v>
       </c>
       <c r="B204" t="str">
-        <v>Median</v>
+        <v>Beobachter</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>mean</v>
+        <v>Illuminant</v>
       </c>
       <c r="B205" t="str">
-        <v>Mittelwert</v>
+        <v>Lichtart</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>patches</v>
+        <v>Condition</v>
       </c>
       <c r="B206" t="str">
-        <v>Farbfelder</v>
+        <v>Bedingung</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>{n} duplicates</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B207" t="str">
-        <v>{n} Duplikate</v>
+        <v>{n} Duplikat(e) filtern</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Transform result</v>
+        <v>median</v>
       </c>
       <c r="B208" t="str">
-        <v>Transformationsergebnis</v>
+        <v>Median</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>mean</v>
       </c>
       <c r="B209" t="str">
-        <v>{src} → {dst} · {n} Farbfelder</v>
+        <v>Mittelwert</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>patches</v>
       </c>
       <c r="B210" t="str">
-        <v>Zeigt die ersten {shown} von {total} — Speichern schreibt alle.</v>
+        <v>Farbfelder</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save as</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B211" t="str">
-        <v>Speichern unter</v>
+        <v>{n} Duplikate</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Save</v>
+        <v>Transform result</v>
       </c>
       <c r="B212" t="str">
-        <v>Speichern</v>
+        <v>Transformationsergebnis</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Invert Transform</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B213" t="str">
-        <v>Transformation umkehren</v>
+        <v>{src} → {dst} · {n} Farbfelder</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Inverting…</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B214" t="str">
-        <v>Wird umgekehrt…</v>
+        <v>Zeigt die ersten {shown} von {total} — Speichern schreibt alle.</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert</v>
+        <v>Save as</v>
       </c>
       <c r="B215" t="str">
-        <v>Umkehren</v>
+        <v>Speichern unter</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>last stage</v>
+        <v>Save</v>
       </c>
       <c r="B216" t="str">
-        <v>letzte Stufe</v>
+        <v>Speichern</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>first stage</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B217" t="str">
-        <v>erste Stufe</v>
+        <v>Transformation umkehren</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>Inverting…</v>
       </c>
       <c r="B218" t="str">
-        <v>Daten in {in} → Suche {out}</v>
+        <v>Wird umgekehrt…</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Invert</v>
       </c>
       <c r="B219" t="str">
-        <v>Die Umkehrung benötigt eine Kette aus 2–3 Profilen</v>
+        <v>Umkehren</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>last stage</v>
       </c>
       <c r="B220" t="str">
-        <v>Der Datensatz muss in {in} vorliegen; die inverse Suche liefert {out} sowie einen Invertierbarkeits-Kostenwert pro Farbfeld.</v>
+        <v>letzte Stufe</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>ΔE cost</v>
+        <v>first stage</v>
       </c>
       <c r="B221" t="str">
-        <v>ΔE-Kosten</v>
+        <v>erste Stufe</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B222" t="str">
-        <v>Dieses Bild enthält ein eingebettetes ICC-Profil.</v>
+        <v>Daten in {in} → Suche {out}</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B223" t="str">
-        <v>Extrahieren &amp; zur Kette hinzufügen</v>
+        <v>Die Umkehrung benötigt eine Kette aus 2–3 Profilen</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Extracting…</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B224" t="str">
-        <v>Wird extrahiert…</v>
+        <v>Der Datensatz muss in {in} vorliegen; die inverse Suche liefert {out} sowie einen Invertierbarkeits-Kostenwert pro Farbfeld.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Dismiss</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B225" t="str">
-        <v>Verwerfen</v>
+        <v>ΔE-Kosten</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B226" t="str">
-        <v>Eingebettetes Profil extrahiert — zum Pool hinzugefügt und an den Anfang der Kette gesetzt.</v>
+        <v>Dieses Bild enthält ein eingebettetes ICC-Profil.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Image output options</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B227" t="str">
-        <v>Bildausgabeoptionen</v>
+        <v>Extrahieren &amp; zur Kette hinzufügen</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Encoding</v>
+        <v>Extracting…</v>
       </c>
       <c r="B228" t="str">
-        <v>Kodierung</v>
+        <v>Wird extrahiert…</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Same as source</v>
+        <v>Dismiss</v>
       </c>
       <c r="B229" t="str">
-        <v>Wie Quelle</v>
+        <v>Verwerfen</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>8-bit</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B230" t="str">
-        <v>8 Bit</v>
+        <v>Eingebettetes Profil extrahiert — zum Pool hinzugefügt und an den Anfang der Kette gesetzt.</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>16-bit</v>
+        <v>Image output options</v>
       </c>
       <c r="B231" t="str">
-        <v>16 Bit</v>
+        <v>Bildausgabeoptionen</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Float (32-bit)</v>
+        <v>Encoding</v>
       </c>
       <c r="B232" t="str">
-        <v>Gleitkomma (32 Bit)</v>
+        <v>Kodierung</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Compression</v>
+        <v>Same as source</v>
       </c>
       <c r="B233" t="str">
-        <v>Komprimierung</v>
+        <v>Wie Quelle</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>None</v>
+        <v>8-bit</v>
       </c>
       <c r="B234" t="str">
-        <v>Keine</v>
+        <v>8 Bit</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Planar</v>
+        <v>16-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>Planar</v>
+        <v>16 Bit</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Composite</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B236" t="str">
-        <v>Verschachtelt</v>
+        <v>Gleitkomma (32 Bit)</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Separated</v>
+        <v>Compression</v>
       </c>
       <c r="B237" t="str">
-        <v>Getrennt</v>
+        <v>Komprimierung</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>CMM interpolation</v>
+        <v>None</v>
       </c>
       <c r="B238" t="str">
-        <v>CMM-Interpolation</v>
+        <v>Keine</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Tetrahedral</v>
+        <v>Planar</v>
       </c>
       <c r="B239" t="str">
-        <v>Tetraedrisch</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Linear</v>
+        <v>Composite</v>
       </c>
       <c r="B240" t="str">
-        <v>Linear</v>
+        <v>Verschachtelt</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Embed ICC</v>
+        <v>Separated</v>
       </c>
       <c r="B241" t="str">
-        <v>ICC-Profil einbetten</v>
+        <v>Getrennt</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B242" t="str">
-        <v>Kodierung, Komprimierung und Planaranordnung bestimmen das gespeicherte TIFF. Die RGB-/Gray-Ausgabe bleibt PNG, sofern keine TIFF-spezifische Option (Gleitkomma, LZW/ZIP, Getrennt) gewählt wird.</v>
+        <v>CMM-Interpolation</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B243" t="str">
-        <v>Spektrales TIFF zusammenstellen</v>
+        <v>Tetraedrisch</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Linear</v>
       </c>
       <c r="B244" t="str">
-        <v>Einkanalige Spektralbilder in Kanalreihenfolge ablegen und zu einem mehrkanaligen TIFF zusammenfügen.</v>
+        <v>Linear</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B245" t="str">
-        <v>Spektralbilder hier ablegen (oder klicken, um auszuwählen)</v>
+        <v>ICC-Profil einbetten</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>ch</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B246" t="str">
-        <v>Kan</v>
+        <v>Kodierung, Komprimierung und Planaranordnung bestimmen das gespeicherte TIFF. Die RGB-/Gray-Ausgabe bleibt PNG, sofern keine TIFF-spezifische Option (Gleitkomma, LZW/ZIP, Getrennt) gewählt wird.</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B247" t="str">
-        <v>Zusammenfügen &amp; Speichern</v>
+        <v>Spektrales TIFF zusammenstellen</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembling…</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B248" t="str">
-        <v>Wird zusammengefügt…</v>
+        <v>Einkanalige Spektralbilder in Kanalreihenfolge ablegen und zu einem mehrkanaligen TIFF zusammenfügen.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B249" t="str">
-        <v>{n} Kanäle zusammengefügt.</v>
+        <v>Spektralbilder hier ablegen (oder klicken, um auszuwählen)</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>ch</v>
       </c>
       <c r="B250" t="str">
-        <v>Keine dieser Dateien sieht wie ein Bild aus (TIFF, PNG oder JPEG).</v>
+        <v>Kan</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B251" t="str">
-        <v>Abbrechen</v>
+        <v>Zusammenfügen &amp; Speichern</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Assembling…</v>
       </c>
       <c r="B252" t="str">
-        <v>{n} Datei(en) nicht geladen</v>
+        <v>Wird zusammengefügt…</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B253" t="str">
-        <v>Diese Dateien sind keine ICC-Profile und wurden daher nicht zum Pool hinzugefügt:</v>
+        <v>{n} Kanäle zusammengefügt.</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>OK</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B254" t="str">
-        <v>OK</v>
+        <v>Keine dieser Dateien sieht wie ein Bild aus (TIFF, PNG oder JPEG).</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Cancel</v>
       </c>
       <c r="B255" t="str">
-        <v>ICC-Profil hierher ziehen</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>or</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B256" t="str">
-        <v>oder</v>
+        <v>{n} Datei(en) nicht geladen</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Choose file</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B257" t="str">
-        <v>Datei wählen</v>
+        <v>Diese Dateien sind keine ICC-Profile und wurden daher nicht zum Pool hinzugefügt:</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>.icc and .icm files</v>
+        <v>OK</v>
       </c>
       <c r="B258" t="str">
-        <v>.icc- und .icm-Dateien</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Header</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B259" t="str">
-        <v>Header</v>
+        <v>ICC-Profil hierher ziehen</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Tags</v>
+        <v>or</v>
       </c>
       <c r="B260" t="str">
-        <v>Tags</v>
+        <v>oder</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Validation</v>
+        <v>Choose file</v>
       </c>
       <c r="B261" t="str">
-        <v>Validierung</v>
+        <v>Datei wählen</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Analysis</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B262" t="str">
-        <v>Analyse</v>
+        <v>.icc- und .icm-Dateien</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Header</v>
       </c>
       <c r="B263" t="str">
-        <v>Neutralachsen-Einfärbung</v>
+        <v>Header</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Tags</v>
       </c>
       <c r="B264" t="str">
-        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Validation</v>
       </c>
       <c r="B265" t="str">
-        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Validierung</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Analysis</v>
       </c>
       <c r="B266" t="str">
-        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Rendering intent</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B267" t="str">
-        <v>Render-Intent</v>
+        <v>Neutralachsen-Einfärbung</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>% ink</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B268" t="str">
-        <v>% Farbe</v>
+        <v>Auf der Neutralachse (a*=b*=0) aufgetragene Farbe, während die Helligkeit von Weiß (L*=100) zu Schwarz (L*=0) verläuft.</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>L* out (tone)</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B269" t="str">
-        <v>L* Ausgabe (Tonwert)</v>
+        <v>Die Neutralachsen-Einfärbung ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Δa*b*</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B270" t="str">
-        <v>Δa*b*</v>
+        <v>Dieses Profil hat keine B2A-Tabelle (PCS→Gerät) zum Abtasten.</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B271" t="str">
-        <v>Kolorimetrie der Extremwerte</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>% ink</v>
       </c>
       <c r="B272" t="str">
-        <v>Die Enden des Wiedergabeumfangs des Profils: das Weiß des Bedruckstoffs, das dunkelste Schwarz, das es druckt, der Farbauftrag, den dieses Schwarz kostet, und der Punkt, an dem jeder Farbton am gesättigtsten ist.</v>
+        <v>% Farbe</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B273" t="str">
-        <v>Der Weißpunkt ist die Farbe bei null Farbmittel — der blanke Bedruckstoff. Der Schwarzpunkt ergibt sich, indem PCS-Schwarz (L*=0, a*=b*=0) durch die gewählte B2A-Tabelle geführt wird, um den Farbauftrag zu erhalten, den das Profil für Schwarz wählt, und dieser Farbauftrag anschließend über A2B1 zurückgelesen wird. Der Gesamtfarbauftrag (TAC) ist die Summe dieses Farbauftrags. Die absolute Kolorimetrie zeigt die Eigenfarbe des Bedruckstoffs; die relative bezieht sie auf ein perfektes Weiß.</v>
+        <v>L* Ausgabe (Tonwert)</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Relative</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B274" t="str">
-        <v>Relativ</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Absolute</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B275" t="str">
-        <v>Absolut</v>
+        <v>Kolorimetrie der Extremwerte</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>White point</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B276" t="str">
-        <v>Weißpunkt</v>
+        <v>Die Enden des Wiedergabeumfangs des Profils: das Weiß des Bedruckstoffs, das dunkelste Schwarz, das es druckt, der Farbauftrag, den dieses Schwarz kostet, und der Punkt, an dem jeder Farbton am gesättigtsten ist.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Black point</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B277" t="str">
-        <v>Schwarzpunkt</v>
+        <v>Der Weißpunkt ist die Farbe bei null Farbmittel — der blanke Bedruckstoff. Der Schwarzpunkt ergibt sich, indem PCS-Schwarz (L*=0, a*=b*=0) durch die gewählte B2A-Tabelle geführt wird, um den Farbauftrag zu erhalten, den das Profil für Schwarz wählt, und dieser Farbauftrag anschließend über A2B1 zurückgelesen wird. Der Gesamtfarbauftrag (TAC) ist die Summe dieses Farbauftrags. Die absolute Kolorimetrie zeigt die Eigenfarbe des Bedruckstoffs; die relative bezieht sie auf ein perfektes Weiß.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Inking at black point</v>
+        <v>Relative</v>
       </c>
       <c r="B278" t="str">
-        <v>Farbauftrag am Schwarzpunkt</v>
+        <v>Relativ</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>TAC</v>
+        <v>Absolute</v>
       </c>
       <c r="B279" t="str">
-        <v>TAC</v>
+        <v>Absolut</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>White point</v>
       </c>
       <c r="B280" t="str">
-        <v>Dieses Profil hat kein Medien-Weißpunkt-Tag, daher ist die absolute Kolorimetrie nicht verfügbar.</v>
+        <v>Weißpunkt</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>Black point</v>
       </c>
       <c r="B281" t="str">
-        <v>Die Kolorimetrie der Extremwerte ist nur für Ausgabeprofile (Drucker) verfügbar — sie setzt voraus, dass null Farbmittel dem blanken Bedruckstoff entspricht.</v>
+        <v>Schwarzpunkt</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Vollton gegenüber maximalem Chroma</v>
+        <v>Farbauftrag am Schwarzpunkt</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>TAC</v>
       </c>
       <c r="B283" t="str">
-        <v>Wo jede Farbecke landet und der farbigste Punkt auf dem Weg dorthin. Gemessen über A2B1, daher ändern sich diese Zeilen nicht mit dem Render-Intent oben. Bei einem gutmütigen Profil stimmen beide Zeilen überein; wird das maximale Chroma vor dem Vollton erreicht, verdunkelt die Farbe darüber hinaus nur noch.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Hue</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B284" t="str">
-        <v>Farbton</v>
+        <v>Dieses Profil hat kein Medien-Weißpunkt-Tag, daher ist die absolute Kolorimetrie nicht verfügbar.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Full tone</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B285" t="str">
-        <v>Vollton</v>
+        <v>Die Kolorimetrie der Extremwerte ist nur für Ausgabeprofile (Drucker) verfügbar — sie setzt voraus, dass null Farbmittel dem blanken Bedruckstoff entspricht.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Max C*</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B286" t="str">
-        <v>Max. C*</v>
+        <v>Vollton gegenüber maximalem Chroma</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>At ink</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B287" t="str">
-        <v>Bei Farbauftrag</v>
+        <v>Wo jede Farbecke landet und der farbigste Punkt auf dem Weg dorthin. Gemessen über A2B1, daher ändern sich diese Zeilen nicht mit dem Render-Intent oben. Bei einem gutmütigen Profil stimmen beide Zeilen überein; wird das maximale Chroma vor dem Vollton erreicht, verdunkelt die Farbe darüber hinaus nur noch.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>Hue</v>
       </c>
       <c r="B288" t="str">
-        <v>Das maximale Chroma wird vor dem Vollton erreicht — Farbe darüber hinaus verdunkelt nur.</v>
+        <v>Farbton</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Full tone</v>
       </c>
       <c r="B289" t="str">
-        <v>Farbverbrauch in den Tiefen</v>
+        <v>Vollton</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Max C*</v>
       </c>
       <c r="B290" t="str">
-        <v>Vier gerade Pfade durch die a*b*-Ebene bei einer konstanten, bewusst dunklen Helligkeit, geführt durch die gewählte B2A-Tabelle. Alle Abtastwerte teilen dieselbe L*, sodass jeder abrupte Sprung oder jede Umkehr eines Farbmittels allein aus der Behandlung von Farbton und Chroma stammt — die Signatur eines Gamut-Mapping-Artefakts in den Tiefen.</v>
+        <v>Max. C*</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>At ink</v>
       </c>
       <c r="B291" t="str">
-        <v>Der Farbverbrauch in den Tiefen ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
+        <v>Bei Farbauftrag</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Constant L* plane</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B292" t="str">
-        <v>Ebene konstanter L*</v>
+        <v>Das maximale Chroma wird vor dem Vollton erreicht — Farbe darüber hinaus verdunkelt nur.</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>black-point compensated from</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B293" t="str">
-        <v>schwarzpunktkompensiert ab</v>
+        <v>Farbverbrauch in den Tiefen</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Position along path</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B294" t="str">
-        <v>Position entlang des Pfades</v>
+        <v>Vier gerade Pfade durch die a*b*-Ebene bei einer konstanten, bewusst dunklen Helligkeit, geführt durch die gewählte B2A-Tabelle. Alle Abtastwerte teilen dieselbe L*, sodass jeder abrupte Sprung oder jede Umkehr eines Farbmittels allein aus der Behandlung von Farbton und Chroma stammt — die Signatur eines Gamut-Mapping-Artefakts in den Tiefen.</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Path</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B295" t="str">
-        <v>Pfad</v>
+        <v>Der Farbverbrauch in den Tiefen ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Cyan</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B296" t="str">
-        <v>Cyan</v>
+        <v>Ebene konstanter L*</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Magenta</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B297" t="str">
-        <v>Magenta</v>
+        <v>schwarzpunktkompensiert ab</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Yellow</v>
+        <v>Position along path</v>
       </c>
       <c r="B298" t="str">
-        <v>Gelb</v>
+        <v>Position entlang des Pfades</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Red</v>
+        <v>Path</v>
       </c>
       <c r="B299" t="str">
-        <v>Rot</v>
+        <v>Pfad</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Green</v>
+        <v>Cyan</v>
       </c>
       <c r="B300" t="str">
-        <v>Grün</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Blue</v>
+        <v>Magenta</v>
       </c>
       <c r="B301" t="str">
-        <v>Blau</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Black</v>
+        <v>Yellow</v>
       </c>
       <c r="B302" t="str">
-        <v>Schwarz</v>
+        <v>Gelb</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Perceptual</v>
+        <v>Red</v>
       </c>
       <c r="B303" t="str">
-        <v>Perzeptiv</v>
+        <v>Rot</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Green</v>
       </c>
       <c r="B304" t="str">
-        <v>Relativ farbmetrisch</v>
+        <v>Grün</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Saturation</v>
+        <v>Blue</v>
       </c>
       <c r="B305" t="str">
-        <v>Sättigung</v>
+        <v>Blau</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Black</v>
       </c>
       <c r="B306" t="str">
-        <v>Absolut farbmetrisch</v>
+        <v>Schwarz</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Profile Statistics</v>
+        <v>Perceptual</v>
       </c>
       <c r="B307" t="str">
-        <v>Profilstatistik</v>
+        <v>Perzeptiv</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B308" t="str">
-        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
+        <v>Relativ farbmetrisch</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B309" t="str">
-        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
+        <v>Sättigung</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Rendering intent</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B310" t="str">
-        <v>Render-Intent</v>
+        <v>Absolut farbmetrisch</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B311" t="str">
-        <v>Gamut-Volumen (ΔE³)</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B312" t="str">
-        <v>Roundtrip-ΔE</v>
+        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B313" t="str">
-        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
+        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>mean</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B314" t="str">
-        <v>Mittel</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>P90</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B315" t="str">
-        <v>P90</v>
+        <v>Gamut-Volumen (ΔE³)</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>max</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B316" t="str">
-        <v>Max.</v>
+        <v>Roundtrip-ΔE</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Analysing…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B317" t="str">
-        <v>Analyse läuft…</v>
+        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Analysis</v>
+        <v>mean</v>
       </c>
       <c r="B318" t="str">
-        <v>Analyse</v>
+        <v>Mittel</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>P90</v>
       </c>
       <c r="B319" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Plot</v>
+        <v>max</v>
       </c>
       <c r="B320" t="str">
-        <v>Diagramm</v>
+        <v>Max.</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Raw Output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B321" t="str">
-        <v>Rohausgabe</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>XML</v>
+        <v>Analysis</v>
       </c>
       <c r="B322" t="str">
-        <v>XML</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>JSON</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B323" t="str">
-        <v>JSON</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Curves</v>
+        <v>Plot</v>
       </c>
       <c r="B324" t="str">
-        <v>Kurven</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Input curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B325" t="str">
-        <v>Eingangskurven</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Output curves</v>
+        <v>XML</v>
       </c>
       <c r="B326" t="str">
-        <v>Ausgangskurven</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>CLUT image</v>
+        <v>JSON</v>
       </c>
       <c r="B327" t="str">
-        <v>CLUT-Bild</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Gamut image</v>
+        <v>Curves</v>
       </c>
       <c r="B328" t="str">
-        <v>Gamut-Bild</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Chromaticity</v>
+        <v>Input curves</v>
       </c>
       <c r="B329" t="str">
-        <v>Chromazität</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Scatter plot</v>
+        <v>Output curves</v>
       </c>
       <c r="B330" t="str">
-        <v>Streudiagramm</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Tone response curve</v>
+        <v>CLUT image</v>
       </c>
       <c r="B331" t="str">
-        <v>Tonwertkurve</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Curve table</v>
+        <v>Gamut image</v>
       </c>
       <c r="B332" t="str">
-        <v>Kurventabelle</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Tables</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B333" t="str">
-        <v>Tabellen</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Data</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B334" t="str">
-        <v>Daten</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Evaluate</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B335" t="str">
-        <v>Auswerten</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Loading…</v>
+        <v>Curve table</v>
       </c>
       <c r="B336" t="str">
-        <v>Wird geladen…</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Input</v>
+        <v>Tables</v>
       </c>
       <c r="B337" t="str">
-        <v>Eingang</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Output</v>
+        <v>Data</v>
       </c>
       <c r="B338" t="str">
-        <v>Ausgang</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Floating point</v>
+        <v>Evaluate</v>
       </c>
       <c r="B339" t="str">
-        <v>Gleitkomma</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Grid point</v>
+        <v>Loading…</v>
       </c>
       <c r="B340" t="str">
-        <v>Gitterpunkt</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Normalized</v>
+        <v>Input</v>
       </c>
       <c r="B341" t="str">
-        <v>Normalisiert</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Human</v>
+        <v>Output</v>
       </c>
       <c r="B342" t="str">
-        <v>Lesbar</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Device → PCS</v>
+        <v>Floating point</v>
       </c>
       <c r="B343" t="str">
-        <v>Gerät → PCS</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>PCS → Device</v>
+        <v>Grid point</v>
       </c>
       <c r="B344" t="str">
-        <v>PCS → Gerät</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>No CLUT grid</v>
+        <v>Normalized</v>
       </c>
       <c r="B345" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Loading…</v>
+        <v>Human</v>
       </c>
       <c r="B346" t="str">
-        <v>Wird geladen…</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B347" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Invalid profile URL:</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B348" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B349" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Loading…</v>
       </c>
       <c r="B350" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B351" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B352" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B353" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Security</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B354" t="str">
-        <v>Sicherheit</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Conformance</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B355" t="str">
-        <v>Konformität</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Quality</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B356" t="str">
-        <v>Qualität</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>REPORT</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B357" t="str">
-        <v>BERICHT</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>FAIL</v>
+        <v>Security</v>
       </c>
       <c r="B358" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>checks</v>
+        <v>Conformance</v>
       </c>
       <c r="B359" t="str">
-        <v>Prüfungen</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Quality</v>
       </c>
       <c r="B360" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B361" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B362" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B363" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B364" t="str">
-        <v>Abonnieren</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B365" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B366" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B367" t="str">
-        <v>Schließen</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B368" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B369" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B370" t="str">
-        <v>sie@example.com</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B371" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B372" t="str">
-        <v>(optional)</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B373" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B374" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B375" t="str">
-        <v>Abbrechen</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B376" t="str">
-        <v>Abonnieren</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B377" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B378" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B379" t="str">
-        <v>Schließen</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B380" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B381" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B382" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B383" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B384" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B385" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B386" t="str">
-        <v>Fehler:</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B387" t="str">
-        <v>In XML konvertieren</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B388" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B389" t="str">
-        <v>In ICC konvertieren</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B390" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B391" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B392" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B393" t="str">
-        <v>ICC-Profil laden</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B394" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B395" t="str">
-        <v>Profil-ID</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B396" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B397" t="str">
-        <v>Tag-Name</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B398" t="str">
-        <v>ID</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B399" t="str">
-        <v>Offset</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B400" t="str">
-        <v>Größe</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B401" t="str">
-        <v>Auffüllung</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B402" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B403" t="str">
-        <v>Typ</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B404" t="str">
-        <v>Array von {type}</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B405" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B406" t="str">
-        <v>Bytes</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B407" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B408" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B409" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B410" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B411" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B412" t="str">
-        <v>Profil ist gültig</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B413" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B414" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B415" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B416" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B417" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B418" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B419" t="str">
-        <v>Gültig</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B420" t="str">
-        <v>Warnung</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B421" t="str">
-        <v>Fehler</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B422" t="str">
-        <v>Unbekannt</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B423" t="str">
-        <v>Bestanden</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B424" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B425" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B426" t="str">
-        <v>Validierungsdetail</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B427" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B428" t="str">
-        <v>Feld</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B429" t="str">
-        <v>Aktueller Wert</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B430" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B431" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B432" t="str">
-        <v>Ungültig</v>
+        <v>Feld</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B433" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Aktueller Wert</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B434" t="str">
-        <v>Schließen</v>
+        <v>Erforderlich: 0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B435" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Erwartet: {value}</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B436" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Ungültig</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B437" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B438" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B439" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Lade XML-Editor…</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B440" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Lade JSON-Editor…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B441" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B442" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B443" t="str">
-        <v>Einrückung</v>
+        <v>● nicht gespeicherte XML-Änderungen</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B444" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>● nicht gespeicherte JSON-Änderungen</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B445" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B446" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B447" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B448" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B445" t="str">
+      <c r="B449" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-De.xlsx
+++ b/translations/Eng-De.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B449"/>
+  <dimension ref="A1:B466"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2803,1207 +2803,1343 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Cyan</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B300" t="str">
-        <v>Cyan</v>
+        <v>Primärfarben-Pfade durch Neutral</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Magenta</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B301" t="str">
-        <v>Magenta</v>
+        <v>Drei Pfade im Gamut — Cyan→Rot, Magenta→Grün, Gelb→Blau — jeder durch die Neutralachse bei der mittleren Helligkeit seiner Endpunkte, durch die gewählte B2A-Tabelle geführt. Jeder Messpunkt liegt im Gamut, daher ist – anders als bei den Schattenpfaden – jede abrupte Stufe oder Umkehr eines Farbmittels ein CLUT-Glättungsfehler und kein Gamut-Mapping-Artefakt.</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Yellow</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B302" t="str">
-        <v>Gelb</v>
+        <v>Primärfarben-Pfade sind nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Red</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B303" t="str">
-        <v>Rot</v>
+        <v>Position entlang des Pfades (Neutral in der Mitte)</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Green</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B304" t="str">
-        <v>Grün</v>
+        <v>Schwarzpunktkompensation für diese Absicht angewendet.</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Blue</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B305" t="str">
-        <v>Blau</v>
+        <v>Farbverbrauchsstatistik</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Black</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B306" t="str">
-        <v>Schwarz</v>
+        <v>Wie viel von jedem Farbmittel das Profil aufträgt, als Summe und als Anteil am Gesamtwert — die Farbverbrauchssignatur der Separation.</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Perceptual</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B307" t="str">
-        <v>Perzeptiv</v>
+        <v>Die Farbverbrauchsstatistik ist nur für Ausgabeprofile (Drucker) verfügbar.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B308" t="str">
-        <v>Relativ farbmetrisch</v>
+        <v>Neutralachse</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Saturation</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B309" t="str">
-        <v>Sättigung</v>
+        <v>Mittlere Deckung</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Share of ink</v>
       </c>
       <c r="B310" t="str">
-        <v>Absolut farbmetrisch</v>
+        <v>Farbanteil</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Profile Statistics</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B311" t="str">
-        <v>Profilstatistik</v>
+        <v>Der Farbanteil ist der Fingerabdruck des Neutralaufbaus — der Anteil jedes Farbmittels an der gesamten aufgetragenen Farbe, unabhängig von der Anzahl der Messpunkte.</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B312" t="str">
-        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
+        <v>Punkte im Gamut</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B313" t="str">
-        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
+        <v>Der Farbverbrauch über alle Gamut-Farben benötigt die B2A-Gamutgrenze, die noch nicht implementiert ist — ausstehend.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Rendering intent</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B314" t="str">
-        <v>Render-Intent</v>
+        <v>Keine Farbmitteldaten zum Zusammenfassen.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B315" t="str">
-        <v>Gamut-Volumen (ΔE³)</v>
+        <v>Wählen Sie unten eine B2A-Tabelle (PCS→Gerät), um auch ein Graustufenbild der Farbdeckung für jedes Farbmittel anzuzeigen.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B316" t="str">
-        <v>Roundtrip-ΔE</v>
+        <v>Farbdeckung jedes Farbmittels über dasselbe Gitter (dunkler = mehr Farbe).</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Cyan</v>
       </c>
       <c r="B317" t="str">
-        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>mean</v>
+        <v>Magenta</v>
       </c>
       <c r="B318" t="str">
-        <v>Mittel</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>P90</v>
+        <v>Yellow</v>
       </c>
       <c r="B319" t="str">
-        <v>P90</v>
+        <v>Gelb</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>max</v>
+        <v>Red</v>
       </c>
       <c r="B320" t="str">
-        <v>Max.</v>
+        <v>Rot</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Analysing…</v>
+        <v>Green</v>
       </c>
       <c r="B321" t="str">
-        <v>Analyse läuft…</v>
+        <v>Grün</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Analysis</v>
+        <v>Blue</v>
       </c>
       <c r="B322" t="str">
-        <v>Analyse</v>
+        <v>Blau</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Black</v>
       </c>
       <c r="B323" t="str">
-        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
+        <v>Schwarz</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Plot</v>
+        <v>Perceptual</v>
       </c>
       <c r="B324" t="str">
-        <v>Diagramm</v>
+        <v>Perzeptiv</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Raw Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B325" t="str">
-        <v>Rohausgabe</v>
+        <v>Relativ farbmetrisch</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>XML</v>
+        <v>Saturation</v>
       </c>
       <c r="B326" t="str">
-        <v>XML</v>
+        <v>Sättigung</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>JSON</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B327" t="str">
-        <v>JSON</v>
+        <v>Absolut farbmetrisch</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Curves</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B328" t="str">
-        <v>Kurven</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Input curves</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B329" t="str">
-        <v>Eingangskurven</v>
+        <v>Profilweite Kennzahlen je Render-Intent: das vom Gerät→PCS-Transform umschlossene Gamut-Volumen (ΔE*ab³) und die B2A-Roundtrip-Genauigkeit — ΔE*ab eines Lab → Gerät → Lab-Umlaufs durch das Profil.</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Output curves</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B330" t="str">
-        <v>Ausgangskurven</v>
+        <v>Keine Gerät↔PCS-CLUTs in diesem Profil — die Profilstatistik ist nicht anwendbar (z. B. ein Matrix/TRC-Displayprofil).</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>CLUT image</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B331" t="str">
-        <v>CLUT-Bild</v>
+        <v>Render-Intent</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut image</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B332" t="str">
-        <v>Gamut-Bild</v>
+        <v>Gamut-Volumen (ΔE³)</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Chromaticity</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B333" t="str">
-        <v>Chromazität</v>
+        <v>Roundtrip-ΔE</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Scatter plot</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B334" t="str">
-        <v>Streudiagramm</v>
+        <v>Die Gamut-Grenze ist kollabiert oder war größtenteils undefiniert; dieses Gamut-Volumen ist unzuverlässig.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Tone response curve</v>
+        <v>mean</v>
       </c>
       <c r="B335" t="str">
-        <v>Tonwertkurve</v>
+        <v>Mittel</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Curve table</v>
+        <v>P90</v>
       </c>
       <c r="B336" t="str">
-        <v>Kurventabelle</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Tables</v>
+        <v>max</v>
       </c>
       <c r="B337" t="str">
-        <v>Tabellen</v>
+        <v>Max.</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Data</v>
+        <v>Analysing…</v>
       </c>
       <c r="B338" t="str">
-        <v>Daten</v>
+        <v>Analyse läuft…</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Evaluate</v>
+        <v>Analysis</v>
       </c>
       <c r="B339" t="str">
-        <v>Auswerten</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Loading…</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B340" t="str">
-        <v>Wird geladen…</v>
+        <v>Profilweite Qualitätsanalysen, abgeleitet aus der Gerät→PCS-Transformation.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Input</v>
+        <v>Plot</v>
       </c>
       <c r="B341" t="str">
-        <v>Eingang</v>
+        <v>Diagramm</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Output</v>
+        <v>Raw Output</v>
       </c>
       <c r="B342" t="str">
-        <v>Ausgang</v>
+        <v>Rohausgabe</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Floating point</v>
+        <v>XML</v>
       </c>
       <c r="B343" t="str">
-        <v>Gleitkomma</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Grid point</v>
+        <v>JSON</v>
       </c>
       <c r="B344" t="str">
-        <v>Gitterpunkt</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Normalized</v>
+        <v>Curves</v>
       </c>
       <c r="B345" t="str">
-        <v>Normalisiert</v>
+        <v>Kurven</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Human</v>
+        <v>Input curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Lesbar</v>
+        <v>Eingangskurven</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Device → PCS</v>
+        <v>Output curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Gerät → PCS</v>
+        <v>Ausgangskurven</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>PCS → Device</v>
+        <v>CLUT image</v>
       </c>
       <c r="B348" t="str">
-        <v>PCS → Gerät</v>
+        <v>CLUT-Bild</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut image</v>
       </c>
       <c r="B349" t="str">
-        <v>Kein CLUT-Gitter</v>
+        <v>Gamut-Bild</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Loading…</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B350" t="str">
-        <v>Wird geladen…</v>
+        <v>Chromazität</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B351" t="str">
-        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
+        <v>Streudiagramm</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B352" t="str">
-        <v>Ungültige Profil-URL:</v>
+        <v>Tonwertkurve</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curve table</v>
       </c>
       <c r="B353" t="str">
-        <v>Profil konnte nicht abgerufen werden von</v>
+        <v>Kurventabelle</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Tables</v>
       </c>
       <c r="B354" t="str">
-        <v>Ein ICC-Profil von dieser externen Website laden?</v>
+        <v>Tabellen</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Data</v>
       </c>
       <c r="B355" t="str">
-        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
+        <v>Daten</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B356" t="str">
-        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
+        <v>Auswerten</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading…</v>
       </c>
       <c r="B357" t="str">
-        <v>Profile-Assessment-WG-Bericht</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Security</v>
+        <v>Input</v>
       </c>
       <c r="B358" t="str">
-        <v>Sicherheit</v>
+        <v>Eingang</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Conformance</v>
+        <v>Output</v>
       </c>
       <c r="B359" t="str">
-        <v>Konformität</v>
+        <v>Ausgang</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Quality</v>
+        <v>Floating point</v>
       </c>
       <c r="B360" t="str">
-        <v>Qualität</v>
+        <v>Gleitkomma</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>REPORT</v>
+        <v>Grid point</v>
       </c>
       <c r="B361" t="str">
-        <v>BERICHT</v>
+        <v>Gitterpunkt</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>FAIL</v>
+        <v>Normalized</v>
       </c>
       <c r="B362" t="str">
-        <v>FEHLGESCHLAGEN</v>
+        <v>Normalisiert</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>checks</v>
+        <v>Human</v>
       </c>
       <c r="B363" t="str">
-        <v>Prüfungen</v>
+        <v>Lesbar</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B364" t="str">
-        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
+        <v>Gerät → PCS</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B365" t="str">
-        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
+        <v>PCS → Gerät</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ICC Profile Tool</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B366" t="str">
-        <v>ICC-Profil-Tool</v>
+        <v>Kein CLUT-Gitter</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Powered by {lib}</v>
+        <v>Loading…</v>
       </c>
       <c r="B367" t="str">
-        <v>Betrieben mit {lib}</v>
+        <v>Wird geladen…</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Subscribe</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B368" t="str">
-        <v>Abonnieren</v>
+        <v>Neutral = im Gamut · rot = außerhalb des Gamuts</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B369" t="str">
-        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
+        <v>Ungültige Profil-URL:</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Get notified about new releases</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B370" t="str">
-        <v>Bei neuen Releases benachrichtigt werden</v>
+        <v>Profil konnte nicht abgerufen werden von</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Close</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B371" t="str">
-        <v>Schließen</v>
+        <v>Ein ICC-Profil von dieser externen Website laden?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B372" t="str">
-        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
+        <v>Profile-Assessment-WG-Bericht wird geladen…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Email address</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B373" t="str">
-        <v>E-Mail-Adresse</v>
+        <v>Profile-Assessment-WG-Prüfungen werden ausgeführt…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>you@example.com</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B374" t="str">
-        <v>sie@example.com</v>
+        <v>Profile-Assessment-WG-Bericht</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Security</v>
       </c>
       <c r="B375" t="str">
-        <v>Wofür werden Sie profiletool nutzen?</v>
+        <v>Sicherheit</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>(optional)</v>
+        <v>Conformance</v>
       </c>
       <c r="B376" t="str">
-        <v>(optional)</v>
+        <v>Konformität</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Quality</v>
       </c>
       <c r="B377" t="str">
-        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
+        <v>Qualität</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B378" t="str">
-        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
+        <v>BERICHT</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B379" t="str">
-        <v>Abbrechen</v>
+        <v>FEHLGESCHLAGEN</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B380" t="str">
-        <v>Abonnieren</v>
+        <v>Prüfungen</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B381" t="str">
-        <v>Danke — wir melden uns.</v>
+        <v>Erstellt von iccPawgReport (iccDEV) · Checkliste der ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B382" t="str">
-        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
+        <v>ICC-Profil-Tool · betrieben mit IccProfLib</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B383" t="str">
-        <v>Schließen</v>
+        <v>ICC-Profil-Tool</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B384" t="str">
-        <v>Datenschutzhinweis</v>
+        <v>Betrieben mit {lib}</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B385" t="str">
-        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B386" t="str">
-        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
+        <v>Bei neuen profiletool-Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B387" t="str">
-        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
+        <v>Bei neuen Releases benachrichtigt werden</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B388" t="str">
-        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B389" t="str">
-        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
+        <v>Wir benachrichtigen Sie per E-Mail, sobald ein neues Major- oder Minor-Release von profiletool erscheint. Patch-Releases werden übersprungen. Ihre Adresse wird manuell geprüft, bevor sie aufgenommen wird.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B390" t="str">
-        <v>Fehler:</v>
+        <v>E-Mail-Adresse</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B391" t="str">
-        <v>In XML konvertieren</v>
+        <v>sie@example.com</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B392" t="str">
-        <v>In JSON konvertieren</v>
+        <v>Wofür werden Sie profiletool nutzen?</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B393" t="str">
-        <v>In ICC konvertieren</v>
+        <v>(optional)</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B394" t="str">
-        <v>Konvertiere in XML…</v>
+        <v>z. B. ICC-Profile für Druckkalibrierung evaluieren</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B395" t="str">
-        <v>Konvertiere in JSON…</v>
+        <v>Ich willige ein, E-Mails über profiletool-Releases zu erhalten. Ich kann mich jederzeit abmelden.</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B396" t="str">
-        <v>Konvertiere in ICC…</v>
+        <v>Abbrechen</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B397" t="str">
-        <v>ICC-Profil laden</v>
+        <v>Abonnieren</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B398" t="str">
-        <v>Ablagebereich für ICC-Profil-Dateien</v>
+        <v>Danke — wir melden uns.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B399" t="str">
-        <v>Profil-ID</v>
+        <v>Nach Freigabe erhalten Sie eine Willkommens-E-Mail. Danach hören Sie nur dann von uns, wenn ein neues profiletool-Release erscheint.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>Keine Tags gefunden.</v>
+        <v>Schließen</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B401" t="str">
-        <v>Tag-Name</v>
+        <v>Datenschutzhinweis</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B402" t="str">
-        <v>ID</v>
+        <v>Bitte geben Sie eine gültige E-Mail-Adresse ein.</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B403" t="str">
-        <v>Offset</v>
+        <v>Zu viele Anfragen. Bitte versuchen Sie es später erneut.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B404" t="str">
-        <v>Größe</v>
+        <v>Bitte überprüfen Sie das Formular und versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>Auffüllung</v>
+        <v>Anfrage konnte nicht gesendet werden. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>Bytes seit dem Laden geändert</v>
+        <v>Netzwerkfehler. Bitte versuchen Sie es erneut.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B407" t="str">
-        <v>Typ</v>
+        <v>Fehler:</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B408" t="str">
-        <v>Array von {type}</v>
+        <v>In XML konvertieren</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B409" t="str">
-        <v>(Kein Inhalt)</v>
+        <v>In JSON konvertieren</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B410" t="str">
-        <v>Bytes</v>
+        <v>In ICC konvertieren</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B411" t="str">
-        <v>Lade vollständige Beschreibung…</v>
+        <v>Konvertiere in XML…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B412" t="str">
-        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
+        <v>Konvertiere in JSON…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B413" t="str">
-        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
+        <v>Konvertiere in ICC…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B414" t="str">
-        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
+        <v>ICC-Profil laden</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B415" t="str">
-        <v>Keine Validierungsausgabe</v>
+        <v>Ablagebereich für ICC-Profil-Dateien</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B416" t="str">
-        <v>Profil ist gültig</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B417" t="str">
-        <v>Profil hat Warnung(en)</v>
+        <v>Keine Tags gefunden.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B418" t="str">
-        <v>Profil ist nicht konform</v>
+        <v>Tag-Name</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B419" t="str">
-        <v>Kritischer Validierungsfehler</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B420" t="str">
-        <v>Unbekannter Validierungsstatus</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B421" t="str">
-        <v>Kritisch — nur zur Ansicht angezeigt</v>
+        <v>Größe</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B422" t="str">
-        <v>Keine Warnungen oder Fehler gefunden.</v>
+        <v>Auffüllung</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B423" t="str">
-        <v>Gültig</v>
+        <v>Bytes seit dem Laden geändert</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B424" t="str">
-        <v>Warnung</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B425" t="str">
-        <v>Fehler</v>
+        <v>Array von {type}</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B426" t="str">
-        <v>Unbekannt</v>
+        <v>(Kein Inhalt)</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B427" t="str">
-        <v>Bestanden</v>
+        <v>Bytes</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B428" t="str">
-        <v>Fehlgeschlagen</v>
+        <v>Lade vollständige Beschreibung…</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B429" t="str">
-        <v>Im Kontext anzeigen</v>
+        <v>Vollständige Beschreibung konnte nicht geladen werden:</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B430" t="str">
-        <v>Validierungsdetail</v>
+        <v>Dieses Profil konnte nicht vollständig gelesen werden und darf nicht angewendet werden. Der Header und das Tag-Verzeichnis unten dienen nur zur Ansicht.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B431" t="str">
-        <v>Ausgelöst durch</v>
+        <v>Tag-Inhalt nicht verfügbar — das Profil konnte nicht vollständig gelesen werden.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B432" t="str">
-        <v>Feld</v>
+        <v>Keine Validierungsausgabe</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B433" t="str">
-        <v>Aktueller Wert</v>
+        <v>Profil ist gültig</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B434" t="str">
-        <v>Erforderlich: 0</v>
+        <v>Profil hat Warnung(en)</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B435" t="str">
-        <v>Erwartet: {value}</v>
+        <v>Profil ist nicht konform</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B436" t="str">
-        <v>Ungültig</v>
+        <v>Kritischer Validierungsfehler</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B437" t="str">
-        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+        <v>Unbekannter Validierungsstatus</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B438" t="str">
-        <v>Schließen</v>
+        <v>Kritisch — nur zur Ansicht angezeigt</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B439" t="str">
-        <v>Lade XML-Editor…</v>
+        <v>Keine Warnungen oder Fehler gefunden.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B440" t="str">
-        <v>Lade JSON-Editor…</v>
+        <v>Gültig</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B441" t="str">
-        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Warnung</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B442" t="str">
-        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+        <v>Fehler</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B443" t="str">
-        <v>● nicht gespeicherte XML-Änderungen</v>
+        <v>Unbekannt</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B444" t="str">
-        <v>● nicht gespeicherte JSON-Änderungen</v>
+        <v>Bestanden</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B445" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+        <v>Fehlgeschlagen</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B446" t="str">
-        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+        <v>Im Kontext anzeigen</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B447" t="str">
-        <v>Einrückung</v>
+        <v>Validierungsdetail</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B448" t="str">
-        <v>Schlüssel sortieren</v>
+        <v>Ausgelöst durch</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B449" t="str">
+        <v>Feld</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B450" t="str">
+        <v>Aktueller Wert</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B451" t="str">
+        <v>Erforderlich: 0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B452" t="str">
+        <v>Erwartet: {value}</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B453" t="str">
+        <v>Ungültig</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B454" t="str">
+        <v>Dieser Befund konnte keinem bestimmten Feld zugeordnet werden.</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B455" t="str">
+        <v>Schließen</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B456" t="str">
+        <v>Lade XML-Editor…</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B457" t="str">
+        <v>Lade JSON-Editor…</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B458" t="str">
+        <v>Sie haben nicht gespeicherte XML-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B459" t="str">
+        <v>Sie haben nicht gespeicherte JSON-Änderungen. Mit einer neuen Konvertierung aus dem ICC-Profil überschreiben?</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B460" t="str">
+        <v>● nicht gespeicherte XML-Änderungen</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B461" t="str">
+        <v>● nicht gespeicherte JSON-Änderungen</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B462" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In XML konvertieren&lt;/em&gt;, um eine bearbeitbare XML-Darstellung dieses Profils zu erzeugen. Das XML wird vom gleichen IccLibXML-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToXml&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B463" t="str">
+        <v>Klicken Sie auf &lt;em&gt;In JSON konvertieren&lt;/em&gt;, um eine bearbeitbare JSON-Darstellung dieses Profils zu erzeugen. Das JSON wird vom gleichen IccLibJSON-Codepfad erzeugt, den auch das Upstream-Tool &lt;code&gt;IccToJson&lt;/code&gt; verwendet.</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B464" t="str">
+        <v>Einrückung</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B465" t="str">
+        <v>Schlüssel sortieren</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B449" t="str">
+      <c r="B466" t="str">
         <v>Profil aus Änderungen geschrieben, aber Neuvalidierung fehlgeschlagen:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
   </ignoredErrors>
 </worksheet>
 </file>